--- a/data.xlsx
+++ b/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kiuchi-my.sharepoint.com/personal/isozaki_kiuchi_co_jp/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kiuchi-my.sharepoint.com/personal/isozaki_kiuchi_co_jp/Documents/fmsf-phone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="791" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0783A071-25C2-4306-BFFD-287CCEFF3F6A}"/>
+  <xr:revisionPtr revIDLastSave="799" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95DB5FCE-D6FB-43FE-810B-B4C88B68F019}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
+    <workbookView xWindow="11844" yWindow="348" windowWidth="11544" windowHeight="12360" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
   </bookViews>
   <sheets>
     <sheet name="電話帳リスト251113" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="1060">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="1065">
   <si>
     <t>氏名</t>
   </si>
@@ -4156,6 +4156,50 @@
     <rPh sb="3" eb="5">
       <t>ギョウシャ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>屋根・板金工事</t>
+    <rPh sb="0" eb="2">
+      <t>ヤネ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>バンキン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>有限会社ピーエス板金工業</t>
+    <rPh sb="0" eb="4">
+      <t>ユウゲンガイシャ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バンキン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上宮 広宣</t>
+    <rPh sb="0" eb="2">
+      <t>ウエミヤ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〒420-0911静岡県静岡市葵区瀬名1-17-11</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>054-655-0014</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4572,7 +4616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED22340-6398-430F-AD0F-E88DFD8C2F52}">
-  <dimension ref="A1:J176"/>
+  <dimension ref="A1:J177"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.8984375" customWidth="1"/>
@@ -7954,35 +7998,27 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="B119" t="s">
-        <v>518</v>
+        <v>1060</v>
       </c>
       <c r="C119" t="s">
-        <v>396</v>
+        <v>1061</v>
       </c>
       <c r="D119" t="s">
-        <v>397</v>
+        <v>959</v>
       </c>
       <c r="E119" t="s">
-        <v>395</v>
+        <v>1062</v>
       </c>
       <c r="F119" t="s">
-        <v>398</v>
+        <v>1063</v>
       </c>
       <c r="G119" t="s">
-        <v>399</v>
-      </c>
-      <c r="H119" t="s">
-        <v>400</v>
-      </c>
-      <c r="I119" t="s">
-        <v>401</v>
-      </c>
-      <c r="J119" t="s">
-        <v>402</v>
-      </c>
+        <v>1064</v>
+      </c>
+      <c r="J119" s="1"/>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
@@ -7992,28 +8028,28 @@
         <v>518</v>
       </c>
       <c r="C120" t="s">
-        <v>316</v>
+        <v>396</v>
       </c>
       <c r="D120" t="s">
-        <v>317</v>
+        <v>397</v>
       </c>
       <c r="E120" t="s">
-        <v>315</v>
+        <v>395</v>
       </c>
       <c r="F120" t="s">
-        <v>318</v>
+        <v>398</v>
       </c>
       <c r="G120" t="s">
-        <v>319</v>
+        <v>399</v>
       </c>
       <c r="H120" t="s">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="I120" t="s">
-        <v>321</v>
+        <v>401</v>
       </c>
       <c r="J120" t="s">
-        <v>322</v>
+        <v>402</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.45">
@@ -8021,31 +8057,31 @@
         <v>1059</v>
       </c>
       <c r="B121" t="s">
-        <v>907</v>
+        <v>518</v>
       </c>
       <c r="C121" t="s">
-        <v>702</v>
+        <v>316</v>
       </c>
       <c r="D121" t="s">
-        <v>703</v>
+        <v>317</v>
       </c>
       <c r="E121" t="s">
-        <v>704</v>
+        <v>315</v>
       </c>
       <c r="F121" t="s">
-        <v>884</v>
+        <v>318</v>
       </c>
       <c r="G121" t="s">
-        <v>705</v>
+        <v>319</v>
       </c>
       <c r="H121" t="s">
-        <v>706</v>
+        <v>320</v>
       </c>
       <c r="I121" t="s">
-        <v>707</v>
+        <v>321</v>
       </c>
       <c r="J121" t="s">
-        <v>708</v>
+        <v>322</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.45">
@@ -8053,31 +8089,31 @@
         <v>1059</v>
       </c>
       <c r="B122" t="s">
-        <v>516</v>
+        <v>907</v>
       </c>
       <c r="C122" t="s">
-        <v>300</v>
+        <v>702</v>
       </c>
       <c r="D122" t="s">
-        <v>301</v>
+        <v>703</v>
       </c>
       <c r="E122" t="s">
-        <v>299</v>
+        <v>704</v>
       </c>
       <c r="F122" t="s">
-        <v>302</v>
+        <v>884</v>
       </c>
       <c r="G122" t="s">
-        <v>303</v>
+        <v>705</v>
       </c>
       <c r="H122" t="s">
-        <v>304</v>
+        <v>706</v>
       </c>
       <c r="I122" t="s">
-        <v>305</v>
+        <v>707</v>
       </c>
       <c r="J122" t="s">
-        <v>306</v>
+        <v>708</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.45">
@@ -8085,25 +8121,31 @@
         <v>1059</v>
       </c>
       <c r="B123" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C123" t="s">
-        <v>618</v>
+        <v>300</v>
       </c>
       <c r="D123" t="s">
-        <v>656</v>
+        <v>301</v>
       </c>
       <c r="E123" t="s">
-        <v>657</v>
+        <v>299</v>
       </c>
       <c r="F123" t="s">
-        <v>878</v>
+        <v>302</v>
       </c>
       <c r="G123" t="s">
-        <v>658</v>
+        <v>303</v>
+      </c>
+      <c r="H123" t="s">
+        <v>304</v>
+      </c>
+      <c r="I123" t="s">
+        <v>305</v>
       </c>
       <c r="J123" t="s">
-        <v>659</v>
+        <v>306</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.45">
@@ -8117,10 +8159,10 @@
         <v>618</v>
       </c>
       <c r="D124" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E124" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="F124" t="s">
         <v>878</v>
@@ -8128,11 +8170,8 @@
       <c r="G124" t="s">
         <v>658</v>
       </c>
-      <c r="H124" t="s">
-        <v>663</v>
-      </c>
       <c r="J124" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.45">
@@ -8143,28 +8182,25 @@
         <v>514</v>
       </c>
       <c r="C125" t="s">
-        <v>284</v>
+        <v>618</v>
       </c>
       <c r="D125" t="s">
-        <v>285</v>
+        <v>661</v>
       </c>
       <c r="E125" t="s">
-        <v>283</v>
+        <v>662</v>
       </c>
       <c r="F125" t="s">
-        <v>286</v>
+        <v>878</v>
       </c>
       <c r="G125" t="s">
-        <v>287</v>
+        <v>658</v>
       </c>
       <c r="H125" t="s">
-        <v>288</v>
-      </c>
-      <c r="I125" t="s">
-        <v>289</v>
+        <v>663</v>
       </c>
       <c r="J125" t="s">
-        <v>290</v>
+        <v>664</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.45">
@@ -8177,23 +8213,26 @@
       <c r="C126" t="s">
         <v>284</v>
       </c>
+      <c r="D126" t="s">
+        <v>285</v>
+      </c>
       <c r="E126" t="s">
-        <v>814</v>
+        <v>283</v>
       </c>
       <c r="F126" t="s">
-        <v>893</v>
+        <v>286</v>
       </c>
       <c r="G126" t="s">
-        <v>815</v>
+        <v>287</v>
       </c>
       <c r="H126" t="s">
-        <v>816</v>
+        <v>288</v>
       </c>
       <c r="I126" t="s">
-        <v>817</v>
+        <v>289</v>
       </c>
       <c r="J126" t="s">
-        <v>818</v>
+        <v>290</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.45">
@@ -8206,26 +8245,23 @@
       <c r="C127" t="s">
         <v>284</v>
       </c>
-      <c r="D127" t="s">
-        <v>572</v>
-      </c>
       <c r="E127" t="s">
-        <v>833</v>
+        <v>814</v>
       </c>
       <c r="F127" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="G127" t="s">
-        <v>834</v>
+        <v>815</v>
       </c>
       <c r="H127" t="s">
-        <v>835</v>
+        <v>816</v>
       </c>
       <c r="I127" t="s">
-        <v>836</v>
+        <v>817</v>
       </c>
       <c r="J127" t="s">
-        <v>837</v>
+        <v>818</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
@@ -8233,28 +8269,31 @@
         <v>1059</v>
       </c>
       <c r="B128" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="C128" t="s">
-        <v>594</v>
+        <v>284</v>
       </c>
       <c r="D128" t="s">
-        <v>595</v>
+        <v>572</v>
+      </c>
+      <c r="E128" t="s">
+        <v>833</v>
       </c>
       <c r="F128" t="s">
-        <v>596</v>
+        <v>896</v>
       </c>
       <c r="G128" t="s">
-        <v>597</v>
+        <v>834</v>
       </c>
       <c r="H128" t="s">
-        <v>598</v>
+        <v>835</v>
       </c>
       <c r="I128" t="s">
-        <v>599</v>
+        <v>836</v>
       </c>
       <c r="J128" t="s">
-        <v>600</v>
+        <v>837</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.45">
@@ -8265,28 +8304,25 @@
         <v>529</v>
       </c>
       <c r="C129" t="s">
-        <v>443</v>
+        <v>594</v>
       </c>
       <c r="D129" t="s">
-        <v>444</v>
-      </c>
-      <c r="E129" t="s">
-        <v>442</v>
+        <v>595</v>
       </c>
       <c r="F129" t="s">
-        <v>445</v>
+        <v>596</v>
       </c>
       <c r="G129" t="s">
-        <v>446</v>
+        <v>597</v>
       </c>
       <c r="H129" t="s">
-        <v>447</v>
+        <v>598</v>
       </c>
       <c r="I129" t="s">
-        <v>448</v>
+        <v>599</v>
       </c>
       <c r="J129" t="s">
-        <v>449</v>
+        <v>600</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.45">
@@ -8294,31 +8330,31 @@
         <v>1059</v>
       </c>
       <c r="B130" t="s">
-        <v>501</v>
+        <v>529</v>
       </c>
       <c r="C130" t="s">
-        <v>138</v>
+        <v>443</v>
       </c>
       <c r="D130" t="s">
-        <v>139</v>
+        <v>444</v>
       </c>
       <c r="E130" t="s">
-        <v>137</v>
+        <v>442</v>
       </c>
       <c r="F130" t="s">
-        <v>140</v>
+        <v>445</v>
       </c>
       <c r="G130" t="s">
-        <v>141</v>
+        <v>446</v>
       </c>
       <c r="H130" t="s">
-        <v>142</v>
+        <v>447</v>
       </c>
       <c r="I130" t="s">
-        <v>143</v>
+        <v>448</v>
       </c>
       <c r="J130" t="s">
-        <v>144</v>
+        <v>449</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.45">
@@ -8326,31 +8362,31 @@
         <v>1059</v>
       </c>
       <c r="B131" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="C131" t="s">
-        <v>254</v>
+        <v>138</v>
       </c>
       <c r="D131" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="E131" t="s">
-        <v>253</v>
+        <v>137</v>
       </c>
       <c r="F131" t="s">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="G131" t="s">
-        <v>256</v>
+        <v>141</v>
       </c>
       <c r="H131" t="s">
-        <v>256</v>
+        <v>142</v>
       </c>
       <c r="I131" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="J131" t="s">
-        <v>258</v>
+        <v>144</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.45">
@@ -8358,31 +8394,31 @@
         <v>1059</v>
       </c>
       <c r="B132" t="s">
-        <v>903</v>
+        <v>512</v>
       </c>
       <c r="C132" t="s">
-        <v>607</v>
+        <v>254</v>
       </c>
       <c r="D132" t="s">
-        <v>608</v>
+        <v>165</v>
       </c>
       <c r="E132" t="s">
-        <v>609</v>
+        <v>253</v>
       </c>
       <c r="F132" t="s">
-        <v>874</v>
+        <v>255</v>
       </c>
       <c r="G132" t="s">
-        <v>610</v>
+        <v>256</v>
       </c>
       <c r="H132" t="s">
-        <v>611</v>
+        <v>256</v>
       </c>
       <c r="I132" t="s">
-        <v>612</v>
+        <v>257</v>
       </c>
       <c r="J132" t="s">
-        <v>613</v>
+        <v>258</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.45">
@@ -8396,10 +8432,10 @@
         <v>607</v>
       </c>
       <c r="D133" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="E133" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="F133" t="s">
         <v>874</v>
@@ -8411,10 +8447,10 @@
         <v>611</v>
       </c>
       <c r="I133" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="J133" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.45">
@@ -8422,31 +8458,31 @@
         <v>1059</v>
       </c>
       <c r="B134" t="s">
-        <v>530</v>
+        <v>903</v>
       </c>
       <c r="C134" t="s">
-        <v>458</v>
+        <v>607</v>
       </c>
       <c r="D134" t="s">
-        <v>165</v>
+        <v>614</v>
       </c>
       <c r="E134" t="s">
-        <v>457</v>
+        <v>615</v>
       </c>
       <c r="F134" t="s">
-        <v>459</v>
+        <v>874</v>
       </c>
       <c r="G134" t="s">
-        <v>460</v>
+        <v>610</v>
       </c>
       <c r="H134" t="s">
-        <v>461</v>
+        <v>611</v>
       </c>
       <c r="I134" t="s">
-        <v>462</v>
+        <v>616</v>
       </c>
       <c r="J134" t="s">
-        <v>463</v>
+        <v>617</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.45">
@@ -8459,8 +8495,11 @@
       <c r="C135" t="s">
         <v>458</v>
       </c>
+      <c r="D135" t="s">
+        <v>165</v>
+      </c>
       <c r="E135" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="F135" t="s">
         <v>459</v>
@@ -8472,7 +8511,7 @@
         <v>461</v>
       </c>
       <c r="I135" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="J135" t="s">
         <v>463</v>
@@ -8483,31 +8522,28 @@
         <v>1059</v>
       </c>
       <c r="B136" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C136" t="s">
-        <v>491</v>
-      </c>
-      <c r="D136" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="E136" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
       <c r="F136" t="s">
-        <v>493</v>
+        <v>459</v>
       </c>
       <c r="G136" t="s">
-        <v>494</v>
+        <v>460</v>
       </c>
       <c r="H136" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="I136" t="s">
-        <v>496</v>
+        <v>465</v>
       </c>
       <c r="J136" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.45">
@@ -8515,31 +8551,31 @@
         <v>1059</v>
       </c>
       <c r="B137" t="s">
-        <v>991</v>
+        <v>533</v>
       </c>
       <c r="C137" t="s">
-        <v>979</v>
+        <v>491</v>
       </c>
       <c r="D137" t="s">
-        <v>959</v>
+        <v>492</v>
       </c>
       <c r="E137" t="s">
-        <v>980</v>
+        <v>490</v>
       </c>
       <c r="F137" t="s">
-        <v>1027</v>
+        <v>493</v>
       </c>
       <c r="G137" t="s">
-        <v>992</v>
+        <v>494</v>
       </c>
       <c r="H137" t="s">
-        <v>992</v>
+        <v>495</v>
       </c>
       <c r="I137" t="s">
-        <v>993</v>
-      </c>
-      <c r="J137" s="1" t="s">
-        <v>981</v>
+        <v>496</v>
+      </c>
+      <c r="J137" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.45">
@@ -8547,34 +8583,48 @@
         <v>1059</v>
       </c>
       <c r="B138" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="C138" t="s">
-        <v>982</v>
+        <v>979</v>
+      </c>
+      <c r="D138" t="s">
+        <v>959</v>
+      </c>
+      <c r="E138" t="s">
+        <v>980</v>
+      </c>
+      <c r="F138" t="s">
+        <v>1027</v>
       </c>
       <c r="G138" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="H138" t="s">
-        <v>995</v>
-      </c>
-      <c r="J138" s="1"/>
+        <v>992</v>
+      </c>
+      <c r="I138" t="s">
+        <v>993</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>1059</v>
       </c>
       <c r="B139" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C139" t="s">
-        <v>996</v>
+        <v>982</v>
       </c>
       <c r="G139" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="H139" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="J139" s="1"/>
     </row>
@@ -8583,16 +8633,16 @@
         <v>1059</v>
       </c>
       <c r="B140" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C140" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="G140" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="H140" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J140" s="1"/>
     </row>
@@ -8601,16 +8651,16 @@
         <v>1059</v>
       </c>
       <c r="B141" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C141" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="G141" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="H141" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="J141" s="1"/>
     </row>
@@ -8619,13 +8669,16 @@
         <v>1059</v>
       </c>
       <c r="B142" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C142" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="G142" t="s">
-        <v>1006</v>
+        <v>1003</v>
+      </c>
+      <c r="H142" t="s">
+        <v>1004</v>
       </c>
       <c r="J142" s="1"/>
     </row>
@@ -8634,16 +8687,13 @@
         <v>1059</v>
       </c>
       <c r="B143" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C143" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G143" t="s">
-        <v>1008</v>
-      </c>
-      <c r="H143" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="J143" s="1"/>
     </row>
@@ -8652,16 +8702,16 @@
         <v>1059</v>
       </c>
       <c r="B144" t="s">
-        <v>1010</v>
+        <v>988</v>
       </c>
       <c r="C144" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="G144" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="H144" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="J144" s="1"/>
     </row>
@@ -8670,16 +8720,16 @@
         <v>1059</v>
       </c>
       <c r="B145" t="s">
-        <v>989</v>
+        <v>1010</v>
       </c>
       <c r="C145" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="G145" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="H145" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="J145" s="1"/>
     </row>
@@ -8688,16 +8738,16 @@
         <v>1059</v>
       </c>
       <c r="B146" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C146" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="G146" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="H146" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="J146" s="1"/>
     </row>
@@ -8706,32 +8756,18 @@
         <v>1059</v>
       </c>
       <c r="B147" t="s">
-        <v>897</v>
+        <v>990</v>
       </c>
       <c r="C147" t="s">
-        <v>260</v>
-      </c>
-      <c r="D147" t="s">
-        <v>261</v>
-      </c>
-      <c r="E147" t="s">
-        <v>259</v>
-      </c>
-      <c r="F147" t="s">
-        <v>262</v>
+        <v>1017</v>
       </c>
       <c r="G147" t="s">
-        <v>263</v>
+        <v>1018</v>
       </c>
       <c r="H147" t="s">
-        <v>264</v>
-      </c>
-      <c r="I147" t="s">
-        <v>265</v>
-      </c>
-      <c r="J147" t="s">
-        <v>266</v>
-      </c>
+        <v>1019</v>
+      </c>
+      <c r="J147" s="1"/>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
@@ -8741,28 +8777,28 @@
         <v>897</v>
       </c>
       <c r="C148" t="s">
-        <v>541</v>
+        <v>260</v>
       </c>
       <c r="D148" t="s">
-        <v>542</v>
+        <v>261</v>
       </c>
       <c r="E148" t="s">
-        <v>543</v>
+        <v>259</v>
       </c>
       <c r="F148" t="s">
-        <v>866</v>
+        <v>262</v>
       </c>
       <c r="G148" t="s">
-        <v>544</v>
+        <v>263</v>
       </c>
       <c r="H148" t="s">
-        <v>545</v>
+        <v>264</v>
       </c>
       <c r="I148" t="s">
-        <v>546</v>
+        <v>265</v>
       </c>
       <c r="J148" t="s">
-        <v>547</v>
+        <v>266</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.45">
@@ -8773,28 +8809,28 @@
         <v>897</v>
       </c>
       <c r="C149" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="D149" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E149" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="F149" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G149" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="H149" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="I149" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="J149" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.45">
@@ -8805,54 +8841,57 @@
         <v>897</v>
       </c>
       <c r="C150" t="s">
-        <v>164</v>
+        <v>549</v>
       </c>
       <c r="D150" t="s">
-        <v>165</v>
+        <v>550</v>
       </c>
       <c r="E150" t="s">
-        <v>163</v>
+        <v>551</v>
       </c>
       <c r="F150" t="s">
-        <v>166</v>
+        <v>867</v>
       </c>
       <c r="G150" t="s">
-        <v>167</v>
+        <v>552</v>
       </c>
       <c r="H150" t="s">
-        <v>168</v>
+        <v>553</v>
+      </c>
+      <c r="I150" t="s">
+        <v>554</v>
       </c>
       <c r="J150" t="s">
-        <v>169</v>
+        <v>555</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="B151" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="C151" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="D151" t="s">
-        <v>858</v>
+        <v>165</v>
       </c>
       <c r="E151" t="s">
-        <v>857</v>
+        <v>163</v>
       </c>
       <c r="F151" t="s">
-        <v>859</v>
+        <v>166</v>
       </c>
       <c r="G151" t="s">
-        <v>860</v>
+        <v>167</v>
       </c>
       <c r="H151" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="J151" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.45">
@@ -8866,25 +8905,22 @@
         <v>115</v>
       </c>
       <c r="D152" t="s">
-        <v>619</v>
+        <v>858</v>
       </c>
       <c r="E152" t="s">
-        <v>620</v>
+        <v>857</v>
       </c>
       <c r="F152" t="s">
-        <v>875</v>
+        <v>859</v>
       </c>
       <c r="G152" t="s">
-        <v>621</v>
+        <v>860</v>
       </c>
       <c r="H152" t="s">
         <v>119</v>
       </c>
-      <c r="I152" t="s">
-        <v>622</v>
-      </c>
       <c r="J152" t="s">
-        <v>623</v>
+        <v>120</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.45">
@@ -8898,16 +8934,25 @@
         <v>115</v>
       </c>
       <c r="D153" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="E153" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="F153" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="G153" t="s">
-        <v>626</v>
+        <v>621</v>
+      </c>
+      <c r="H153" t="s">
+        <v>119</v>
+      </c>
+      <c r="I153" t="s">
+        <v>622</v>
+      </c>
+      <c r="J153" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.45">
@@ -8921,25 +8966,16 @@
         <v>115</v>
       </c>
       <c r="D154" t="s">
-        <v>542</v>
+        <v>624</v>
       </c>
       <c r="E154" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F154" t="s">
         <v>876</v>
       </c>
       <c r="G154" t="s">
         <v>626</v>
-      </c>
-      <c r="H154" t="s">
-        <v>628</v>
-      </c>
-      <c r="I154" t="s">
-        <v>629</v>
-      </c>
-      <c r="J154" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.45">
@@ -8953,10 +8989,10 @@
         <v>115</v>
       </c>
       <c r="D155" t="s">
-        <v>631</v>
+        <v>542</v>
       </c>
       <c r="E155" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="F155" t="s">
         <v>876</v>
@@ -8968,10 +9004,10 @@
         <v>628</v>
       </c>
       <c r="I155" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="J155" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.45">
@@ -8985,25 +9021,25 @@
         <v>115</v>
       </c>
       <c r="D156" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="E156" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="F156" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G156" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="H156" t="s">
-        <v>119</v>
+        <v>628</v>
       </c>
       <c r="I156" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="J156" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.45">
@@ -9017,25 +9053,25 @@
         <v>115</v>
       </c>
       <c r="D157" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="E157" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="F157" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="G157" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H157" t="s">
-        <v>628</v>
+        <v>119</v>
       </c>
       <c r="I157" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="J157" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.45">
@@ -9049,22 +9085,25 @@
         <v>115</v>
       </c>
       <c r="D158" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E158" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="F158" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="G158" t="s">
-        <v>645</v>
+        <v>626</v>
+      </c>
+      <c r="H158" t="s">
+        <v>628</v>
       </c>
       <c r="I158" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="J158" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.45">
@@ -9078,10 +9117,10 @@
         <v>115</v>
       </c>
       <c r="D159" t="s">
-        <v>317</v>
+        <v>643</v>
       </c>
       <c r="E159" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="F159" t="s">
         <v>877</v>
@@ -9090,10 +9129,10 @@
         <v>645</v>
       </c>
       <c r="I159" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="J159" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.45">
@@ -9107,25 +9146,22 @@
         <v>115</v>
       </c>
       <c r="D160" t="s">
-        <v>631</v>
+        <v>317</v>
       </c>
       <c r="E160" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="F160" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="G160" t="s">
-        <v>652</v>
-      </c>
-      <c r="H160" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="I160" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="J160" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.45">
@@ -9133,25 +9169,31 @@
         <v>1055</v>
       </c>
       <c r="B161" t="s">
-        <v>913</v>
+        <v>900</v>
       </c>
       <c r="C161" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="D161" t="s">
-        <v>10</v>
+        <v>631</v>
       </c>
       <c r="E161" t="s">
-        <v>8</v>
+        <v>651</v>
       </c>
       <c r="F161" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
       <c r="G161" t="s">
-        <v>12</v>
+        <v>652</v>
       </c>
       <c r="H161" t="s">
-        <v>13</v>
+        <v>653</v>
+      </c>
+      <c r="I161" t="s">
+        <v>654</v>
+      </c>
+      <c r="J161" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.45">
@@ -9162,28 +9204,22 @@
         <v>913</v>
       </c>
       <c r="C162" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D162" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E162" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F162" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G162" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H162" t="s">
-        <v>19</v>
-      </c>
-      <c r="I162" t="s">
-        <v>20</v>
-      </c>
-      <c r="J162" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.45">
@@ -9197,10 +9233,10 @@
         <v>15</v>
       </c>
       <c r="D163" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E163" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F163" t="s">
         <v>17</v>
@@ -9212,10 +9248,10 @@
         <v>19</v>
       </c>
       <c r="I163" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J163" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.45">
@@ -9229,25 +9265,25 @@
         <v>15</v>
       </c>
       <c r="D164" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E164" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F164" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G164" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H164" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I164" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J164" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.45">
@@ -9261,10 +9297,10 @@
         <v>15</v>
       </c>
       <c r="D165" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E165" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
@@ -9276,10 +9312,10 @@
         <v>30</v>
       </c>
       <c r="I165" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J165" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.45">
@@ -9293,10 +9329,10 @@
         <v>15</v>
       </c>
       <c r="D166" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E166" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -9308,10 +9344,10 @@
         <v>30</v>
       </c>
       <c r="I166" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J166" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.45">
@@ -9322,42 +9358,57 @@
         <v>913</v>
       </c>
       <c r="C167" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="D167" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="E167" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="F167" t="s">
-        <v>117</v>
+        <v>28</v>
       </c>
       <c r="G167" t="s">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="H167" t="s">
-        <v>119</v>
+        <v>30</v>
+      </c>
+      <c r="I167" t="s">
+        <v>39</v>
       </c>
       <c r="J167" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
-        <v>921</v>
+        <v>1055</v>
+      </c>
+      <c r="B168" t="s">
+        <v>913</v>
       </c>
       <c r="C168" t="s">
-        <v>946</v>
+        <v>115</v>
       </c>
       <c r="D168" t="s">
-        <v>922</v>
+        <v>116</v>
       </c>
       <c r="E168" t="s">
-        <v>926</v>
-      </c>
-      <c r="I168" t="s">
-        <v>937</v>
+        <v>114</v>
+      </c>
+      <c r="F168" t="s">
+        <v>117</v>
+      </c>
+      <c r="G168" t="s">
+        <v>118</v>
+      </c>
+      <c r="H168" t="s">
+        <v>119</v>
+      </c>
+      <c r="J168" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.45">
@@ -9368,13 +9419,13 @@
         <v>946</v>
       </c>
       <c r="D169" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E169" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I169" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.45">
@@ -9385,13 +9436,13 @@
         <v>946</v>
       </c>
       <c r="D170" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E170" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I170" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.45">
@@ -9402,13 +9453,13 @@
         <v>946</v>
       </c>
       <c r="D171" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E171" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I171" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.45">
@@ -9419,13 +9470,13 @@
         <v>946</v>
       </c>
       <c r="D172" t="s">
-        <v>935</v>
+        <v>925</v>
       </c>
       <c r="E172" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I172" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.45">
@@ -9439,10 +9490,10 @@
         <v>935</v>
       </c>
       <c r="E173" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="I173" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.45">
@@ -9453,13 +9504,13 @@
         <v>946</v>
       </c>
       <c r="D174" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E174" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I174" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.45">
@@ -9473,10 +9524,10 @@
         <v>936</v>
       </c>
       <c r="E175" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="I175" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.45">
@@ -9490,15 +9541,32 @@
         <v>936</v>
       </c>
       <c r="E176" t="s">
+        <v>933</v>
+      </c>
+      <c r="I176" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A177" t="s">
+        <v>921</v>
+      </c>
+      <c r="C177" t="s">
+        <v>946</v>
+      </c>
+      <c r="D177" t="s">
+        <v>936</v>
+      </c>
+      <c r="E177" t="s">
         <v>934</v>
       </c>
-      <c r="I176" t="s">
+      <c r="I177" t="s">
         <v>945</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A43:J167">
-    <sortCondition ref="A43:A167"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A43:J168">
+    <sortCondition ref="A43:A168"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -9506,7 +9574,7 @@
     <hyperlink ref="J87" r:id="rId2" xr:uid="{04B79727-E872-4B92-B9FF-E52CDD567289}"/>
     <hyperlink ref="J88" r:id="rId3" xr:uid="{58FC3E9B-DA5E-47AE-A0FA-48744DC7E69C}"/>
     <hyperlink ref="J118" r:id="rId4" xr:uid="{0CDDE2B0-9A66-4763-82CA-FB9054DBD36D}"/>
-    <hyperlink ref="J137" r:id="rId5" xr:uid="{D959C86A-275E-4D89-91FD-60DBE69A6EE8}"/>
+    <hyperlink ref="J138" r:id="rId5" xr:uid="{D959C86A-275E-4D89-91FD-60DBE69A6EE8}"/>
     <hyperlink ref="J82" r:id="rId6" xr:uid="{AE797D3F-4BC0-45F7-BAAF-49AAE05332D6}"/>
     <hyperlink ref="J117" r:id="rId7" xr:uid="{E353EA49-C20B-4A50-9E3E-3B8FC192D763}"/>
   </hyperlinks>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kiuchi-my.sharepoint.com/personal/isozaki_kiuchi_co_jp/Documents/fmsf-phone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="799" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95DB5FCE-D6FB-43FE-810B-B4C88B68F019}"/>
+  <xr:revisionPtr revIDLastSave="800" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AD16B07-EC7C-4F0B-B7CD-6FC59A7A3F99}"/>
   <bookViews>
-    <workbookView xWindow="11844" yWindow="348" windowWidth="11544" windowHeight="12360" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
+    <workbookView xWindow="11496" yWindow="0" windowWidth="11544" windowHeight="12360" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
   </bookViews>
   <sheets>
-    <sheet name="電話帳リスト251113" sheetId="1" r:id="rId1"/>
+    <sheet name="data.xlsx" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kiuchi-my.sharepoint.com/personal/isozaki_kiuchi_co_jp/Documents/fmsf-phone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="800" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AD16B07-EC7C-4F0B-B7CD-6FC59A7A3F99}"/>
+  <xr:revisionPtr revIDLastSave="809" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F254132-0282-44F5-BB59-50DA3C5195DC}"/>
   <bookViews>
-    <workbookView xWindow="11496" yWindow="0" windowWidth="11544" windowHeight="12360" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
   </bookViews>
   <sheets>
     <sheet name="data.xlsx" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="1036">
   <si>
     <t>氏名</t>
   </si>
@@ -1890,27 +1889,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部署</t>
-  </si>
-  <si>
-    <t>TEL</t>
-  </si>
-  <si>
-    <t>FAX</t>
-  </si>
-  <si>
-    <t>携帯</t>
-  </si>
-  <si>
-    <t>E-mail</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>備考</t>
-  </si>
-  <si>
     <t>富士機株式會社</t>
   </si>
   <si>
@@ -1932,9 +1910,6 @@
     <t>r-nakamura@fujikizai-g.co.jp</t>
   </si>
   <si>
-    <t>本社 〒102-8373 東京都千代田区一番町12</t>
-  </si>
-  <si>
     <t>富士精工株式会社</t>
   </si>
   <si>
@@ -1956,9 +1931,6 @@
     <t>hirabayashi@fujiseikou.biz</t>
   </si>
   <si>
-    <t>http://www.fujiseikou.biz</t>
-  </si>
-  <si>
     <t>ミノシマ株式会社</t>
   </si>
   <si>
@@ -1980,9 +1952,6 @@
     <t>masuda-t@myisland.co.jp</t>
   </si>
   <si>
-    <t>https://www.myisland.co.jp</t>
-  </si>
-  <si>
     <t>チーフリーダー</t>
   </si>
   <si>
@@ -2268,9 +2237,6 @@
     <t>aonami@rental.co.jp</t>
   </si>
   <si>
-    <t>三菱商事のグループ企業です。</t>
-  </si>
-  <si>
     <t>建築チームリーダー</t>
   </si>
   <si>
@@ -2310,12 +2276,6 @@
     <t>oguri_hiroyuki@nippo-c.jp</t>
   </si>
   <si>
-    <t>www.nippo-c.co.jp</t>
-  </si>
-  <si>
-    <t>ISO 9001, ISO 14001, COHSMS JC 108, 再生紙使用</t>
-  </si>
-  <si>
     <t>営業担当</t>
   </si>
   <si>
@@ -2343,9 +2303,6 @@
     <t>kawai@nippokensetsu.co.jp</t>
   </si>
   <si>
-    <t>ISO 9001, ISO 14001</t>
-  </si>
-  <si>
     <t>箱根植木株式会社</t>
   </si>
   <si>
@@ -2361,9 +2318,6 @@
     <t>ishiwata@hakone-ueki.com</t>
   </si>
   <si>
-    <t>http://www.hakone-ueki.com</t>
-  </si>
-  <si>
     <t>マネージャー</t>
   </si>
   <si>
@@ -2391,9 +2345,6 @@
     <t>kasai@hakone-ueki.com</t>
   </si>
   <si>
-    <t>EXPO 2027 YOKOHAMA JAPAN</t>
-  </si>
-  <si>
     <t>フジリース株式会社</t>
   </si>
   <si>
@@ -2415,9 +2366,6 @@
     <t>oomura_yousuke@daikei-gr.co.jp</t>
   </si>
   <si>
-    <t>https://www.fuji-lease.co.jp/</t>
-  </si>
-  <si>
     <t>ヒダ株式会社</t>
   </si>
   <si>
@@ -2436,12 +2384,6 @@
     <t>kikuchi@hida-group.co.jp</t>
   </si>
   <si>
-    <t>www.hida-group.co.jp</t>
-  </si>
-  <si>
-    <t>創業150周年</t>
-  </si>
-  <si>
     <t>阪和興業株式会社</t>
   </si>
   <si>
@@ -2478,9 +2420,6 @@
     <t>minoru.hirata@jp.fujitec.com</t>
   </si>
   <si>
-    <t>www.fujitec.com</t>
-  </si>
-  <si>
     <t>渡邉拓也</t>
   </si>
   <si>
@@ -2490,9 +2429,6 @@
     <t>takuya.watanabe@jp.fujitec.com</t>
   </si>
   <si>
-    <t>故障連絡先 0570-05-2419</t>
-  </si>
-  <si>
     <t>宮野将綱</t>
   </si>
   <si>
@@ -2505,9 +2441,6 @@
     <t>トヨタ不動産株式会社</t>
   </si>
   <si>
-    <t>名古屋本社 〒450-6216 名古屋市中村区名駅4-7-1 ミッドランドスクエア 16F</t>
-  </si>
-  <si>
     <t>生田目南</t>
   </si>
   <si>
@@ -2520,9 +2453,6 @@
     <t>minami@toyotafudosan.com</t>
   </si>
   <si>
-    <t>東富士事務所 〒412-0042 静岡県御殿場市萩原645-1 大岩ビル2F</t>
-  </si>
-  <si>
     <t>斎藤秀俊</t>
   </si>
   <si>
@@ -2574,9 +2504,6 @@
     <t>eiichi.watanabe@toyotafudosan.com"</t>
   </si>
   <si>
-    <t>東富士事務所 〒412-0042 静岡県御殿場市萩原645-1 大岩ビル 2F</t>
-  </si>
-  <si>
     <t>坂川広行</t>
   </si>
   <si>
@@ -2640,12 +2567,6 @@
     <t>chihiro.sato@toyota-ep.co.jp</t>
   </si>
   <si>
-    <t>http://www.toyota-ep.co.jp/</t>
-  </si>
-  <si>
-    <t>〒410-1308 静岡県駿東郡小山町大御神627 ウェルカムセンター TEL: 0550-75-7151, 2024 健康経営優良法人</t>
-  </si>
-  <si>
     <t>株式会社シェイドレーシング</t>
   </si>
   <si>
@@ -2664,9 +2585,6 @@
     <t>kosuke.ogasawara@shade-racing.com</t>
   </si>
   <si>
-    <t>http://www.shade-racing.com</t>
-  </si>
-  <si>
     <t>日建設計コンストラクション・マネジメント株式会社</t>
   </si>
   <si>
@@ -2691,9 +2609,6 @@
     <t>岩阪聡一郎</t>
   </si>
   <si>
-    <t>OCRエラーによりメールアドレス不明</t>
-  </si>
-  <si>
     <t>シニアアソシエイト 認定コンストラクション・マネジャー 一級建築士</t>
   </si>
   <si>
@@ -2727,9 +2642,6 @@
     <t>takada.kazuko@nikken.jp</t>
   </si>
   <si>
-    <t>https://www.sekistone.com</t>
-  </si>
-  <si>
     <t>勝呂誠也</t>
   </si>
   <si>
@@ -2745,9 +2657,6 @@
     <t>seiya.suguro@taiyokenki.com</t>
   </si>
   <si>
-    <t>http://www.taiyokenki.co.jp/</t>
-  </si>
-  <si>
     <t>株式会社静岡床工事</t>
   </si>
   <si>
@@ -2757,9 +2666,6 @@
     <t>054-259-1952</t>
   </si>
   <si>
-    <t>http://www.shizuyuka.co.jp/</t>
-  </si>
-  <si>
     <t>駿河工業株式会社</t>
   </si>
   <si>
@@ -2779,12 +2685,6 @@
   </si>
   <si>
     <t>matsu@surugakogyo.jp</t>
-  </si>
-  <si>
-    <t>https://www.surugakogyo.co.jp/</t>
-  </si>
-  <si>
-    <t>営業所浜松・名古屋・関西・福岡・鹿児島</t>
   </si>
   <si>
     <t>中村直史</t>
@@ -4200,6 +4100,40 @@
   </si>
   <si>
     <t>054-655-0014</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>施工管理係</t>
+    <rPh sb="0" eb="2">
+      <t>セコウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カカリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山河　友貴</t>
+    <rPh sb="0" eb="2">
+      <t>ヤマカワ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>トモ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>タカシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>090-5190-0316</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>YAMAKAWAYU@sip.sanwa-ss.co.jp</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4271,7 +4205,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4279,6 +4213,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4616,7 +4556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED22340-6398-430F-AD0F-E88DFD8C2F52}">
-  <dimension ref="A1:J177"/>
+  <dimension ref="A1:J178"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.8984375" customWidth="1"/>
@@ -4626,10 +4566,10 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>914</v>
+        <v>881</v>
       </c>
       <c r="B1" t="s">
-        <v>920</v>
+        <v>887</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -4661,25 +4601,25 @@
         <v>499</v>
       </c>
       <c r="C2" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
       <c r="D2" t="s">
-        <v>751</v>
+        <v>728</v>
       </c>
       <c r="E2" t="s">
-        <v>752</v>
+        <v>729</v>
       </c>
       <c r="F2" t="s">
-        <v>888</v>
+        <v>855</v>
       </c>
       <c r="G2" t="s">
-        <v>753</v>
+        <v>730</v>
       </c>
       <c r="H2" t="s">
-        <v>742</v>
+        <v>720</v>
       </c>
       <c r="J2" t="s">
-        <v>754</v>
+        <v>731</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
@@ -4687,25 +4627,25 @@
         <v>499</v>
       </c>
       <c r="C3" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
       <c r="D3" t="s">
         <v>317</v>
       </c>
       <c r="E3" t="s">
-        <v>745</v>
+        <v>722</v>
       </c>
       <c r="F3" t="s">
-        <v>888</v>
+        <v>855</v>
       </c>
       <c r="G3" t="s">
-        <v>746</v>
+        <v>723</v>
       </c>
       <c r="H3" t="s">
-        <v>742</v>
+        <v>720</v>
       </c>
       <c r="J3" t="s">
-        <v>747</v>
+        <v>724</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
@@ -4713,25 +4653,25 @@
         <v>499</v>
       </c>
       <c r="C4" t="s">
+        <v>717</v>
+      </c>
+      <c r="D4" t="s">
+        <v>735</v>
+      </c>
+      <c r="E4" t="s">
+        <v>736</v>
+      </c>
+      <c r="F4" t="s">
+        <v>855</v>
+      </c>
+      <c r="G4" t="s">
+        <v>737</v>
+      </c>
+      <c r="H4" t="s">
+        <v>720</v>
+      </c>
+      <c r="J4" t="s">
         <v>738</v>
-      </c>
-      <c r="D4" t="s">
-        <v>758</v>
-      </c>
-      <c r="E4" t="s">
-        <v>759</v>
-      </c>
-      <c r="F4" t="s">
-        <v>888</v>
-      </c>
-      <c r="G4" t="s">
-        <v>760</v>
-      </c>
-      <c r="H4" t="s">
-        <v>742</v>
-      </c>
-      <c r="J4" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
@@ -4739,25 +4679,25 @@
         <v>499</v>
       </c>
       <c r="C5" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
       <c r="D5" t="s">
-        <v>758</v>
+        <v>735</v>
       </c>
       <c r="E5" t="s">
-        <v>767</v>
+        <v>743</v>
       </c>
       <c r="F5" t="s">
-        <v>888</v>
+        <v>855</v>
       </c>
       <c r="G5" t="s">
-        <v>768</v>
+        <v>744</v>
       </c>
       <c r="H5" t="s">
-        <v>742</v>
+        <v>720</v>
       </c>
       <c r="J5" t="s">
-        <v>769</v>
+        <v>745</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
@@ -4765,25 +4705,25 @@
         <v>499</v>
       </c>
       <c r="C6" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
       <c r="D6" t="s">
-        <v>758</v>
+        <v>735</v>
       </c>
       <c r="E6" t="s">
-        <v>770</v>
+        <v>746</v>
       </c>
       <c r="F6" t="s">
-        <v>888</v>
+        <v>855</v>
       </c>
       <c r="G6" t="s">
-        <v>771</v>
+        <v>747</v>
       </c>
       <c r="H6" t="s">
-        <v>742</v>
+        <v>720</v>
       </c>
       <c r="J6" t="s">
-        <v>772</v>
+        <v>748</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
@@ -4791,25 +4731,25 @@
         <v>499</v>
       </c>
       <c r="C7" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
       <c r="D7" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E7" t="s">
-        <v>763</v>
+        <v>739</v>
       </c>
       <c r="F7" t="s">
-        <v>888</v>
+        <v>855</v>
       </c>
       <c r="G7" t="s">
-        <v>764</v>
+        <v>740</v>
       </c>
       <c r="H7" t="s">
-        <v>765</v>
+        <v>741</v>
       </c>
       <c r="J7" t="s">
-        <v>766</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
@@ -4817,22 +4757,22 @@
         <v>499</v>
       </c>
       <c r="C8" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
       <c r="E8" t="s">
-        <v>748</v>
+        <v>725</v>
       </c>
       <c r="F8" t="s">
-        <v>888</v>
+        <v>855</v>
       </c>
       <c r="G8" t="s">
-        <v>749</v>
+        <v>726</v>
       </c>
       <c r="H8" t="s">
-        <v>742</v>
+        <v>720</v>
       </c>
       <c r="J8" t="s">
-        <v>750</v>
+        <v>727</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
@@ -4840,22 +4780,22 @@
         <v>499</v>
       </c>
       <c r="C9" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
       <c r="E9" t="s">
-        <v>755</v>
+        <v>732</v>
       </c>
       <c r="F9" t="s">
-        <v>888</v>
+        <v>855</v>
       </c>
       <c r="G9" t="s">
-        <v>756</v>
+        <v>733</v>
       </c>
       <c r="H9" t="s">
-        <v>742</v>
+        <v>720</v>
       </c>
       <c r="J9" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
@@ -4863,22 +4803,22 @@
         <v>499</v>
       </c>
       <c r="C10" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
       <c r="E10" t="s">
-        <v>740</v>
+        <v>718</v>
       </c>
       <c r="F10" t="s">
-        <v>888</v>
+        <v>855</v>
       </c>
       <c r="G10" t="s">
-        <v>741</v>
+        <v>719</v>
       </c>
       <c r="H10" t="s">
-        <v>742</v>
+        <v>720</v>
       </c>
       <c r="J10" t="s">
-        <v>743</v>
+        <v>721</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
@@ -4886,16 +4826,16 @@
         <v>499</v>
       </c>
       <c r="C11" t="s">
-        <v>854</v>
+        <v>821</v>
       </c>
       <c r="D11" t="s">
-        <v>855</v>
+        <v>822</v>
       </c>
       <c r="E11" t="s">
-        <v>853</v>
+        <v>820</v>
       </c>
       <c r="F11" t="s">
-        <v>865</v>
+        <v>832</v>
       </c>
       <c r="G11" t="s">
         <v>110</v>
@@ -4912,16 +4852,16 @@
         <v>499</v>
       </c>
       <c r="C12" t="s">
-        <v>854</v>
+        <v>821</v>
       </c>
       <c r="D12" t="s">
-        <v>855</v>
+        <v>822</v>
       </c>
       <c r="E12" t="s">
-        <v>856</v>
+        <v>823</v>
       </c>
       <c r="F12" t="s">
-        <v>865</v>
+        <v>832</v>
       </c>
       <c r="G12" t="s">
         <v>110</v>
@@ -4938,25 +4878,25 @@
         <v>499</v>
       </c>
       <c r="C13" t="s">
-        <v>786</v>
+        <v>760</v>
       </c>
       <c r="E13" t="s">
-        <v>787</v>
+        <v>761</v>
       </c>
       <c r="F13" t="s">
-        <v>891</v>
+        <v>858</v>
       </c>
       <c r="G13" t="s">
-        <v>788</v>
+        <v>762</v>
       </c>
       <c r="H13" t="s">
-        <v>789</v>
+        <v>763</v>
       </c>
       <c r="I13" t="s">
-        <v>790</v>
+        <v>764</v>
       </c>
       <c r="J13" t="s">
-        <v>791</v>
+        <v>765</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
@@ -4964,30 +4904,30 @@
         <v>499</v>
       </c>
       <c r="C14" t="s">
-        <v>778</v>
+        <v>754</v>
       </c>
       <c r="E14" t="s">
-        <v>779</v>
+        <v>755</v>
       </c>
       <c r="F14" t="s">
-        <v>890</v>
+        <v>857</v>
       </c>
       <c r="G14" t="s">
-        <v>780</v>
+        <v>756</v>
       </c>
       <c r="H14" t="s">
-        <v>781</v>
+        <v>757</v>
       </c>
       <c r="I14" t="s">
-        <v>782</v>
+        <v>758</v>
       </c>
       <c r="J14" t="s">
-        <v>783</v>
+        <v>759</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>898</v>
+        <v>865</v>
       </c>
       <c r="C15" t="s">
         <v>99</v>
@@ -5016,7 +4956,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>898</v>
+        <v>865</v>
       </c>
       <c r="C16" t="s">
         <v>99</v>
@@ -5045,141 +4985,141 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>898</v>
+        <v>865</v>
       </c>
       <c r="C17" t="s">
-        <v>793</v>
+        <v>766</v>
       </c>
       <c r="D17" t="s">
-        <v>794</v>
+        <v>767</v>
       </c>
       <c r="E17" t="s">
-        <v>795</v>
+        <v>768</v>
       </c>
       <c r="F17" t="s">
-        <v>892</v>
+        <v>859</v>
       </c>
       <c r="G17" t="s">
-        <v>796</v>
+        <v>769</v>
       </c>
       <c r="H17" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="I17" t="s">
-        <v>798</v>
+        <v>771</v>
       </c>
       <c r="J17" t="s">
-        <v>799</v>
+        <v>772</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>898</v>
+        <v>865</v>
       </c>
       <c r="C18" t="s">
-        <v>793</v>
+        <v>766</v>
       </c>
       <c r="D18" t="s">
-        <v>794</v>
+        <v>767</v>
       </c>
       <c r="E18" t="s">
-        <v>800</v>
+        <v>773</v>
       </c>
       <c r="F18" t="s">
-        <v>892</v>
+        <v>859</v>
       </c>
       <c r="G18" t="s">
-        <v>796</v>
+        <v>769</v>
       </c>
       <c r="H18" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>898</v>
+        <v>865</v>
       </c>
       <c r="C19" t="s">
-        <v>793</v>
+        <v>766</v>
       </c>
       <c r="D19" t="s">
-        <v>802</v>
+        <v>774</v>
       </c>
       <c r="E19" t="s">
-        <v>803</v>
+        <v>775</v>
       </c>
       <c r="F19" t="s">
-        <v>892</v>
+        <v>859</v>
       </c>
       <c r="G19" t="s">
-        <v>796</v>
+        <v>769</v>
       </c>
       <c r="H19" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="I19" t="s">
-        <v>804</v>
+        <v>776</v>
       </c>
       <c r="J19" t="s">
-        <v>805</v>
+        <v>777</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>898</v>
+        <v>865</v>
       </c>
       <c r="C20" t="s">
-        <v>793</v>
+        <v>766</v>
       </c>
       <c r="D20" t="s">
-        <v>794</v>
+        <v>767</v>
       </c>
       <c r="E20" t="s">
-        <v>806</v>
+        <v>778</v>
       </c>
       <c r="F20" t="s">
-        <v>892</v>
+        <v>859</v>
       </c>
       <c r="G20" t="s">
-        <v>796</v>
+        <v>769</v>
       </c>
       <c r="H20" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="I20" t="s">
-        <v>807</v>
+        <v>779</v>
       </c>
       <c r="J20" t="s">
-        <v>808</v>
+        <v>780</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>898</v>
+        <v>865</v>
       </c>
       <c r="C21" t="s">
-        <v>793</v>
+        <v>766</v>
       </c>
       <c r="D21" t="s">
-        <v>809</v>
+        <v>781</v>
       </c>
       <c r="E21" t="s">
-        <v>810</v>
+        <v>782</v>
       </c>
       <c r="F21" t="s">
-        <v>892</v>
+        <v>859</v>
       </c>
       <c r="G21" t="s">
-        <v>796</v>
+        <v>769</v>
       </c>
       <c r="H21" t="s">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="I21" t="s">
-        <v>811</v>
+        <v>783</v>
       </c>
       <c r="J21" t="s">
-        <v>812</v>
+        <v>784</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
@@ -5401,13 +5341,13 @@
         <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>850</v>
+        <v>817</v>
       </c>
       <c r="E30" t="s">
-        <v>849</v>
+        <v>816</v>
       </c>
       <c r="F30" t="s">
-        <v>864</v>
+        <v>831</v>
       </c>
       <c r="I30" t="s">
         <v>79</v>
@@ -5424,13 +5364,13 @@
         <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>848</v>
+        <v>815</v>
       </c>
       <c r="E31" t="s">
-        <v>847</v>
+        <v>814</v>
       </c>
       <c r="F31" t="s">
-        <v>864</v>
+        <v>831</v>
       </c>
       <c r="I31" t="s">
         <v>77</v>
@@ -5450,7 +5390,7 @@
         <v>92</v>
       </c>
       <c r="E32" t="s">
-        <v>851</v>
+        <v>818</v>
       </c>
       <c r="G32" t="s">
         <v>93</v>
@@ -5470,7 +5410,7 @@
         <v>91</v>
       </c>
       <c r="E33" t="s">
-        <v>852</v>
+        <v>819</v>
       </c>
       <c r="G33" t="s">
         <v>96</v>
@@ -5516,19 +5456,19 @@
         <v>61</v>
       </c>
       <c r="D35" t="s">
-        <v>839</v>
+        <v>806</v>
       </c>
       <c r="E35" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="F35" t="s">
-        <v>861</v>
+        <v>828</v>
       </c>
       <c r="G35" t="s">
-        <v>840</v>
+        <v>807</v>
       </c>
       <c r="H35" t="s">
-        <v>841</v>
+        <v>808</v>
       </c>
       <c r="J35" t="s">
         <v>66</v>
@@ -5542,19 +5482,19 @@
         <v>61</v>
       </c>
       <c r="D36" t="s">
-        <v>839</v>
+        <v>806</v>
       </c>
       <c r="E36" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="F36" t="s">
-        <v>862</v>
+        <v>829</v>
       </c>
       <c r="G36" t="s">
-        <v>842</v>
+        <v>809</v>
       </c>
       <c r="H36" t="s">
-        <v>843</v>
+        <v>810</v>
       </c>
       <c r="J36" t="s">
         <v>66</v>
@@ -5597,16 +5537,16 @@
         <v>68</v>
       </c>
       <c r="D38" t="s">
-        <v>845</v>
+        <v>812</v>
       </c>
       <c r="E38" t="s">
-        <v>844</v>
+        <v>811</v>
       </c>
       <c r="F38" t="s">
-        <v>863</v>
+        <v>830</v>
       </c>
       <c r="G38" t="s">
-        <v>846</v>
+        <v>813</v>
       </c>
       <c r="H38" t="s">
         <v>72</v>
@@ -5692,53 +5632,53 @@
         <v>513</v>
       </c>
       <c r="C42" t="s">
-        <v>915</v>
+        <v>882</v>
       </c>
       <c r="D42" t="s">
-        <v>919</v>
+        <v>886</v>
       </c>
       <c r="G42" t="s">
-        <v>916</v>
+        <v>883</v>
       </c>
       <c r="H42" t="s">
-        <v>916</v>
+        <v>883</v>
       </c>
       <c r="I42" t="s">
-        <v>917</v>
+        <v>884</v>
       </c>
       <c r="J42" t="s">
-        <v>918</v>
+        <v>885</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>910</v>
+        <v>877</v>
       </c>
       <c r="B43" t="s">
-        <v>910</v>
+        <v>877</v>
       </c>
       <c r="C43" t="s">
-        <v>773</v>
+        <v>749</v>
       </c>
       <c r="D43" t="s">
-        <v>774</v>
+        <v>750</v>
       </c>
       <c r="E43" t="s">
-        <v>775</v>
+        <v>751</v>
       </c>
       <c r="F43" t="s">
-        <v>889</v>
+        <v>856</v>
       </c>
       <c r="G43" t="s">
-        <v>776</v>
+        <v>752</v>
       </c>
       <c r="H43" t="s">
-        <v>777</v>
+        <v>753</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B44" t="s">
         <v>508</v>
@@ -5770,7 +5710,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B45" t="s">
         <v>517</v>
@@ -5802,7 +5742,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B46" t="s">
         <v>502</v>
@@ -5834,7 +5774,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B47" t="s">
         <v>524</v>
@@ -5866,71 +5806,71 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B48" t="s">
-        <v>901</v>
+        <v>868</v>
       </c>
       <c r="C48" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="D48" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="E48" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="F48" t="s">
-        <v>868</v>
+        <v>835</v>
       </c>
       <c r="G48" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="H48" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="I48" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="J48" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B49" t="s">
-        <v>901</v>
+        <v>868</v>
       </c>
       <c r="C49" t="s">
+        <v>548</v>
+      </c>
+      <c r="D49" t="s">
+        <v>555</v>
+      </c>
+      <c r="E49" t="s">
+        <v>556</v>
+      </c>
+      <c r="F49" t="s">
+        <v>836</v>
+      </c>
+      <c r="G49" t="s">
         <v>557</v>
       </c>
-      <c r="D49" t="s">
-        <v>565</v>
-      </c>
-      <c r="E49" t="s">
-        <v>566</v>
-      </c>
-      <c r="F49" t="s">
-        <v>869</v>
-      </c>
-      <c r="G49" t="s">
-        <v>567</v>
-      </c>
       <c r="H49" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="I49" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="J49" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B50" t="s">
         <v>520</v>
@@ -5959,7 +5899,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B51" t="s">
         <v>520</v>
@@ -5988,7 +5928,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B52" t="s">
         <v>520</v>
@@ -6017,7 +5957,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B53" t="s">
         <v>520</v>
@@ -6049,7 +5989,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B54" t="s">
         <v>520</v>
@@ -6081,7 +6021,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B55" t="s">
         <v>520</v>
@@ -6113,7 +6053,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B56" t="s">
         <v>527</v>
@@ -6145,158 +6085,158 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B57" t="s">
-        <v>906</v>
+        <v>873</v>
       </c>
       <c r="C57" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="D57" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="E57" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="F57" t="s">
-        <v>882</v>
+        <v>849</v>
       </c>
       <c r="G57" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="H57" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="I57" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="J57" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B58" t="s">
-        <v>906</v>
+        <v>873</v>
       </c>
       <c r="C58" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="D58" t="s">
         <v>366</v>
       </c>
       <c r="E58" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="F58" t="s">
-        <v>883</v>
+        <v>850</v>
       </c>
       <c r="G58" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="H58" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="J58" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B59" t="s">
-        <v>906</v>
+        <v>873</v>
       </c>
       <c r="C59" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="D59" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
       <c r="E59" t="s">
-        <v>693</v>
+        <v>678</v>
       </c>
       <c r="F59" t="s">
-        <v>883</v>
+        <v>850</v>
       </c>
       <c r="G59" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="H59" t="s">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="I59" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="J59" t="s">
-        <v>697</v>
+        <v>682</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B60" t="s">
-        <v>906</v>
+        <v>873</v>
       </c>
       <c r="C60" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="E60" t="s">
-        <v>698</v>
+        <v>683</v>
       </c>
       <c r="F60" t="s">
-        <v>883</v>
+        <v>850</v>
       </c>
       <c r="G60" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="H60" t="s">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="I60" t="s">
-        <v>699</v>
+        <v>684</v>
       </c>
       <c r="J60" t="s">
-        <v>700</v>
+        <v>685</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B61" t="s">
-        <v>908</v>
+        <v>875</v>
       </c>
       <c r="C61" t="s">
-        <v>718</v>
+        <v>699</v>
       </c>
       <c r="E61" t="s">
-        <v>719</v>
+        <v>700</v>
       </c>
       <c r="F61" t="s">
-        <v>886</v>
+        <v>853</v>
       </c>
       <c r="G61" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H61" t="s">
-        <v>721</v>
+        <v>702</v>
       </c>
       <c r="I61" t="s">
-        <v>722</v>
+        <v>703</v>
       </c>
       <c r="J61" t="s">
-        <v>723</v>
+        <v>704</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B62" t="s">
         <v>500</v>
@@ -6328,7 +6268,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B63" t="s">
         <v>500</v>
@@ -6360,7 +6300,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B64" t="s">
         <v>500</v>
@@ -6389,39 +6329,39 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B65" t="s">
         <v>500</v>
       </c>
       <c r="C65" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="D65" t="s">
         <v>165</v>
       </c>
       <c r="E65" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="F65" t="s">
-        <v>873</v>
+        <v>840</v>
       </c>
       <c r="G65" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="H65" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="I65" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="J65" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B66" t="s">
         <v>500</v>
@@ -6453,7 +6393,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B67" t="s">
         <v>503</v>
@@ -6485,7 +6425,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B68" t="s">
         <v>503</v>
@@ -6514,7 +6454,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B69" t="s">
         <v>503</v>
@@ -6546,7 +6486,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B70" t="s">
         <v>503</v>
@@ -6575,7 +6515,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B71" t="s">
         <v>503</v>
@@ -6604,7 +6544,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B72" t="s">
         <v>503</v>
@@ -6636,7 +6576,7 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B73" t="s">
         <v>526</v>
@@ -6668,7 +6608,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B74" t="s">
         <v>510</v>
@@ -6700,7 +6640,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B75" t="s">
         <v>532</v>
@@ -6732,132 +6672,132 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B76" t="s">
-        <v>905</v>
+        <v>872</v>
       </c>
       <c r="C76" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="D76" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="E76" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="F76" t="s">
-        <v>880</v>
+        <v>847</v>
       </c>
       <c r="G76" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="H76" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="I76" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="J76" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B77" t="s">
-        <v>902</v>
+        <v>869</v>
       </c>
       <c r="C77" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="D77" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="E77" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="F77" t="s">
-        <v>871</v>
+        <v>838</v>
       </c>
       <c r="G77" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="H77" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="I77" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="J77" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B78" t="s">
-        <v>902</v>
+        <v>869</v>
       </c>
       <c r="C78" t="s">
+        <v>568</v>
+      </c>
+      <c r="D78" t="s">
+        <v>574</v>
+      </c>
+      <c r="E78" t="s">
+        <v>575</v>
+      </c>
+      <c r="F78" t="s">
+        <v>839</v>
+      </c>
+      <c r="G78" t="s">
+        <v>576</v>
+      </c>
+      <c r="H78" t="s">
+        <v>577</v>
+      </c>
+      <c r="J78" t="s">
         <v>578</v>
-      </c>
-      <c r="D78" t="s">
-        <v>584</v>
-      </c>
-      <c r="E78" t="s">
-        <v>585</v>
-      </c>
-      <c r="F78" t="s">
-        <v>872</v>
-      </c>
-      <c r="G78" t="s">
-        <v>586</v>
-      </c>
-      <c r="H78" t="s">
-        <v>587</v>
-      </c>
-      <c r="J78" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B79" t="s">
-        <v>902</v>
+        <v>869</v>
       </c>
       <c r="C79" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="D79" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="E79" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="F79" t="s">
-        <v>872</v>
+        <v>839</v>
       </c>
       <c r="G79" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="H79" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="I79" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="J79" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B80" t="s">
         <v>515</v>
@@ -6889,7 +6829,7 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B81" t="s">
         <v>531</v>
@@ -6921,171 +6861,171 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B82" t="s">
-        <v>947</v>
+        <v>914</v>
       </c>
       <c r="C82" t="s">
-        <v>948</v>
+        <v>915</v>
       </c>
       <c r="D82" t="s">
-        <v>959</v>
+        <v>926</v>
       </c>
       <c r="E82" t="s">
-        <v>1024</v>
+        <v>991</v>
       </c>
       <c r="F82" t="s">
-        <v>1021</v>
+        <v>988</v>
       </c>
       <c r="G82" t="s">
-        <v>1022</v>
+        <v>989</v>
       </c>
       <c r="H82" t="s">
-        <v>1023</v>
+        <v>990</v>
       </c>
       <c r="I82" t="s">
-        <v>1025</v>
+        <v>992</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>1026</v>
+        <v>993</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B83" t="s">
         <v>510</v>
       </c>
       <c r="C83" t="s">
-        <v>949</v>
+        <v>916</v>
       </c>
       <c r="G83" t="s">
-        <v>952</v>
+        <v>919</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B84" t="s">
         <v>510</v>
       </c>
       <c r="C84" t="s">
-        <v>950</v>
+        <v>917</v>
       </c>
       <c r="G84" t="s">
-        <v>953</v>
+        <v>920</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="B85" t="s">
         <v>510</v>
       </c>
       <c r="C85" t="s">
-        <v>951</v>
+        <v>918</v>
       </c>
       <c r="G85" t="s">
-        <v>954</v>
+        <v>921</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>1058</v>
+        <v>1025</v>
       </c>
       <c r="B86" t="s">
-        <v>956</v>
+        <v>923</v>
       </c>
       <c r="C86" t="s">
-        <v>955</v>
+        <v>922</v>
       </c>
       <c r="E86" t="s">
-        <v>1031</v>
+        <v>998</v>
       </c>
       <c r="F86" t="s">
-        <v>1028</v>
+        <v>995</v>
       </c>
       <c r="G86" t="s">
-        <v>1029</v>
+        <v>996</v>
       </c>
       <c r="H86" t="s">
-        <v>1030</v>
+        <v>997</v>
       </c>
       <c r="I86" t="s">
-        <v>1032</v>
+        <v>999</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>1058</v>
+        <v>1025</v>
       </c>
       <c r="B87" t="s">
-        <v>947</v>
+        <v>914</v>
       </c>
       <c r="C87" t="s">
-        <v>958</v>
+        <v>925</v>
       </c>
       <c r="D87" t="s">
-        <v>959</v>
+        <v>926</v>
       </c>
       <c r="E87" t="s">
-        <v>960</v>
+        <v>927</v>
       </c>
       <c r="F87" t="s">
-        <v>961</v>
+        <v>928</v>
       </c>
       <c r="G87" t="s">
-        <v>978</v>
+        <v>945</v>
       </c>
       <c r="H87" t="s">
-        <v>962</v>
+        <v>929</v>
       </c>
       <c r="I87" t="s">
-        <v>963</v>
+        <v>930</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>964</v>
+        <v>931</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>1058</v>
+        <v>1025</v>
       </c>
       <c r="B88" t="s">
-        <v>947</v>
+        <v>914</v>
       </c>
       <c r="C88" t="s">
-        <v>958</v>
+        <v>925</v>
       </c>
       <c r="D88" t="s">
-        <v>967</v>
+        <v>934</v>
       </c>
       <c r="E88" t="s">
-        <v>968</v>
+        <v>935</v>
       </c>
       <c r="F88" t="s">
-        <v>961</v>
+        <v>928</v>
       </c>
       <c r="G88" t="s">
-        <v>978</v>
+        <v>945</v>
       </c>
       <c r="H88" t="s">
-        <v>962</v>
+        <v>929</v>
       </c>
       <c r="I88" t="s">
-        <v>966</v>
+        <v>933</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>965</v>
+        <v>932</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B89" t="s">
         <v>523</v>
@@ -7117,39 +7057,39 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B90" t="s">
         <v>523</v>
       </c>
       <c r="C90" t="s">
-        <v>710</v>
+        <v>693</v>
       </c>
       <c r="D90" t="s">
         <v>317</v>
       </c>
       <c r="E90" t="s">
-        <v>711</v>
+        <v>694</v>
       </c>
       <c r="F90" t="s">
-        <v>885</v>
+        <v>852</v>
       </c>
       <c r="G90" t="s">
-        <v>712</v>
+        <v>695</v>
       </c>
       <c r="H90" t="s">
-        <v>713</v>
+        <v>696</v>
       </c>
       <c r="I90" t="s">
-        <v>714</v>
+        <v>697</v>
       </c>
       <c r="J90" t="s">
-        <v>715</v>
+        <v>698</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B91" t="s">
         <v>511</v>
@@ -7181,7 +7121,7 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B92" t="s">
         <v>511</v>
@@ -7213,7 +7153,7 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B93" t="s">
         <v>507</v>
@@ -7245,7 +7185,7 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B94" t="s">
         <v>507</v>
@@ -7277,25 +7217,25 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B95" t="s">
-        <v>911</v>
+        <v>878</v>
       </c>
       <c r="C95" t="s">
-        <v>820</v>
+        <v>790</v>
       </c>
       <c r="D95" t="s">
         <v>213</v>
       </c>
       <c r="E95" t="s">
-        <v>821</v>
+        <v>791</v>
       </c>
       <c r="F95" t="s">
-        <v>894</v>
+        <v>861</v>
       </c>
       <c r="G95" t="s">
-        <v>822</v>
+        <v>792</v>
       </c>
       <c r="H95" t="s">
         <v>214</v>
@@ -7309,39 +7249,39 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B96" t="s">
-        <v>899</v>
+        <v>866</v>
       </c>
       <c r="C96" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="D96" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="E96" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="F96" t="s">
-        <v>870</v>
+        <v>837</v>
       </c>
       <c r="G96" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="H96" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="I96" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="J96" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B97" t="s">
         <v>519</v>
@@ -7373,7 +7313,7 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B98" t="s">
         <v>505</v>
@@ -7405,7 +7345,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B99" t="s">
         <v>505</v>
@@ -7435,122 +7375,131 @@
         <v>406</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A100" t="s">
-        <v>1057</v>
-      </c>
-      <c r="B100" t="s">
-        <v>909</v>
-      </c>
-      <c r="C100" t="s">
-        <v>724</v>
-      </c>
-      <c r="D100" t="s">
-        <v>542</v>
-      </c>
-      <c r="E100" t="s">
-        <v>725</v>
-      </c>
-      <c r="F100" t="s">
-        <v>887</v>
-      </c>
-      <c r="G100" t="s">
-        <v>726</v>
-      </c>
-      <c r="H100" t="s">
-        <v>727</v>
-      </c>
-      <c r="I100" t="s">
-        <v>728</v>
-      </c>
-      <c r="J100" t="s">
-        <v>729</v>
+    <row r="100" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A100" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>1035</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B101" t="s">
-        <v>909</v>
+        <v>876</v>
       </c>
       <c r="C101" t="s">
-        <v>724</v>
+        <v>705</v>
+      </c>
+      <c r="D101" t="s">
+        <v>535</v>
       </c>
       <c r="E101" t="s">
-        <v>731</v>
+        <v>706</v>
       </c>
       <c r="F101" t="s">
-        <v>887</v>
+        <v>854</v>
       </c>
       <c r="G101" t="s">
-        <v>726</v>
+        <v>707</v>
       </c>
       <c r="H101" t="s">
-        <v>727</v>
+        <v>708</v>
       </c>
       <c r="I101" t="s">
-        <v>732</v>
+        <v>709</v>
       </c>
       <c r="J101" t="s">
-        <v>733</v>
+        <v>710</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B102" t="s">
-        <v>909</v>
+        <v>876</v>
       </c>
       <c r="C102" t="s">
-        <v>724</v>
+        <v>705</v>
       </c>
       <c r="E102" t="s">
-        <v>735</v>
+        <v>711</v>
       </c>
       <c r="F102" t="s">
-        <v>887</v>
+        <v>854</v>
       </c>
       <c r="G102" t="s">
-        <v>726</v>
+        <v>707</v>
       </c>
       <c r="H102" t="s">
-        <v>727</v>
+        <v>708</v>
       </c>
       <c r="I102" t="s">
-        <v>736</v>
+        <v>712</v>
       </c>
       <c r="J102" t="s">
-        <v>737</v>
+        <v>713</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B103" t="s">
-        <v>522</v>
+        <v>876</v>
       </c>
       <c r="C103" t="s">
-        <v>365</v>
-      </c>
-      <c r="D103" t="s">
-        <v>165</v>
+        <v>705</v>
       </c>
       <c r="E103" t="s">
-        <v>361</v>
+        <v>714</v>
+      </c>
+      <c r="F103" t="s">
+        <v>854</v>
+      </c>
+      <c r="G103" t="s">
+        <v>707</v>
+      </c>
+      <c r="H103" t="s">
+        <v>708</v>
       </c>
       <c r="I103" t="s">
-        <v>362</v>
+        <v>715</v>
       </c>
       <c r="J103" t="s">
-        <v>363</v>
+        <v>716</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B104" t="s">
         <v>522</v>
@@ -7559,53 +7508,44 @@
         <v>365</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
       <c r="E104" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I104" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="J104" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B105" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C105" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="D105" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="E105" t="s">
-        <v>346</v>
-      </c>
-      <c r="F105" t="s">
-        <v>349</v>
-      </c>
-      <c r="G105" t="s">
-        <v>350</v>
-      </c>
-      <c r="H105" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="I105" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="J105" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B106" t="s">
         <v>521</v>
@@ -7614,630 +7554,630 @@
         <v>347</v>
       </c>
       <c r="D106" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E106" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="F106" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="G106" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="H106" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="I106" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="J106" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B107" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="C107" t="s">
-        <v>226</v>
+        <v>347</v>
       </c>
       <c r="D107" t="s">
-        <v>227</v>
+        <v>355</v>
       </c>
       <c r="E107" t="s">
-        <v>225</v>
+        <v>354</v>
       </c>
       <c r="F107" t="s">
-        <v>228</v>
+        <v>356</v>
       </c>
       <c r="G107" t="s">
-        <v>229</v>
+        <v>357</v>
       </c>
       <c r="H107" t="s">
-        <v>230</v>
+        <v>358</v>
       </c>
       <c r="I107" t="s">
-        <v>231</v>
+        <v>359</v>
       </c>
       <c r="J107" t="s">
-        <v>232</v>
+        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B108" t="s">
-        <v>912</v>
+        <v>509</v>
       </c>
       <c r="C108" t="s">
-        <v>824</v>
+        <v>226</v>
       </c>
       <c r="D108" t="s">
-        <v>825</v>
+        <v>227</v>
       </c>
       <c r="E108" t="s">
-        <v>826</v>
+        <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>895</v>
+        <v>228</v>
       </c>
       <c r="G108" t="s">
-        <v>827</v>
+        <v>229</v>
       </c>
       <c r="H108" t="s">
-        <v>828</v>
+        <v>230</v>
       </c>
       <c r="I108" t="s">
-        <v>829</v>
+        <v>231</v>
       </c>
       <c r="J108" t="s">
-        <v>830</v>
+        <v>232</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B109" t="s">
-        <v>904</v>
+        <v>879</v>
       </c>
       <c r="C109" t="s">
-        <v>199</v>
+        <v>793</v>
       </c>
       <c r="D109" t="s">
-        <v>665</v>
+        <v>794</v>
       </c>
       <c r="E109" t="s">
-        <v>666</v>
+        <v>795</v>
       </c>
       <c r="F109" t="s">
-        <v>879</v>
+        <v>862</v>
       </c>
       <c r="G109" t="s">
-        <v>202</v>
+        <v>796</v>
       </c>
       <c r="H109" t="s">
-        <v>203</v>
+        <v>797</v>
       </c>
       <c r="I109" t="s">
-        <v>204</v>
+        <v>798</v>
       </c>
       <c r="J109" t="s">
-        <v>205</v>
+        <v>799</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B110" t="s">
-        <v>904</v>
+        <v>871</v>
       </c>
       <c r="C110" t="s">
         <v>199</v>
       </c>
       <c r="D110" t="s">
-        <v>676</v>
+        <v>654</v>
       </c>
       <c r="E110" t="s">
-        <v>677</v>
+        <v>655</v>
       </c>
       <c r="F110" t="s">
-        <v>881</v>
+        <v>846</v>
       </c>
       <c r="G110" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="H110" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="I110" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="J110" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B111" t="s">
-        <v>525</v>
+        <v>871</v>
       </c>
       <c r="C111" t="s">
-        <v>385</v>
+        <v>199</v>
       </c>
       <c r="D111" t="s">
-        <v>386</v>
+        <v>663</v>
       </c>
       <c r="E111" t="s">
-        <v>384</v>
+        <v>664</v>
       </c>
       <c r="F111" t="s">
-        <v>1035</v>
+        <v>848</v>
       </c>
       <c r="G111" t="s">
-        <v>1036</v>
+        <v>209</v>
       </c>
       <c r="H111" t="s">
-        <v>1037</v>
+        <v>210</v>
       </c>
       <c r="I111" t="s">
-        <v>387</v>
+        <v>211</v>
       </c>
       <c r="J111" t="s">
-        <v>388</v>
+        <v>212</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B112" t="s">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="C112" t="s">
-        <v>191</v>
+        <v>385</v>
       </c>
       <c r="D112" t="s">
-        <v>192</v>
+        <v>386</v>
       </c>
       <c r="E112" t="s">
-        <v>190</v>
+        <v>384</v>
       </c>
       <c r="F112" t="s">
-        <v>193</v>
+        <v>1002</v>
       </c>
       <c r="G112" t="s">
-        <v>194</v>
+        <v>1003</v>
       </c>
       <c r="H112" t="s">
-        <v>195</v>
+        <v>1004</v>
       </c>
       <c r="I112" t="s">
-        <v>196</v>
+        <v>387</v>
       </c>
       <c r="J112" t="s">
-        <v>197</v>
+        <v>388</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B113" t="s">
-        <v>528</v>
+        <v>506</v>
       </c>
       <c r="C113" t="s">
-        <v>436</v>
+        <v>191</v>
       </c>
       <c r="D113" t="s">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="E113" t="s">
-        <v>435</v>
+        <v>190</v>
       </c>
       <c r="F113" t="s">
-        <v>437</v>
+        <v>193</v>
       </c>
       <c r="G113" t="s">
-        <v>438</v>
+        <v>194</v>
       </c>
       <c r="H113" t="s">
-        <v>439</v>
+        <v>195</v>
       </c>
       <c r="I113" t="s">
-        <v>440</v>
+        <v>196</v>
       </c>
       <c r="J113" t="s">
-        <v>441</v>
+        <v>197</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B114" t="s">
-        <v>1053</v>
+        <v>528</v>
       </c>
       <c r="C114" t="s">
-        <v>1033</v>
+        <v>436</v>
       </c>
       <c r="D114" t="s">
-        <v>959</v>
+        <v>129</v>
       </c>
       <c r="E114" t="s">
-        <v>1034</v>
+        <v>435</v>
       </c>
       <c r="F114" t="s">
-        <v>1035</v>
+        <v>437</v>
       </c>
       <c r="G114" t="s">
-        <v>1036</v>
+        <v>438</v>
       </c>
       <c r="H114" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J114" s="1"/>
+        <v>439</v>
+      </c>
+      <c r="I114" t="s">
+        <v>440</v>
+      </c>
+      <c r="J114" t="s">
+        <v>441</v>
+      </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B115" t="s">
-        <v>505</v>
+        <v>1020</v>
       </c>
       <c r="C115" t="s">
-        <v>1044</v>
+        <v>1000</v>
+      </c>
+      <c r="D115" t="s">
+        <v>926</v>
+      </c>
+      <c r="E115" t="s">
+        <v>1001</v>
       </c>
       <c r="F115" t="s">
-        <v>1045</v>
+        <v>1002</v>
       </c>
       <c r="G115" t="s">
-        <v>1046</v>
+        <v>1003</v>
       </c>
       <c r="H115" t="s">
-        <v>1047</v>
-      </c>
+        <v>1004</v>
+      </c>
+      <c r="J115" s="1"/>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B116" t="s">
-        <v>1054</v>
+        <v>505</v>
       </c>
       <c r="C116" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D116" t="s">
-        <v>959</v>
-      </c>
-      <c r="E116" t="s">
-        <v>1049</v>
+        <v>1011</v>
       </c>
       <c r="F116" t="s">
-        <v>1050</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>1051</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>1052</v>
+        <v>1012</v>
+      </c>
+      <c r="G116" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H116" t="s">
+        <v>1014</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B117" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C117" t="s">
-        <v>957</v>
+        <v>1015</v>
       </c>
       <c r="D117" t="s">
-        <v>959</v>
+        <v>926</v>
       </c>
       <c r="E117" t="s">
-        <v>1038</v>
+        <v>1016</v>
       </c>
       <c r="F117" t="s">
-        <v>1039</v>
-      </c>
-      <c r="G117" t="s">
-        <v>1040</v>
-      </c>
-      <c r="H117" t="s">
-        <v>1041</v>
-      </c>
-      <c r="I117" t="s">
-        <v>1042</v>
-      </c>
-      <c r="J117" s="1" t="s">
-        <v>1043</v>
+        <v>1017</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>1019</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B118" t="s">
-        <v>969</v>
+        <v>987</v>
       </c>
       <c r="C118" t="s">
-        <v>970</v>
+        <v>924</v>
       </c>
       <c r="D118" t="s">
-        <v>971</v>
+        <v>926</v>
       </c>
       <c r="E118" t="s">
-        <v>972</v>
+        <v>1005</v>
       </c>
       <c r="F118" t="s">
-        <v>973</v>
+        <v>1006</v>
       </c>
       <c r="G118" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
       <c r="H118" t="s">
-        <v>975</v>
+        <v>1008</v>
       </c>
       <c r="I118" t="s">
-        <v>976</v>
+        <v>1009</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>977</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="B119" t="s">
-        <v>1060</v>
+        <v>936</v>
       </c>
       <c r="C119" t="s">
-        <v>1061</v>
+        <v>937</v>
       </c>
       <c r="D119" t="s">
-        <v>959</v>
+        <v>938</v>
       </c>
       <c r="E119" t="s">
-        <v>1062</v>
+        <v>939</v>
       </c>
       <c r="F119" t="s">
-        <v>1063</v>
+        <v>940</v>
       </c>
       <c r="G119" t="s">
-        <v>1064</v>
-      </c>
-      <c r="J119" s="1"/>
+        <v>941</v>
+      </c>
+      <c r="H119" t="s">
+        <v>942</v>
+      </c>
+      <c r="I119" t="s">
+        <v>943</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>944</v>
+      </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>1059</v>
+        <v>1024</v>
       </c>
       <c r="B120" t="s">
-        <v>518</v>
+        <v>1027</v>
       </c>
       <c r="C120" t="s">
-        <v>396</v>
+        <v>1028</v>
       </c>
       <c r="D120" t="s">
-        <v>397</v>
+        <v>926</v>
       </c>
       <c r="E120" t="s">
-        <v>395</v>
+        <v>1029</v>
       </c>
       <c r="F120" t="s">
-        <v>398</v>
+        <v>1030</v>
       </c>
       <c r="G120" t="s">
-        <v>399</v>
-      </c>
-      <c r="H120" t="s">
-        <v>400</v>
-      </c>
-      <c r="I120" t="s">
-        <v>401</v>
-      </c>
-      <c r="J120" t="s">
-        <v>402</v>
-      </c>
+        <v>1031</v>
+      </c>
+      <c r="J120" s="1"/>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B121" t="s">
         <v>518</v>
       </c>
       <c r="C121" t="s">
-        <v>316</v>
+        <v>396</v>
       </c>
       <c r="D121" t="s">
-        <v>317</v>
+        <v>397</v>
       </c>
       <c r="E121" t="s">
-        <v>315</v>
+        <v>395</v>
       </c>
       <c r="F121" t="s">
-        <v>318</v>
+        <v>398</v>
       </c>
       <c r="G121" t="s">
-        <v>319</v>
+        <v>399</v>
       </c>
       <c r="H121" t="s">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="I121" t="s">
-        <v>321</v>
+        <v>401</v>
       </c>
       <c r="J121" t="s">
-        <v>322</v>
+        <v>402</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B122" t="s">
-        <v>907</v>
+        <v>518</v>
       </c>
       <c r="C122" t="s">
-        <v>702</v>
+        <v>316</v>
       </c>
       <c r="D122" t="s">
-        <v>703</v>
+        <v>317</v>
       </c>
       <c r="E122" t="s">
-        <v>704</v>
+        <v>315</v>
       </c>
       <c r="F122" t="s">
-        <v>884</v>
+        <v>318</v>
       </c>
       <c r="G122" t="s">
-        <v>705</v>
+        <v>319</v>
       </c>
       <c r="H122" t="s">
-        <v>706</v>
+        <v>320</v>
       </c>
       <c r="I122" t="s">
-        <v>707</v>
+        <v>321</v>
       </c>
       <c r="J122" t="s">
-        <v>708</v>
+        <v>322</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B123" t="s">
-        <v>516</v>
+        <v>874</v>
       </c>
       <c r="C123" t="s">
-        <v>300</v>
+        <v>686</v>
       </c>
       <c r="D123" t="s">
-        <v>301</v>
+        <v>687</v>
       </c>
       <c r="E123" t="s">
-        <v>299</v>
+        <v>688</v>
       </c>
       <c r="F123" t="s">
-        <v>302</v>
+        <v>851</v>
       </c>
       <c r="G123" t="s">
-        <v>303</v>
+        <v>689</v>
       </c>
       <c r="H123" t="s">
-        <v>304</v>
+        <v>690</v>
       </c>
       <c r="I123" t="s">
-        <v>305</v>
+        <v>691</v>
       </c>
       <c r="J123" t="s">
-        <v>306</v>
+        <v>692</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B124" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C124" t="s">
-        <v>618</v>
+        <v>300</v>
       </c>
       <c r="D124" t="s">
-        <v>656</v>
+        <v>301</v>
       </c>
       <c r="E124" t="s">
-        <v>657</v>
+        <v>299</v>
       </c>
       <c r="F124" t="s">
-        <v>878</v>
+        <v>302</v>
       </c>
       <c r="G124" t="s">
-        <v>658</v>
+        <v>303</v>
+      </c>
+      <c r="H124" t="s">
+        <v>304</v>
+      </c>
+      <c r="I124" t="s">
+        <v>305</v>
       </c>
       <c r="J124" t="s">
-        <v>659</v>
+        <v>306</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B125" t="s">
         <v>514</v>
       </c>
       <c r="C125" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="D125" t="s">
-        <v>661</v>
+        <v>646</v>
       </c>
       <c r="E125" t="s">
-        <v>662</v>
+        <v>647</v>
       </c>
       <c r="F125" t="s">
-        <v>878</v>
+        <v>845</v>
       </c>
       <c r="G125" t="s">
-        <v>658</v>
-      </c>
-      <c r="H125" t="s">
-        <v>663</v>
+        <v>648</v>
       </c>
       <c r="J125" t="s">
-        <v>664</v>
+        <v>649</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B126" t="s">
         <v>514</v>
       </c>
       <c r="C126" t="s">
-        <v>284</v>
+        <v>608</v>
       </c>
       <c r="D126" t="s">
-        <v>285</v>
+        <v>650</v>
       </c>
       <c r="E126" t="s">
-        <v>283</v>
+        <v>651</v>
       </c>
       <c r="F126" t="s">
-        <v>286</v>
+        <v>845</v>
       </c>
       <c r="G126" t="s">
-        <v>287</v>
+        <v>648</v>
       </c>
       <c r="H126" t="s">
-        <v>288</v>
-      </c>
-      <c r="I126" t="s">
-        <v>289</v>
+        <v>652</v>
       </c>
       <c r="J126" t="s">
-        <v>290</v>
+        <v>653</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B127" t="s">
         <v>514</v>
@@ -8245,28 +8185,31 @@
       <c r="C127" t="s">
         <v>284</v>
       </c>
+      <c r="D127" t="s">
+        <v>285</v>
+      </c>
       <c r="E127" t="s">
-        <v>814</v>
+        <v>283</v>
       </c>
       <c r="F127" t="s">
-        <v>893</v>
+        <v>286</v>
       </c>
       <c r="G127" t="s">
-        <v>815</v>
+        <v>287</v>
       </c>
       <c r="H127" t="s">
-        <v>816</v>
+        <v>288</v>
       </c>
       <c r="I127" t="s">
-        <v>817</v>
+        <v>289</v>
       </c>
       <c r="J127" t="s">
-        <v>818</v>
+        <v>290</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B128" t="s">
         <v>514</v>
@@ -8274,252 +8217,249 @@
       <c r="C128" t="s">
         <v>284</v>
       </c>
-      <c r="D128" t="s">
-        <v>572</v>
-      </c>
       <c r="E128" t="s">
-        <v>833</v>
+        <v>785</v>
       </c>
       <c r="F128" t="s">
-        <v>896</v>
+        <v>860</v>
       </c>
       <c r="G128" t="s">
-        <v>834</v>
+        <v>786</v>
       </c>
       <c r="H128" t="s">
-        <v>835</v>
+        <v>787</v>
       </c>
       <c r="I128" t="s">
-        <v>836</v>
+        <v>788</v>
       </c>
       <c r="J128" t="s">
-        <v>837</v>
+        <v>789</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B129" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="C129" t="s">
-        <v>594</v>
+        <v>284</v>
       </c>
       <c r="D129" t="s">
-        <v>595</v>
+        <v>562</v>
+      </c>
+      <c r="E129" t="s">
+        <v>800</v>
       </c>
       <c r="F129" t="s">
-        <v>596</v>
+        <v>863</v>
       </c>
       <c r="G129" t="s">
-        <v>597</v>
+        <v>801</v>
       </c>
       <c r="H129" t="s">
-        <v>598</v>
+        <v>802</v>
       </c>
       <c r="I129" t="s">
-        <v>599</v>
+        <v>803</v>
       </c>
       <c r="J129" t="s">
-        <v>600</v>
+        <v>804</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B130" t="s">
         <v>529</v>
       </c>
       <c r="C130" t="s">
-        <v>443</v>
+        <v>584</v>
       </c>
       <c r="D130" t="s">
-        <v>444</v>
-      </c>
-      <c r="E130" t="s">
-        <v>442</v>
+        <v>585</v>
       </c>
       <c r="F130" t="s">
-        <v>445</v>
+        <v>586</v>
       </c>
       <c r="G130" t="s">
-        <v>446</v>
+        <v>587</v>
       </c>
       <c r="H130" t="s">
-        <v>447</v>
+        <v>588</v>
       </c>
       <c r="I130" t="s">
-        <v>448</v>
+        <v>589</v>
       </c>
       <c r="J130" t="s">
-        <v>449</v>
+        <v>590</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B131" t="s">
-        <v>501</v>
+        <v>529</v>
       </c>
       <c r="C131" t="s">
-        <v>138</v>
+        <v>443</v>
       </c>
       <c r="D131" t="s">
-        <v>139</v>
+        <v>444</v>
       </c>
       <c r="E131" t="s">
-        <v>137</v>
+        <v>442</v>
       </c>
       <c r="F131" t="s">
-        <v>140</v>
+        <v>445</v>
       </c>
       <c r="G131" t="s">
-        <v>141</v>
+        <v>446</v>
       </c>
       <c r="H131" t="s">
-        <v>142</v>
+        <v>447</v>
       </c>
       <c r="I131" t="s">
-        <v>143</v>
+        <v>448</v>
       </c>
       <c r="J131" t="s">
-        <v>144</v>
+        <v>449</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B132" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="C132" t="s">
-        <v>254</v>
+        <v>138</v>
       </c>
       <c r="D132" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="E132" t="s">
-        <v>253</v>
+        <v>137</v>
       </c>
       <c r="F132" t="s">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="G132" t="s">
-        <v>256</v>
+        <v>141</v>
       </c>
       <c r="H132" t="s">
-        <v>256</v>
+        <v>142</v>
       </c>
       <c r="I132" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="J132" t="s">
-        <v>258</v>
+        <v>144</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B133" t="s">
-        <v>903</v>
+        <v>512</v>
       </c>
       <c r="C133" t="s">
-        <v>607</v>
+        <v>254</v>
       </c>
       <c r="D133" t="s">
-        <v>608</v>
+        <v>165</v>
       </c>
       <c r="E133" t="s">
-        <v>609</v>
+        <v>253</v>
       </c>
       <c r="F133" t="s">
-        <v>874</v>
+        <v>255</v>
       </c>
       <c r="G133" t="s">
-        <v>610</v>
+        <v>256</v>
       </c>
       <c r="H133" t="s">
-        <v>611</v>
+        <v>256</v>
       </c>
       <c r="I133" t="s">
-        <v>612</v>
+        <v>257</v>
       </c>
       <c r="J133" t="s">
-        <v>613</v>
+        <v>258</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B134" t="s">
-        <v>903</v>
+        <v>870</v>
       </c>
       <c r="C134" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="D134" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="E134" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="F134" t="s">
-        <v>874</v>
+        <v>841</v>
       </c>
       <c r="G134" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H134" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="I134" t="s">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="J134" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B135" t="s">
-        <v>530</v>
+        <v>870</v>
       </c>
       <c r="C135" t="s">
-        <v>458</v>
+        <v>597</v>
       </c>
       <c r="D135" t="s">
-        <v>165</v>
+        <v>604</v>
       </c>
       <c r="E135" t="s">
-        <v>457</v>
+        <v>605</v>
       </c>
       <c r="F135" t="s">
-        <v>459</v>
+        <v>841</v>
       </c>
       <c r="G135" t="s">
-        <v>460</v>
+        <v>600</v>
       </c>
       <c r="H135" t="s">
-        <v>461</v>
+        <v>601</v>
       </c>
       <c r="I135" t="s">
-        <v>462</v>
+        <v>606</v>
       </c>
       <c r="J135" t="s">
-        <v>463</v>
+        <v>607</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B136" t="s">
         <v>530</v>
@@ -8527,8 +8467,11 @@
       <c r="C136" t="s">
         <v>458</v>
       </c>
+      <c r="D136" t="s">
+        <v>165</v>
+      </c>
       <c r="E136" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="F136" t="s">
         <v>459</v>
@@ -8540,7 +8483,7 @@
         <v>461</v>
       </c>
       <c r="I136" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="J136" t="s">
         <v>463</v>
@@ -8548,727 +8491,724 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B137" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C137" t="s">
-        <v>491</v>
-      </c>
-      <c r="D137" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="E137" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
       <c r="F137" t="s">
-        <v>493</v>
+        <v>459</v>
       </c>
       <c r="G137" t="s">
-        <v>494</v>
+        <v>460</v>
       </c>
       <c r="H137" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="I137" t="s">
-        <v>496</v>
+        <v>465</v>
       </c>
       <c r="J137" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B138" t="s">
-        <v>991</v>
+        <v>533</v>
       </c>
       <c r="C138" t="s">
-        <v>979</v>
+        <v>491</v>
       </c>
       <c r="D138" t="s">
-        <v>959</v>
+        <v>492</v>
       </c>
       <c r="E138" t="s">
-        <v>980</v>
+        <v>490</v>
       </c>
       <c r="F138" t="s">
-        <v>1027</v>
+        <v>493</v>
       </c>
       <c r="G138" t="s">
-        <v>992</v>
+        <v>494</v>
       </c>
       <c r="H138" t="s">
-        <v>992</v>
+        <v>495</v>
       </c>
       <c r="I138" t="s">
-        <v>993</v>
-      </c>
-      <c r="J138" s="1" t="s">
-        <v>981</v>
+        <v>496</v>
+      </c>
+      <c r="J138" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B139" t="s">
-        <v>983</v>
+        <v>958</v>
       </c>
       <c r="C139" t="s">
-        <v>982</v>
+        <v>946</v>
+      </c>
+      <c r="D139" t="s">
+        <v>926</v>
+      </c>
+      <c r="E139" t="s">
+        <v>947</v>
+      </c>
+      <c r="F139" t="s">
+        <v>994</v>
       </c>
       <c r="G139" t="s">
-        <v>994</v>
+        <v>959</v>
       </c>
       <c r="H139" t="s">
-        <v>995</v>
-      </c>
-      <c r="J139" s="1"/>
+        <v>959</v>
+      </c>
+      <c r="I139" t="s">
+        <v>960</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B140" t="s">
-        <v>984</v>
+        <v>950</v>
       </c>
       <c r="C140" t="s">
-        <v>996</v>
+        <v>949</v>
       </c>
       <c r="G140" t="s">
-        <v>997</v>
+        <v>961</v>
       </c>
       <c r="H140" t="s">
-        <v>998</v>
+        <v>962</v>
       </c>
       <c r="J140" s="1"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B141" t="s">
-        <v>985</v>
+        <v>951</v>
       </c>
       <c r="C141" t="s">
-        <v>999</v>
+        <v>963</v>
       </c>
       <c r="G141" t="s">
-        <v>1000</v>
+        <v>964</v>
       </c>
       <c r="H141" t="s">
-        <v>1001</v>
+        <v>965</v>
       </c>
       <c r="J141" s="1"/>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B142" t="s">
-        <v>986</v>
+        <v>952</v>
       </c>
       <c r="C142" t="s">
-        <v>1002</v>
+        <v>966</v>
       </c>
       <c r="G142" t="s">
-        <v>1003</v>
+        <v>967</v>
       </c>
       <c r="H142" t="s">
-        <v>1004</v>
+        <v>968</v>
       </c>
       <c r="J142" s="1"/>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B143" t="s">
-        <v>987</v>
+        <v>953</v>
       </c>
       <c r="C143" t="s">
-        <v>1005</v>
+        <v>969</v>
       </c>
       <c r="G143" t="s">
-        <v>1006</v>
+        <v>970</v>
+      </c>
+      <c r="H143" t="s">
+        <v>971</v>
       </c>
       <c r="J143" s="1"/>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B144" t="s">
-        <v>988</v>
+        <v>954</v>
       </c>
       <c r="C144" t="s">
-        <v>1007</v>
+        <v>972</v>
       </c>
       <c r="G144" t="s">
-        <v>1008</v>
-      </c>
-      <c r="H144" t="s">
-        <v>1009</v>
+        <v>973</v>
       </c>
       <c r="J144" s="1"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B145" t="s">
-        <v>1010</v>
+        <v>955</v>
       </c>
       <c r="C145" t="s">
-        <v>1011</v>
+        <v>974</v>
       </c>
       <c r="G145" t="s">
-        <v>1012</v>
+        <v>975</v>
       </c>
       <c r="H145" t="s">
-        <v>1013</v>
+        <v>976</v>
       </c>
       <c r="J145" s="1"/>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B146" t="s">
-        <v>989</v>
+        <v>977</v>
       </c>
       <c r="C146" t="s">
-        <v>1014</v>
+        <v>978</v>
       </c>
       <c r="G146" t="s">
-        <v>1015</v>
+        <v>979</v>
       </c>
       <c r="H146" t="s">
-        <v>1016</v>
+        <v>980</v>
       </c>
       <c r="J146" s="1"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B147" t="s">
-        <v>990</v>
+        <v>956</v>
       </c>
       <c r="C147" t="s">
-        <v>1017</v>
+        <v>981</v>
       </c>
       <c r="G147" t="s">
-        <v>1018</v>
+        <v>982</v>
       </c>
       <c r="H147" t="s">
-        <v>1019</v>
+        <v>983</v>
       </c>
       <c r="J147" s="1"/>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B148" t="s">
-        <v>897</v>
+        <v>957</v>
       </c>
       <c r="C148" t="s">
-        <v>260</v>
-      </c>
-      <c r="D148" t="s">
-        <v>261</v>
-      </c>
-      <c r="E148" t="s">
-        <v>259</v>
-      </c>
-      <c r="F148" t="s">
-        <v>262</v>
+        <v>984</v>
       </c>
       <c r="G148" t="s">
-        <v>263</v>
+        <v>985</v>
       </c>
       <c r="H148" t="s">
-        <v>264</v>
-      </c>
-      <c r="I148" t="s">
-        <v>265</v>
-      </c>
-      <c r="J148" t="s">
-        <v>266</v>
-      </c>
+        <v>986</v>
+      </c>
+      <c r="J148" s="1"/>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B149" t="s">
-        <v>897</v>
+        <v>864</v>
       </c>
       <c r="C149" t="s">
-        <v>541</v>
+        <v>260</v>
       </c>
       <c r="D149" t="s">
-        <v>542</v>
+        <v>261</v>
       </c>
       <c r="E149" t="s">
-        <v>543</v>
+        <v>259</v>
       </c>
       <c r="F149" t="s">
-        <v>866</v>
+        <v>262</v>
       </c>
       <c r="G149" t="s">
-        <v>544</v>
+        <v>263</v>
       </c>
       <c r="H149" t="s">
-        <v>545</v>
+        <v>264</v>
       </c>
       <c r="I149" t="s">
-        <v>546</v>
+        <v>265</v>
       </c>
       <c r="J149" t="s">
-        <v>547</v>
+        <v>266</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B150" t="s">
-        <v>897</v>
+        <v>864</v>
       </c>
       <c r="C150" t="s">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="D150" t="s">
-        <v>550</v>
+        <v>535</v>
       </c>
       <c r="E150" t="s">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="F150" t="s">
-        <v>867</v>
+        <v>833</v>
       </c>
       <c r="G150" t="s">
-        <v>552</v>
+        <v>537</v>
       </c>
       <c r="H150" t="s">
-        <v>553</v>
+        <v>538</v>
       </c>
       <c r="I150" t="s">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="J150" t="s">
-        <v>555</v>
+        <v>540</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="B151" t="s">
-        <v>897</v>
+        <v>864</v>
       </c>
       <c r="C151" t="s">
-        <v>164</v>
+        <v>541</v>
       </c>
       <c r="D151" t="s">
-        <v>165</v>
+        <v>542</v>
       </c>
       <c r="E151" t="s">
-        <v>163</v>
+        <v>543</v>
       </c>
       <c r="F151" t="s">
-        <v>166</v>
+        <v>834</v>
       </c>
       <c r="G151" t="s">
-        <v>167</v>
+        <v>544</v>
       </c>
       <c r="H151" t="s">
-        <v>168</v>
+        <v>545</v>
+      </c>
+      <c r="I151" t="s">
+        <v>546</v>
       </c>
       <c r="J151" t="s">
-        <v>169</v>
+        <v>547</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
-        <v>1055</v>
+        <v>1026</v>
       </c>
       <c r="B152" t="s">
-        <v>900</v>
+        <v>864</v>
       </c>
       <c r="C152" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="D152" t="s">
-        <v>858</v>
+        <v>165</v>
       </c>
       <c r="E152" t="s">
-        <v>857</v>
+        <v>163</v>
       </c>
       <c r="F152" t="s">
-        <v>859</v>
+        <v>166</v>
       </c>
       <c r="G152" t="s">
-        <v>860</v>
+        <v>167</v>
       </c>
       <c r="H152" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="J152" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B153" t="s">
-        <v>900</v>
+        <v>867</v>
       </c>
       <c r="C153" t="s">
         <v>115</v>
       </c>
       <c r="D153" t="s">
-        <v>619</v>
+        <v>825</v>
       </c>
       <c r="E153" t="s">
-        <v>620</v>
+        <v>824</v>
       </c>
       <c r="F153" t="s">
-        <v>875</v>
+        <v>826</v>
       </c>
       <c r="G153" t="s">
-        <v>621</v>
+        <v>827</v>
       </c>
       <c r="H153" t="s">
         <v>119</v>
       </c>
-      <c r="I153" t="s">
-        <v>622</v>
-      </c>
       <c r="J153" t="s">
-        <v>623</v>
+        <v>120</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B154" t="s">
-        <v>900</v>
+        <v>867</v>
       </c>
       <c r="C154" t="s">
         <v>115</v>
       </c>
       <c r="D154" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="E154" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="F154" t="s">
-        <v>876</v>
+        <v>842</v>
       </c>
       <c r="G154" t="s">
-        <v>626</v>
+        <v>611</v>
+      </c>
+      <c r="H154" t="s">
+        <v>119</v>
+      </c>
+      <c r="I154" t="s">
+        <v>612</v>
+      </c>
+      <c r="J154" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B155" t="s">
-        <v>900</v>
+        <v>867</v>
       </c>
       <c r="C155" t="s">
         <v>115</v>
       </c>
       <c r="D155" t="s">
-        <v>542</v>
+        <v>614</v>
       </c>
       <c r="E155" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="F155" t="s">
-        <v>876</v>
+        <v>843</v>
       </c>
       <c r="G155" t="s">
-        <v>626</v>
-      </c>
-      <c r="H155" t="s">
-        <v>628</v>
-      </c>
-      <c r="I155" t="s">
-        <v>629</v>
-      </c>
-      <c r="J155" t="s">
-        <v>630</v>
+        <v>616</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B156" t="s">
-        <v>900</v>
+        <v>867</v>
       </c>
       <c r="C156" t="s">
         <v>115</v>
       </c>
       <c r="D156" t="s">
-        <v>631</v>
+        <v>535</v>
       </c>
       <c r="E156" t="s">
-        <v>632</v>
+        <v>617</v>
       </c>
       <c r="F156" t="s">
-        <v>876</v>
+        <v>843</v>
       </c>
       <c r="G156" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="H156" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="I156" t="s">
-        <v>633</v>
+        <v>619</v>
       </c>
       <c r="J156" t="s">
-        <v>634</v>
+        <v>620</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B157" t="s">
-        <v>900</v>
+        <v>867</v>
       </c>
       <c r="C157" t="s">
         <v>115</v>
       </c>
       <c r="D157" t="s">
-        <v>635</v>
+        <v>621</v>
       </c>
       <c r="E157" t="s">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="F157" t="s">
-        <v>875</v>
+        <v>843</v>
       </c>
       <c r="G157" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="H157" t="s">
-        <v>119</v>
+        <v>618</v>
       </c>
       <c r="I157" t="s">
-        <v>637</v>
+        <v>623</v>
       </c>
       <c r="J157" t="s">
-        <v>638</v>
+        <v>624</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B158" t="s">
-        <v>900</v>
+        <v>867</v>
       </c>
       <c r="C158" t="s">
         <v>115</v>
       </c>
       <c r="D158" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
       <c r="E158" t="s">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="F158" t="s">
-        <v>876</v>
+        <v>842</v>
       </c>
       <c r="G158" t="s">
-        <v>626</v>
+        <v>611</v>
       </c>
       <c r="H158" t="s">
+        <v>119</v>
+      </c>
+      <c r="I158" t="s">
+        <v>627</v>
+      </c>
+      <c r="J158" t="s">
         <v>628</v>
-      </c>
-      <c r="I158" t="s">
-        <v>641</v>
-      </c>
-      <c r="J158" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B159" t="s">
-        <v>900</v>
+        <v>867</v>
       </c>
       <c r="C159" t="s">
         <v>115</v>
       </c>
       <c r="D159" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="E159" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="F159" t="s">
-        <v>877</v>
+        <v>843</v>
       </c>
       <c r="G159" t="s">
-        <v>645</v>
+        <v>616</v>
+      </c>
+      <c r="H159" t="s">
+        <v>618</v>
       </c>
       <c r="I159" t="s">
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="J159" t="s">
-        <v>647</v>
+        <v>632</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B160" t="s">
-        <v>900</v>
+        <v>867</v>
       </c>
       <c r="C160" t="s">
         <v>115</v>
       </c>
       <c r="D160" t="s">
-        <v>317</v>
+        <v>633</v>
       </c>
       <c r="E160" t="s">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="F160" t="s">
-        <v>877</v>
+        <v>844</v>
       </c>
       <c r="G160" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="I160" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="J160" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B161" t="s">
-        <v>900</v>
+        <v>867</v>
       </c>
       <c r="C161" t="s">
         <v>115</v>
       </c>
       <c r="D161" t="s">
-        <v>631</v>
+        <v>317</v>
       </c>
       <c r="E161" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="F161" t="s">
-        <v>875</v>
+        <v>844</v>
       </c>
       <c r="G161" t="s">
-        <v>652</v>
-      </c>
-      <c r="H161" t="s">
-        <v>653</v>
+        <v>635</v>
       </c>
       <c r="I161" t="s">
-        <v>654</v>
+        <v>639</v>
       </c>
       <c r="J161" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B162" t="s">
-        <v>913</v>
+        <v>867</v>
       </c>
       <c r="C162" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="D162" t="s">
-        <v>10</v>
+        <v>621</v>
       </c>
       <c r="E162" t="s">
-        <v>8</v>
+        <v>641</v>
       </c>
       <c r="F162" t="s">
-        <v>11</v>
+        <v>842</v>
       </c>
       <c r="G162" t="s">
-        <v>12</v>
+        <v>642</v>
       </c>
       <c r="H162" t="s">
-        <v>13</v>
+        <v>643</v>
+      </c>
+      <c r="I162" t="s">
+        <v>644</v>
+      </c>
+      <c r="J162" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B163" t="s">
-        <v>913</v>
+        <v>880</v>
       </c>
       <c r="C163" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D163" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E163" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F163" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G163" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H163" t="s">
-        <v>19</v>
-      </c>
-      <c r="I163" t="s">
-        <v>20</v>
-      </c>
-      <c r="J163" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B164" t="s">
-        <v>913</v>
+        <v>880</v>
       </c>
       <c r="C164" t="s">
         <v>15</v>
       </c>
       <c r="D164" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E164" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F164" t="s">
         <v>17</v>
@@ -9280,59 +9220,59 @@
         <v>19</v>
       </c>
       <c r="I164" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J164" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B165" t="s">
-        <v>913</v>
+        <v>880</v>
       </c>
       <c r="C165" t="s">
         <v>15</v>
       </c>
       <c r="D165" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E165" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F165" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G165" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H165" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I165" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J165" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B166" t="s">
-        <v>913</v>
+        <v>880</v>
       </c>
       <c r="C166" t="s">
         <v>15</v>
       </c>
       <c r="D166" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E166" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -9344,27 +9284,27 @@
         <v>30</v>
       </c>
       <c r="I166" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J166" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B167" t="s">
-        <v>913</v>
+        <v>880</v>
       </c>
       <c r="C167" t="s">
         <v>15</v>
       </c>
       <c r="D167" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E167" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F167" t="s">
         <v>28</v>
@@ -9376,440 +9316,241 @@
         <v>30</v>
       </c>
       <c r="I167" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J167" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="B168" t="s">
-        <v>913</v>
+        <v>880</v>
       </c>
       <c r="C168" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="D168" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="E168" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="F168" t="s">
-        <v>117</v>
+        <v>28</v>
       </c>
       <c r="G168" t="s">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="H168" t="s">
-        <v>119</v>
+        <v>30</v>
+      </c>
+      <c r="I168" t="s">
+        <v>39</v>
       </c>
       <c r="J168" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>921</v>
+        <v>1022</v>
+      </c>
+      <c r="B169" t="s">
+        <v>880</v>
       </c>
       <c r="C169" t="s">
-        <v>946</v>
+        <v>115</v>
       </c>
       <c r="D169" t="s">
-        <v>922</v>
+        <v>116</v>
       </c>
       <c r="E169" t="s">
-        <v>926</v>
-      </c>
-      <c r="I169" t="s">
-        <v>937</v>
+        <v>114</v>
+      </c>
+      <c r="F169" t="s">
+        <v>117</v>
+      </c>
+      <c r="G169" t="s">
+        <v>118</v>
+      </c>
+      <c r="H169" t="s">
+        <v>119</v>
+      </c>
+      <c r="J169" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
-        <v>921</v>
+        <v>888</v>
       </c>
       <c r="C170" t="s">
-        <v>946</v>
+        <v>913</v>
       </c>
       <c r="D170" t="s">
-        <v>923</v>
+        <v>889</v>
       </c>
       <c r="E170" t="s">
-        <v>927</v>
+        <v>893</v>
       </c>
       <c r="I170" t="s">
-        <v>938</v>
+        <v>904</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
-        <v>921</v>
+        <v>888</v>
       </c>
       <c r="C171" t="s">
-        <v>946</v>
+        <v>913</v>
       </c>
       <c r="D171" t="s">
-        <v>924</v>
+        <v>890</v>
       </c>
       <c r="E171" t="s">
-        <v>928</v>
+        <v>894</v>
       </c>
       <c r="I171" t="s">
-        <v>939</v>
+        <v>905</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>921</v>
+        <v>888</v>
       </c>
       <c r="C172" t="s">
-        <v>946</v>
+        <v>913</v>
       </c>
       <c r="D172" t="s">
-        <v>925</v>
+        <v>891</v>
       </c>
       <c r="E172" t="s">
-        <v>929</v>
+        <v>895</v>
       </c>
       <c r="I172" t="s">
-        <v>940</v>
+        <v>906</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
-        <v>921</v>
+        <v>888</v>
       </c>
       <c r="C173" t="s">
-        <v>946</v>
+        <v>913</v>
       </c>
       <c r="D173" t="s">
-        <v>935</v>
+        <v>892</v>
       </c>
       <c r="E173" t="s">
-        <v>930</v>
+        <v>896</v>
       </c>
       <c r="I173" t="s">
-        <v>941</v>
+        <v>907</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
-        <v>921</v>
+        <v>888</v>
       </c>
       <c r="C174" t="s">
-        <v>946</v>
+        <v>913</v>
       </c>
       <c r="D174" t="s">
-        <v>935</v>
+        <v>902</v>
       </c>
       <c r="E174" t="s">
-        <v>931</v>
+        <v>897</v>
       </c>
       <c r="I174" t="s">
-        <v>942</v>
+        <v>908</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
-        <v>921</v>
+        <v>888</v>
       </c>
       <c r="C175" t="s">
-        <v>946</v>
+        <v>913</v>
       </c>
       <c r="D175" t="s">
-        <v>936</v>
+        <v>902</v>
       </c>
       <c r="E175" t="s">
-        <v>932</v>
+        <v>898</v>
       </c>
       <c r="I175" t="s">
-        <v>943</v>
+        <v>909</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
-        <v>921</v>
+        <v>888</v>
       </c>
       <c r="C176" t="s">
-        <v>946</v>
+        <v>913</v>
       </c>
       <c r="D176" t="s">
-        <v>936</v>
+        <v>903</v>
       </c>
       <c r="E176" t="s">
-        <v>933</v>
+        <v>899</v>
       </c>
       <c r="I176" t="s">
-        <v>944</v>
+        <v>910</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>921</v>
+        <v>888</v>
       </c>
       <c r="C177" t="s">
-        <v>946</v>
+        <v>913</v>
       </c>
       <c r="D177" t="s">
-        <v>936</v>
+        <v>903</v>
       </c>
       <c r="E177" t="s">
-        <v>934</v>
+        <v>900</v>
       </c>
       <c r="I177" t="s">
-        <v>945</v>
+        <v>911</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A178" t="s">
+        <v>888</v>
+      </c>
+      <c r="C178" t="s">
+        <v>913</v>
+      </c>
+      <c r="D178" t="s">
+        <v>903</v>
+      </c>
+      <c r="E178" t="s">
+        <v>901</v>
+      </c>
+      <c r="I178" t="s">
+        <v>912</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A43:J168">
-    <sortCondition ref="A43:A168"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A43:J169">
+    <sortCondition ref="A43:A169"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="J42" r:id="rId1" xr:uid="{8A5F4D1B-75DE-4D67-8A11-0F1BAE0155F6}"/>
     <hyperlink ref="J87" r:id="rId2" xr:uid="{04B79727-E872-4B92-B9FF-E52CDD567289}"/>
     <hyperlink ref="J88" r:id="rId3" xr:uid="{58FC3E9B-DA5E-47AE-A0FA-48744DC7E69C}"/>
-    <hyperlink ref="J118" r:id="rId4" xr:uid="{0CDDE2B0-9A66-4763-82CA-FB9054DBD36D}"/>
-    <hyperlink ref="J138" r:id="rId5" xr:uid="{D959C86A-275E-4D89-91FD-60DBE69A6EE8}"/>
+    <hyperlink ref="J119" r:id="rId4" xr:uid="{0CDDE2B0-9A66-4763-82CA-FB9054DBD36D}"/>
+    <hyperlink ref="J139" r:id="rId5" xr:uid="{D959C86A-275E-4D89-91FD-60DBE69A6EE8}"/>
     <hyperlink ref="J82" r:id="rId6" xr:uid="{AE797D3F-4BC0-45F7-BAAF-49AAE05332D6}"/>
-    <hyperlink ref="J117" r:id="rId7" xr:uid="{E353EA49-C20B-4A50-9E3E-3B8FC192D763}"/>
+    <hyperlink ref="J118" r:id="rId7" xr:uid="{E353EA49-C20B-4A50-9E3E-3B8FC192D763}"/>
+    <hyperlink ref="J100" r:id="rId8" xr:uid="{A98CDD58-6463-49F3-9952-BC0BEE6FEAA2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{286C0F70-C109-48E0-BABC-1B82B703E990}">
-  <dimension ref="A1:K101"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="5" max="5" width="11.3984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>535</v>
-      </c>
-      <c r="G1" t="s">
-        <v>536</v>
-      </c>
-      <c r="H1" t="s">
-        <v>537</v>
-      </c>
-      <c r="I1" t="s">
-        <v>538</v>
-      </c>
-      <c r="J1" t="s">
-        <v>539</v>
-      </c>
-      <c r="K1" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="38" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="K38" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="39" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J39" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="40" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J40" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="41" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J41" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="63" spans="11:11" x14ac:dyDescent="0.45">
-      <c r="K63" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="66" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J66" t="s">
-        <v>674</v>
-      </c>
-      <c r="K66" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="68" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="K68" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="69" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J69" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="71" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J71" t="s">
-        <v>691</v>
-      </c>
-      <c r="K71" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="72" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J72" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="73" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J73" t="s">
-        <v>716</v>
-      </c>
-      <c r="K73" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="75" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J75" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="76" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J76" t="s">
-        <v>730</v>
-      </c>
-      <c r="K76" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="77" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J77" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="78" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="K78" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="79" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="K79" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="80" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="K80" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="81" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="K81" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="82" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="K82" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="83" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="K83" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="84" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="K84" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="85" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="K85" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="86" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="K86" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="87" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="K87" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="89" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J89" t="s">
-        <v>784</v>
-      </c>
-      <c r="K89" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="90" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J90" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="92" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J92" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="96" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J96" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="97" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J97" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="98" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J98" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="99" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J99" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="100" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J100" t="s">
-        <v>831</v>
-      </c>
-      <c r="K100" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="101" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="J101" t="s">
-        <v>819</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kiuchi-my.sharepoint.com/personal/isozaki_kiuchi_co_jp/Documents/fmsf-phone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="809" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F254132-0282-44F5-BB59-50DA3C5195DC}"/>
+  <xr:revisionPtr revIDLastSave="821" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEE41166-3AD9-4CD8-B784-4EB617F49FA9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
   </bookViews>
   <sheets>
     <sheet name="data.xlsx" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="1036">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="1043">
   <si>
     <t>氏名</t>
   </si>
@@ -4134,6 +4134,49 @@
   </si>
   <si>
     <t>YAMAKAWAYU@sip.sanwa-ss.co.jp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイル工事</t>
+    <rPh sb="3" eb="5">
+      <t>コウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>㈱静興タイル商会</t>
+    <rPh sb="1" eb="2">
+      <t>シズ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショウカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>畦地</t>
+    <rPh sb="0" eb="2">
+      <t>アゼチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〒422-8045静岡県静岡市駿河区西島１３６－２</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>054-238-2381</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>054-238-2382</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>azechi-seikou@ny.tokai.or.jp</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4141,7 +4184,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4179,6 +4222,14 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4215,10 +4266,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4237,6 +4288,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4556,15 +4611,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED22340-6398-430F-AD0F-E88DFD8C2F52}">
-  <dimension ref="A1:J178"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:J179"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="8.8984375" customWidth="1"/>
+    <col min="1" max="2" width="8.9140625" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="5" max="5" width="15.09765625" customWidth="1"/>
+    <col min="5" max="5" width="15.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>881</v>
       </c>
@@ -4596,7 +4651,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>499</v>
       </c>
@@ -4622,7 +4677,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>499</v>
       </c>
@@ -4648,7 +4703,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>499</v>
       </c>
@@ -4674,7 +4729,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>499</v>
       </c>
@@ -4700,7 +4755,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>499</v>
       </c>
@@ -4726,7 +4781,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>499</v>
       </c>
@@ -4752,7 +4807,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>499</v>
       </c>
@@ -4775,7 +4830,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>499</v>
       </c>
@@ -4798,7 +4853,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>499</v>
       </c>
@@ -4821,7 +4876,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>499</v>
       </c>
@@ -4847,7 +4902,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>499</v>
       </c>
@@ -4873,7 +4928,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>499</v>
       </c>
@@ -4899,7 +4954,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>499</v>
       </c>
@@ -4925,7 +4980,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>865</v>
       </c>
@@ -4954,7 +5009,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>865</v>
       </c>
@@ -4983,7 +5038,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>865</v>
       </c>
@@ -5012,7 +5067,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>865</v>
       </c>
@@ -5035,7 +5090,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>865</v>
       </c>
@@ -5064,7 +5119,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>865</v>
       </c>
@@ -5093,7 +5148,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>865</v>
       </c>
@@ -5122,7 +5177,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>498</v>
       </c>
@@ -5151,7 +5206,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>498</v>
       </c>
@@ -5180,7 +5235,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>498</v>
       </c>
@@ -5206,7 +5261,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>498</v>
       </c>
@@ -5235,7 +5290,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>498</v>
       </c>
@@ -5261,7 +5316,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>498</v>
       </c>
@@ -5287,7 +5342,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>498</v>
       </c>
@@ -5310,7 +5365,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>498</v>
       </c>
@@ -5333,7 +5388,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>498</v>
       </c>
@@ -5356,7 +5411,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>498</v>
       </c>
@@ -5379,7 +5434,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>498</v>
       </c>
@@ -5402,7 +5457,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>498</v>
       </c>
@@ -5422,7 +5477,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>498</v>
       </c>
@@ -5448,7 +5503,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>498</v>
       </c>
@@ -5474,7 +5529,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>498</v>
       </c>
@@ -5500,7 +5555,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>498</v>
       </c>
@@ -5529,7 +5584,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>498</v>
       </c>
@@ -5558,7 +5613,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>513</v>
       </c>
@@ -5587,7 +5642,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>513</v>
       </c>
@@ -5610,7 +5665,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>513</v>
       </c>
@@ -5627,7 +5682,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>513</v>
       </c>
@@ -5650,7 +5705,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>877</v>
       </c>
@@ -5676,7 +5731,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>1023</v>
       </c>
@@ -5708,7 +5763,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>1023</v>
       </c>
@@ -5740,7 +5795,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>1023</v>
       </c>
@@ -5772,7 +5827,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>1023</v>
       </c>
@@ -5804,7 +5859,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>1023</v>
       </c>
@@ -5836,7 +5891,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>1023</v>
       </c>
@@ -5868,7 +5923,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>1023</v>
       </c>
@@ -5897,7 +5952,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>1023</v>
       </c>
@@ -5926,7 +5981,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>1023</v>
       </c>
@@ -5955,7 +6010,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>1023</v>
       </c>
@@ -5987,7 +6042,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>1023</v>
       </c>
@@ -6019,7 +6074,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>1023</v>
       </c>
@@ -6051,7 +6106,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>1023</v>
       </c>
@@ -6083,7 +6138,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>1023</v>
       </c>
@@ -6115,7 +6170,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>1023</v>
       </c>
@@ -6144,7 +6199,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>1023</v>
       </c>
@@ -6176,7 +6231,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>1023</v>
       </c>
@@ -6205,7 +6260,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>1023</v>
       </c>
@@ -6234,7 +6289,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>1023</v>
       </c>
@@ -6266,7 +6321,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>1023</v>
       </c>
@@ -6298,7 +6353,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>1023</v>
       </c>
@@ -6327,7 +6382,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>1023</v>
       </c>
@@ -6359,7 +6414,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>1023</v>
       </c>
@@ -6391,7 +6446,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>1023</v>
       </c>
@@ -6423,7 +6478,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>1023</v>
       </c>
@@ -6452,7 +6507,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>1023</v>
       </c>
@@ -6484,7 +6539,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>1023</v>
       </c>
@@ -6513,7 +6568,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>1023</v>
       </c>
@@ -6542,7 +6597,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>1023</v>
       </c>
@@ -6574,7 +6629,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>1023</v>
       </c>
@@ -6606,7 +6661,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>1023</v>
       </c>
@@ -6638,7 +6693,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>1023</v>
       </c>
@@ -6670,7 +6725,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>1023</v>
       </c>
@@ -6702,7 +6757,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>1023</v>
       </c>
@@ -6734,7 +6789,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>1023</v>
       </c>
@@ -6763,7 +6818,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>1023</v>
       </c>
@@ -6795,7 +6850,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>1023</v>
       </c>
@@ -6827,7 +6882,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>1023</v>
       </c>
@@ -6859,7 +6914,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>1023</v>
       </c>
@@ -6891,7 +6946,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>1023</v>
       </c>
@@ -6905,7 +6960,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>1023</v>
       </c>
@@ -6919,7 +6974,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>1023</v>
       </c>
@@ -6933,7 +6988,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>1025</v>
       </c>
@@ -6959,7 +7014,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>1025</v>
       </c>
@@ -6991,7 +7046,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>1025</v>
       </c>
@@ -7023,7 +7078,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>1024</v>
       </c>
@@ -7055,7 +7110,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>1024</v>
       </c>
@@ -7087,7 +7142,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>1024</v>
       </c>
@@ -7119,7 +7174,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>1024</v>
       </c>
@@ -7151,7 +7206,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>1024</v>
       </c>
@@ -7183,7 +7238,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>1024</v>
       </c>
@@ -7215,7 +7270,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>1024</v>
       </c>
@@ -7247,7 +7302,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>1024</v>
       </c>
@@ -7279,7 +7334,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>1024</v>
       </c>
@@ -7311,7 +7366,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>1024</v>
       </c>
@@ -7343,7 +7398,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>1024</v>
       </c>
@@ -7375,39 +7430,39 @@
         <v>406</v>
       </c>
     </row>
-    <row r="100" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A100" s="3" t="s">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" t="s">
         <v>1024</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" t="s">
         <v>505</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" t="s">
         <v>183</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" t="s">
         <v>1032</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="E100" t="s">
         <v>1033</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="F100" t="s">
         <v>185</v>
       </c>
-      <c r="G100" s="3" t="s">
+      <c r="G100" t="s">
         <v>186</v>
       </c>
-      <c r="H100" s="3" t="s">
+      <c r="H100" t="s">
         <v>187</v>
       </c>
-      <c r="I100" s="3" t="s">
+      <c r="I100" t="s">
         <v>1034</v>
       </c>
-      <c r="J100" s="4" t="s">
+      <c r="J100" s="3" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>1024</v>
       </c>
@@ -7439,7 +7494,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>1024</v>
       </c>
@@ -7468,7 +7523,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>1024</v>
       </c>
@@ -7497,7 +7552,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>1024</v>
       </c>
@@ -7520,7 +7575,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>1024</v>
       </c>
@@ -7543,7 +7598,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>1024</v>
       </c>
@@ -7575,7 +7630,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
         <v>1024</v>
       </c>
@@ -7607,7 +7662,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
         <v>1024</v>
       </c>
@@ -7639,7 +7694,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>1024</v>
       </c>
@@ -7671,7 +7726,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>1024</v>
       </c>
@@ -7703,7 +7758,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
         <v>1024</v>
       </c>
@@ -7735,7 +7790,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
         <v>1024</v>
       </c>
@@ -7767,7 +7822,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
         <v>1024</v>
       </c>
@@ -7799,7 +7854,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
         <v>1024</v>
       </c>
@@ -7831,7 +7886,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>1024</v>
       </c>
@@ -7858,7 +7913,7 @@
       </c>
       <c r="J115" s="1"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
         <v>1024</v>
       </c>
@@ -7878,7 +7933,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>1024</v>
       </c>
@@ -7904,7 +7959,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
         <v>1024</v>
       </c>
@@ -7936,7 +7991,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>1024</v>
       </c>
@@ -7968,7 +8023,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
         <v>1024</v>
       </c>
@@ -7992,39 +8047,33 @@
       </c>
       <c r="J120" s="1"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B121" t="s">
-        <v>518</v>
+        <v>1036</v>
       </c>
       <c r="C121" t="s">
-        <v>396</v>
-      </c>
-      <c r="D121" t="s">
-        <v>397</v>
+        <v>1037</v>
       </c>
       <c r="E121" t="s">
-        <v>395</v>
+        <v>1038</v>
       </c>
       <c r="F121" t="s">
-        <v>398</v>
+        <v>1039</v>
       </c>
       <c r="G121" t="s">
-        <v>399</v>
-      </c>
-      <c r="H121" t="s">
-        <v>400</v>
-      </c>
-      <c r="I121" t="s">
-        <v>401</v>
-      </c>
-      <c r="J121" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.45">
+        <v>1040</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>1026</v>
       </c>
@@ -8032,121 +8081,127 @@
         <v>518</v>
       </c>
       <c r="C122" t="s">
-        <v>316</v>
+        <v>396</v>
       </c>
       <c r="D122" t="s">
-        <v>317</v>
+        <v>397</v>
       </c>
       <c r="E122" t="s">
-        <v>315</v>
+        <v>395</v>
       </c>
       <c r="F122" t="s">
-        <v>318</v>
+        <v>398</v>
       </c>
       <c r="G122" t="s">
-        <v>319</v>
+        <v>399</v>
       </c>
       <c r="H122" t="s">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="I122" t="s">
-        <v>321</v>
+        <v>401</v>
       </c>
       <c r="J122" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>1026</v>
       </c>
       <c r="B123" t="s">
-        <v>874</v>
+        <v>518</v>
       </c>
       <c r="C123" t="s">
-        <v>686</v>
+        <v>316</v>
       </c>
       <c r="D123" t="s">
-        <v>687</v>
+        <v>317</v>
       </c>
       <c r="E123" t="s">
-        <v>688</v>
+        <v>315</v>
       </c>
       <c r="F123" t="s">
-        <v>851</v>
+        <v>318</v>
       </c>
       <c r="G123" t="s">
-        <v>689</v>
+        <v>319</v>
       </c>
       <c r="H123" t="s">
-        <v>690</v>
+        <v>320</v>
       </c>
       <c r="I123" t="s">
-        <v>691</v>
+        <v>321</v>
       </c>
       <c r="J123" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
         <v>1026</v>
       </c>
       <c r="B124" t="s">
-        <v>516</v>
+        <v>874</v>
       </c>
       <c r="C124" t="s">
-        <v>300</v>
+        <v>686</v>
       </c>
       <c r="D124" t="s">
-        <v>301</v>
+        <v>687</v>
       </c>
       <c r="E124" t="s">
-        <v>299</v>
+        <v>688</v>
       </c>
       <c r="F124" t="s">
-        <v>302</v>
+        <v>851</v>
       </c>
       <c r="G124" t="s">
-        <v>303</v>
+        <v>689</v>
       </c>
       <c r="H124" t="s">
-        <v>304</v>
+        <v>690</v>
       </c>
       <c r="I124" t="s">
-        <v>305</v>
+        <v>691</v>
       </c>
       <c r="J124" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.45">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
         <v>1026</v>
       </c>
       <c r="B125" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C125" t="s">
-        <v>608</v>
+        <v>300</v>
       </c>
       <c r="D125" t="s">
-        <v>646</v>
+        <v>301</v>
       </c>
       <c r="E125" t="s">
-        <v>647</v>
+        <v>299</v>
       </c>
       <c r="F125" t="s">
-        <v>845</v>
+        <v>302</v>
       </c>
       <c r="G125" t="s">
-        <v>648</v>
+        <v>303</v>
+      </c>
+      <c r="H125" t="s">
+        <v>304</v>
+      </c>
+      <c r="I125" t="s">
+        <v>305</v>
       </c>
       <c r="J125" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
         <v>1026</v>
       </c>
@@ -8157,10 +8212,10 @@
         <v>608</v>
       </c>
       <c r="D126" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="E126" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="F126" t="s">
         <v>845</v>
@@ -8168,14 +8223,11 @@
       <c r="G126" t="s">
         <v>648</v>
       </c>
-      <c r="H126" t="s">
-        <v>652</v>
-      </c>
       <c r="J126" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
         <v>1026</v>
       </c>
@@ -8183,31 +8235,28 @@
         <v>514</v>
       </c>
       <c r="C127" t="s">
-        <v>284</v>
+        <v>608</v>
       </c>
       <c r="D127" t="s">
-        <v>285</v>
+        <v>650</v>
       </c>
       <c r="E127" t="s">
-        <v>283</v>
+        <v>651</v>
       </c>
       <c r="F127" t="s">
-        <v>286</v>
+        <v>845</v>
       </c>
       <c r="G127" t="s">
-        <v>287</v>
+        <v>648</v>
       </c>
       <c r="H127" t="s">
-        <v>288</v>
-      </c>
-      <c r="I127" t="s">
-        <v>289</v>
+        <v>652</v>
       </c>
       <c r="J127" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
         <v>1026</v>
       </c>
@@ -8217,26 +8266,29 @@
       <c r="C128" t="s">
         <v>284</v>
       </c>
+      <c r="D128" t="s">
+        <v>285</v>
+      </c>
       <c r="E128" t="s">
-        <v>785</v>
+        <v>283</v>
       </c>
       <c r="F128" t="s">
-        <v>860</v>
+        <v>286</v>
       </c>
       <c r="G128" t="s">
-        <v>786</v>
+        <v>287</v>
       </c>
       <c r="H128" t="s">
-        <v>787</v>
+        <v>288</v>
       </c>
       <c r="I128" t="s">
-        <v>788</v>
+        <v>289</v>
       </c>
       <c r="J128" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.45">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
         <v>1026</v>
       </c>
@@ -8246,58 +8298,58 @@
       <c r="C129" t="s">
         <v>284</v>
       </c>
-      <c r="D129" t="s">
-        <v>562</v>
-      </c>
       <c r="E129" t="s">
-        <v>800</v>
+        <v>785</v>
       </c>
       <c r="F129" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="G129" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="H129" t="s">
-        <v>802</v>
+        <v>787</v>
       </c>
       <c r="I129" t="s">
-        <v>803</v>
+        <v>788</v>
       </c>
       <c r="J129" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.45">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
         <v>1026</v>
       </c>
       <c r="B130" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="C130" t="s">
-        <v>584</v>
+        <v>284</v>
       </c>
       <c r="D130" t="s">
-        <v>585</v>
+        <v>562</v>
+      </c>
+      <c r="E130" t="s">
+        <v>800</v>
       </c>
       <c r="F130" t="s">
-        <v>586</v>
+        <v>863</v>
       </c>
       <c r="G130" t="s">
-        <v>587</v>
+        <v>801</v>
       </c>
       <c r="H130" t="s">
-        <v>588</v>
+        <v>802</v>
       </c>
       <c r="I130" t="s">
-        <v>589</v>
+        <v>803</v>
       </c>
       <c r="J130" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.45">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
         <v>1026</v>
       </c>
@@ -8305,127 +8357,124 @@
         <v>529</v>
       </c>
       <c r="C131" t="s">
-        <v>443</v>
+        <v>584</v>
       </c>
       <c r="D131" t="s">
-        <v>444</v>
-      </c>
-      <c r="E131" t="s">
-        <v>442</v>
+        <v>585</v>
       </c>
       <c r="F131" t="s">
-        <v>445</v>
+        <v>586</v>
       </c>
       <c r="G131" t="s">
-        <v>446</v>
+        <v>587</v>
       </c>
       <c r="H131" t="s">
-        <v>447</v>
+        <v>588</v>
       </c>
       <c r="I131" t="s">
-        <v>448</v>
+        <v>589</v>
       </c>
       <c r="J131" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.45">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
         <v>1026</v>
       </c>
       <c r="B132" t="s">
-        <v>501</v>
+        <v>529</v>
       </c>
       <c r="C132" t="s">
-        <v>138</v>
+        <v>443</v>
       </c>
       <c r="D132" t="s">
-        <v>139</v>
+        <v>444</v>
       </c>
       <c r="E132" t="s">
-        <v>137</v>
+        <v>442</v>
       </c>
       <c r="F132" t="s">
-        <v>140</v>
+        <v>445</v>
       </c>
       <c r="G132" t="s">
-        <v>141</v>
+        <v>446</v>
       </c>
       <c r="H132" t="s">
-        <v>142</v>
+        <v>447</v>
       </c>
       <c r="I132" t="s">
-        <v>143</v>
+        <v>448</v>
       </c>
       <c r="J132" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.45">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
         <v>1026</v>
       </c>
       <c r="B133" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="C133" t="s">
-        <v>254</v>
+        <v>138</v>
       </c>
       <c r="D133" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="E133" t="s">
-        <v>253</v>
+        <v>137</v>
       </c>
       <c r="F133" t="s">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="G133" t="s">
-        <v>256</v>
+        <v>141</v>
       </c>
       <c r="H133" t="s">
-        <v>256</v>
+        <v>142</v>
       </c>
       <c r="I133" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="J133" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.45">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
         <v>1026</v>
       </c>
       <c r="B134" t="s">
-        <v>870</v>
+        <v>512</v>
       </c>
       <c r="C134" t="s">
-        <v>597</v>
+        <v>254</v>
       </c>
       <c r="D134" t="s">
-        <v>598</v>
+        <v>165</v>
       </c>
       <c r="E134" t="s">
-        <v>599</v>
+        <v>253</v>
       </c>
       <c r="F134" t="s">
-        <v>841</v>
+        <v>255</v>
       </c>
       <c r="G134" t="s">
-        <v>600</v>
+        <v>256</v>
       </c>
       <c r="H134" t="s">
-        <v>601</v>
+        <v>256</v>
       </c>
       <c r="I134" t="s">
-        <v>602</v>
+        <v>257</v>
       </c>
       <c r="J134" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
         <v>1026</v>
       </c>
@@ -8436,10 +8485,10 @@
         <v>597</v>
       </c>
       <c r="D135" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="E135" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="F135" t="s">
         <v>841</v>
@@ -8451,45 +8500,45 @@
         <v>601</v>
       </c>
       <c r="I135" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="J135" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.45">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
         <v>1026</v>
       </c>
       <c r="B136" t="s">
-        <v>530</v>
+        <v>870</v>
       </c>
       <c r="C136" t="s">
-        <v>458</v>
+        <v>597</v>
       </c>
       <c r="D136" t="s">
-        <v>165</v>
+        <v>604</v>
       </c>
       <c r="E136" t="s">
-        <v>457</v>
+        <v>605</v>
       </c>
       <c r="F136" t="s">
-        <v>459</v>
+        <v>841</v>
       </c>
       <c r="G136" t="s">
-        <v>460</v>
+        <v>600</v>
       </c>
       <c r="H136" t="s">
-        <v>461</v>
+        <v>601</v>
       </c>
       <c r="I136" t="s">
-        <v>462</v>
+        <v>606</v>
       </c>
       <c r="J136" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.45">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
         <v>1026</v>
       </c>
@@ -8499,8 +8548,11 @@
       <c r="C137" t="s">
         <v>458</v>
       </c>
+      <c r="D137" t="s">
+        <v>165</v>
+      </c>
       <c r="E137" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="F137" t="s">
         <v>459</v>
@@ -8512,268 +8564,265 @@
         <v>461</v>
       </c>
       <c r="I137" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="J137" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
         <v>1026</v>
       </c>
       <c r="B138" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C138" t="s">
-        <v>491</v>
-      </c>
-      <c r="D138" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="E138" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
       <c r="F138" t="s">
-        <v>493</v>
+        <v>459</v>
       </c>
       <c r="G138" t="s">
-        <v>494</v>
+        <v>460</v>
       </c>
       <c r="H138" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="I138" t="s">
-        <v>496</v>
+        <v>465</v>
       </c>
       <c r="J138" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.45">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
         <v>1026</v>
       </c>
       <c r="B139" t="s">
-        <v>958</v>
+        <v>533</v>
       </c>
       <c r="C139" t="s">
-        <v>946</v>
+        <v>491</v>
       </c>
       <c r="D139" t="s">
-        <v>926</v>
+        <v>492</v>
       </c>
       <c r="E139" t="s">
-        <v>947</v>
+        <v>490</v>
       </c>
       <c r="F139" t="s">
-        <v>994</v>
+        <v>493</v>
       </c>
       <c r="G139" t="s">
-        <v>959</v>
+        <v>494</v>
       </c>
       <c r="H139" t="s">
-        <v>959</v>
+        <v>495</v>
       </c>
       <c r="I139" t="s">
-        <v>960</v>
-      </c>
-      <c r="J139" s="1" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.45">
+        <v>496</v>
+      </c>
+      <c r="J139" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
         <v>1026</v>
       </c>
       <c r="B140" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="C140" t="s">
-        <v>949</v>
+        <v>946</v>
+      </c>
+      <c r="D140" t="s">
+        <v>926</v>
+      </c>
+      <c r="E140" t="s">
+        <v>947</v>
+      </c>
+      <c r="F140" t="s">
+        <v>994</v>
       </c>
       <c r="G140" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="H140" t="s">
-        <v>962</v>
-      </c>
-      <c r="J140" s="1"/>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.45">
+        <v>959</v>
+      </c>
+      <c r="I140" t="s">
+        <v>960</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
         <v>1026</v>
       </c>
       <c r="B141" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C141" t="s">
-        <v>963</v>
+        <v>949</v>
       </c>
       <c r="G141" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="H141" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="J141" s="1"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
         <v>1026</v>
       </c>
       <c r="B142" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C142" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="G142" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="H142" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="J142" s="1"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
         <v>1026</v>
       </c>
       <c r="B143" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C143" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="G143" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="H143" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="J143" s="1"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
         <v>1026</v>
       </c>
       <c r="B144" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C144" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="G144" t="s">
-        <v>973</v>
+        <v>970</v>
+      </c>
+      <c r="H144" t="s">
+        <v>971</v>
       </c>
       <c r="J144" s="1"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
         <v>1026</v>
       </c>
       <c r="B145" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C145" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G145" t="s">
-        <v>975</v>
-      </c>
-      <c r="H145" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="J145" s="1"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
         <v>1026</v>
       </c>
       <c r="B146" t="s">
-        <v>977</v>
+        <v>955</v>
       </c>
       <c r="C146" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="G146" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="H146" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="J146" s="1"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" t="s">
         <v>1026</v>
       </c>
       <c r="B147" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="C147" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="G147" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="H147" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="J147" s="1"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" t="s">
         <v>1026</v>
       </c>
       <c r="B148" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C148" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="G148" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="H148" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="J148" s="1"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
         <v>1026</v>
       </c>
       <c r="B149" t="s">
-        <v>864</v>
+        <v>957</v>
       </c>
       <c r="C149" t="s">
-        <v>260</v>
-      </c>
-      <c r="D149" t="s">
-        <v>261</v>
-      </c>
-      <c r="E149" t="s">
-        <v>259</v>
-      </c>
-      <c r="F149" t="s">
-        <v>262</v>
+        <v>984</v>
       </c>
       <c r="G149" t="s">
-        <v>263</v>
+        <v>985</v>
       </c>
       <c r="H149" t="s">
-        <v>264</v>
-      </c>
-      <c r="I149" t="s">
-        <v>265</v>
-      </c>
-      <c r="J149" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.45">
+        <v>986</v>
+      </c>
+      <c r="J149" s="1"/>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
         <v>1026</v>
       </c>
@@ -8781,31 +8830,31 @@
         <v>864</v>
       </c>
       <c r="C150" t="s">
-        <v>534</v>
+        <v>260</v>
       </c>
       <c r="D150" t="s">
-        <v>535</v>
+        <v>261</v>
       </c>
       <c r="E150" t="s">
-        <v>536</v>
+        <v>259</v>
       </c>
       <c r="F150" t="s">
-        <v>833</v>
+        <v>262</v>
       </c>
       <c r="G150" t="s">
-        <v>537</v>
+        <v>263</v>
       </c>
       <c r="H150" t="s">
-        <v>538</v>
+        <v>264</v>
       </c>
       <c r="I150" t="s">
-        <v>539</v>
+        <v>265</v>
       </c>
       <c r="J150" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.45">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" t="s">
         <v>1026</v>
       </c>
@@ -8813,31 +8862,31 @@
         <v>864</v>
       </c>
       <c r="C151" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D151" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="E151" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="F151" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G151" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="H151" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="I151" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="J151" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.45">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
         <v>1026</v>
       </c>
@@ -8845,57 +8894,60 @@
         <v>864</v>
       </c>
       <c r="C152" t="s">
+        <v>541</v>
+      </c>
+      <c r="D152" t="s">
+        <v>542</v>
+      </c>
+      <c r="E152" t="s">
+        <v>543</v>
+      </c>
+      <c r="F152" t="s">
+        <v>834</v>
+      </c>
+      <c r="G152" t="s">
+        <v>544</v>
+      </c>
+      <c r="H152" t="s">
+        <v>545</v>
+      </c>
+      <c r="I152" t="s">
+        <v>546</v>
+      </c>
+      <c r="J152" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A153" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B153" t="s">
+        <v>864</v>
+      </c>
+      <c r="C153" t="s">
         <v>164</v>
       </c>
-      <c r="D152" t="s">
+      <c r="D153" t="s">
         <v>165</v>
       </c>
-      <c r="E152" t="s">
+      <c r="E153" t="s">
         <v>163</v>
       </c>
-      <c r="F152" t="s">
+      <c r="F153" t="s">
         <v>166</v>
       </c>
-      <c r="G152" t="s">
+      <c r="G153" t="s">
         <v>167</v>
       </c>
-      <c r="H152" t="s">
+      <c r="H153" t="s">
         <v>168</v>
       </c>
-      <c r="J152" t="s">
+      <c r="J153" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A153" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B153" t="s">
-        <v>867</v>
-      </c>
-      <c r="C153" t="s">
-        <v>115</v>
-      </c>
-      <c r="D153" t="s">
-        <v>825</v>
-      </c>
-      <c r="E153" t="s">
-        <v>824</v>
-      </c>
-      <c r="F153" t="s">
-        <v>826</v>
-      </c>
-      <c r="G153" t="s">
-        <v>827</v>
-      </c>
-      <c r="H153" t="s">
-        <v>119</v>
-      </c>
-      <c r="J153" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
         <v>1022</v>
       </c>
@@ -8906,28 +8958,25 @@
         <v>115</v>
       </c>
       <c r="D154" t="s">
-        <v>609</v>
+        <v>825</v>
       </c>
       <c r="E154" t="s">
-        <v>610</v>
+        <v>824</v>
       </c>
       <c r="F154" t="s">
-        <v>842</v>
+        <v>826</v>
       </c>
       <c r="G154" t="s">
-        <v>611</v>
+        <v>827</v>
       </c>
       <c r="H154" t="s">
         <v>119</v>
       </c>
-      <c r="I154" t="s">
-        <v>612</v>
-      </c>
       <c r="J154" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" t="s">
         <v>1022</v>
       </c>
@@ -8938,19 +8987,28 @@
         <v>115</v>
       </c>
       <c r="D155" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="E155" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="F155" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G155" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.45">
+        <v>611</v>
+      </c>
+      <c r="H155" t="s">
+        <v>119</v>
+      </c>
+      <c r="I155" t="s">
+        <v>612</v>
+      </c>
+      <c r="J155" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" t="s">
         <v>1022</v>
       </c>
@@ -8961,10 +9019,10 @@
         <v>115</v>
       </c>
       <c r="D156" t="s">
-        <v>535</v>
+        <v>614</v>
       </c>
       <c r="E156" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="F156" t="s">
         <v>843</v>
@@ -8972,17 +9030,8 @@
       <c r="G156" t="s">
         <v>616</v>
       </c>
-      <c r="H156" t="s">
-        <v>618</v>
-      </c>
-      <c r="I156" t="s">
-        <v>619</v>
-      </c>
-      <c r="J156" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.45">
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" t="s">
         <v>1022</v>
       </c>
@@ -8993,10 +9042,10 @@
         <v>115</v>
       </c>
       <c r="D157" t="s">
-        <v>621</v>
+        <v>535</v>
       </c>
       <c r="E157" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="F157" t="s">
         <v>843</v>
@@ -9008,13 +9057,13 @@
         <v>618</v>
       </c>
       <c r="I157" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="J157" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.45">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" t="s">
         <v>1022</v>
       </c>
@@ -9025,28 +9074,28 @@
         <v>115</v>
       </c>
       <c r="D158" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="E158" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="F158" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G158" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="H158" t="s">
-        <v>119</v>
+        <v>618</v>
       </c>
       <c r="I158" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="J158" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.45">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" t="s">
         <v>1022</v>
       </c>
@@ -9057,28 +9106,28 @@
         <v>115</v>
       </c>
       <c r="D159" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="E159" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="F159" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G159" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="H159" t="s">
-        <v>618</v>
+        <v>119</v>
       </c>
       <c r="I159" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="J159" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.45">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" t="s">
         <v>1022</v>
       </c>
@@ -9089,25 +9138,28 @@
         <v>115</v>
       </c>
       <c r="D160" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="E160" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="F160" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G160" t="s">
-        <v>635</v>
+        <v>616</v>
+      </c>
+      <c r="H160" t="s">
+        <v>618</v>
       </c>
       <c r="I160" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="J160" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.45">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" t="s">
         <v>1022</v>
       </c>
@@ -9118,10 +9170,10 @@
         <v>115</v>
       </c>
       <c r="D161" t="s">
-        <v>317</v>
+        <v>633</v>
       </c>
       <c r="E161" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="F161" t="s">
         <v>844</v>
@@ -9130,13 +9182,13 @@
         <v>635</v>
       </c>
       <c r="I161" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="J161" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.45">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" t="s">
         <v>1022</v>
       </c>
@@ -9147,54 +9199,57 @@
         <v>115</v>
       </c>
       <c r="D162" t="s">
-        <v>621</v>
+        <v>317</v>
       </c>
       <c r="E162" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F162" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="G162" t="s">
-        <v>642</v>
-      </c>
-      <c r="H162" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="I162" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="J162" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.45">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" t="s">
         <v>1022</v>
       </c>
       <c r="B163" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
       <c r="C163" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="D163" t="s">
-        <v>10</v>
+        <v>621</v>
       </c>
       <c r="E163" t="s">
-        <v>8</v>
+        <v>641</v>
       </c>
       <c r="F163" t="s">
-        <v>11</v>
+        <v>842</v>
       </c>
       <c r="G163" t="s">
-        <v>12</v>
+        <v>642</v>
       </c>
       <c r="H163" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.45">
+        <v>643</v>
+      </c>
+      <c r="I163" t="s">
+        <v>644</v>
+      </c>
+      <c r="J163" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" t="s">
         <v>1022</v>
       </c>
@@ -9202,31 +9257,25 @@
         <v>880</v>
       </c>
       <c r="C164" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D164" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E164" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F164" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G164" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H164" t="s">
-        <v>19</v>
-      </c>
-      <c r="I164" t="s">
-        <v>20</v>
-      </c>
-      <c r="J164" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" t="s">
         <v>1022</v>
       </c>
@@ -9237,10 +9286,10 @@
         <v>15</v>
       </c>
       <c r="D165" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E165" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F165" t="s">
         <v>17</v>
@@ -9252,13 +9301,13 @@
         <v>19</v>
       </c>
       <c r="I165" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J165" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.45">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" t="s">
         <v>1022</v>
       </c>
@@ -9269,28 +9318,28 @@
         <v>15</v>
       </c>
       <c r="D166" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E166" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F166" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G166" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H166" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I166" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J166" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" t="s">
         <v>1022</v>
       </c>
@@ -9301,10 +9350,10 @@
         <v>15</v>
       </c>
       <c r="D167" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E167" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F167" t="s">
         <v>28</v>
@@ -9316,13 +9365,13 @@
         <v>30</v>
       </c>
       <c r="I167" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J167" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" t="s">
         <v>1022</v>
       </c>
@@ -9333,10 +9382,10 @@
         <v>15</v>
       </c>
       <c r="D168" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E168" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -9348,13 +9397,13 @@
         <v>30</v>
       </c>
       <c r="I168" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J168" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.45">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" t="s">
         <v>1022</v>
       </c>
@@ -9362,45 +9411,60 @@
         <v>880</v>
       </c>
       <c r="C169" t="s">
+        <v>15</v>
+      </c>
+      <c r="D169" t="s">
+        <v>38</v>
+      </c>
+      <c r="E169" t="s">
+        <v>37</v>
+      </c>
+      <c r="F169" t="s">
+        <v>28</v>
+      </c>
+      <c r="G169" t="s">
+        <v>29</v>
+      </c>
+      <c r="H169" t="s">
+        <v>30</v>
+      </c>
+      <c r="I169" t="s">
+        <v>39</v>
+      </c>
+      <c r="J169" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A170" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B170" t="s">
+        <v>880</v>
+      </c>
+      <c r="C170" t="s">
         <v>115</v>
       </c>
-      <c r="D169" t="s">
+      <c r="D170" t="s">
         <v>116</v>
       </c>
-      <c r="E169" t="s">
+      <c r="E170" t="s">
         <v>114</v>
       </c>
-      <c r="F169" t="s">
+      <c r="F170" t="s">
         <v>117</v>
       </c>
-      <c r="G169" t="s">
+      <c r="G170" t="s">
         <v>118</v>
       </c>
-      <c r="H169" t="s">
+      <c r="H170" t="s">
         <v>119</v>
       </c>
-      <c r="J169" t="s">
+      <c r="J170" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A170" t="s">
-        <v>888</v>
-      </c>
-      <c r="C170" t="s">
-        <v>913</v>
-      </c>
-      <c r="D170" t="s">
-        <v>889</v>
-      </c>
-      <c r="E170" t="s">
-        <v>893</v>
-      </c>
-      <c r="I170" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" t="s">
         <v>888</v>
       </c>
@@ -9408,16 +9472,16 @@
         <v>913</v>
       </c>
       <c r="D171" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E171" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="I171" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.45">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" t="s">
         <v>888</v>
       </c>
@@ -9425,16 +9489,16 @@
         <v>913</v>
       </c>
       <c r="D172" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E172" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="I172" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.45">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" t="s">
         <v>888</v>
       </c>
@@ -9442,16 +9506,16 @@
         <v>913</v>
       </c>
       <c r="D173" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E173" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="I173" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.45">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" t="s">
         <v>888</v>
       </c>
@@ -9459,16 +9523,16 @@
         <v>913</v>
       </c>
       <c r="D174" t="s">
-        <v>902</v>
+        <v>892</v>
       </c>
       <c r="E174" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="I174" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.45">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" t="s">
         <v>888</v>
       </c>
@@ -9479,13 +9543,13 @@
         <v>902</v>
       </c>
       <c r="E175" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="I175" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.45">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" t="s">
         <v>888</v>
       </c>
@@ -9493,16 +9557,16 @@
         <v>913</v>
       </c>
       <c r="D176" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E176" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="I176" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.45">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" t="s">
         <v>888</v>
       </c>
@@ -9513,13 +9577,13 @@
         <v>903</v>
       </c>
       <c r="E177" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="I177" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.45">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" t="s">
         <v>888</v>
       </c>
@@ -9530,15 +9594,32 @@
         <v>903</v>
       </c>
       <c r="E178" t="s">
+        <v>900</v>
+      </c>
+      <c r="I178" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A179" t="s">
+        <v>888</v>
+      </c>
+      <c r="C179" t="s">
+        <v>913</v>
+      </c>
+      <c r="D179" t="s">
+        <v>903</v>
+      </c>
+      <c r="E179" t="s">
         <v>901</v>
       </c>
-      <c r="I178" t="s">
+      <c r="I179" t="s">
         <v>912</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A43:J169">
-    <sortCondition ref="A43:A169"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A43:J170">
+    <sortCondition ref="A43:A170"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -9546,10 +9627,11 @@
     <hyperlink ref="J87" r:id="rId2" xr:uid="{04B79727-E872-4B92-B9FF-E52CDD567289}"/>
     <hyperlink ref="J88" r:id="rId3" xr:uid="{58FC3E9B-DA5E-47AE-A0FA-48744DC7E69C}"/>
     <hyperlink ref="J119" r:id="rId4" xr:uid="{0CDDE2B0-9A66-4763-82CA-FB9054DBD36D}"/>
-    <hyperlink ref="J139" r:id="rId5" xr:uid="{D959C86A-275E-4D89-91FD-60DBE69A6EE8}"/>
+    <hyperlink ref="J140" r:id="rId5" xr:uid="{D959C86A-275E-4D89-91FD-60DBE69A6EE8}"/>
     <hyperlink ref="J82" r:id="rId6" xr:uid="{AE797D3F-4BC0-45F7-BAAF-49AAE05332D6}"/>
     <hyperlink ref="J118" r:id="rId7" xr:uid="{E353EA49-C20B-4A50-9E3E-3B8FC192D763}"/>
     <hyperlink ref="J100" r:id="rId8" xr:uid="{A98CDD58-6463-49F3-9952-BC0BEE6FEAA2}"/>
+    <hyperlink ref="J121" r:id="rId9" xr:uid="{AB76B266-A10F-4CFC-8443-AA6443702A5B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="821" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEE41166-3AD9-4CD8-B784-4EB617F49FA9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
+    <workbookView xWindow="340" yWindow="0" windowWidth="9600" windowHeight="10080" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
   </bookViews>
   <sheets>
     <sheet name="data.xlsx" sheetId="1" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kiuchi-my.sharepoint.com/personal/isozaki_kiuchi_co_jp/Documents/fmsf-phone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="821" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEE41166-3AD9-4CD8-B784-4EB617F49FA9}"/>
+  <xr:revisionPtr revIDLastSave="842" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6835AA75-F783-4CD3-B043-31EE5AFDA4F8}"/>
   <bookViews>
-    <workbookView xWindow="340" yWindow="0" windowWidth="9600" windowHeight="10080" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
   </bookViews>
   <sheets>
     <sheet name="data.xlsx" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="1043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="1055">
   <si>
     <t>氏名</t>
   </si>
@@ -4177,6 +4177,87 @@
   </si>
   <si>
     <t>azechi-seikou@ny.tokai.or.jp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>久保田 繁美</t>
+    <rPh sb="0" eb="3">
+      <t>クボタ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シゲミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kubota-seikou@ny.tokai.or.jp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宮川 大樹</t>
+    <rPh sb="0" eb="2">
+      <t>ミヤガワ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ダイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>090-4114-7980</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>080-2605-5119</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>080-2605-5326</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>福井 一博</t>
+    <rPh sb="0" eb="2">
+      <t>フクイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥村 峰仁</t>
+    <rPh sb="0" eb="2">
+      <t>オクムラ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ミネ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ジン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>浅見</t>
+    <rPh sb="0" eb="2">
+      <t>アサミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>粟田</t>
+    <rPh sb="0" eb="2">
+      <t>アワタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>asami@ys-h.co.jp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>awata@ys-h.co.jp</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4611,7 +4692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED22340-6398-430F-AD0F-E88DFD8C2F52}">
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J184"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="8.9140625" customWidth="1"/>
@@ -7923,6 +8004,9 @@
       <c r="C116" t="s">
         <v>1011</v>
       </c>
+      <c r="E116" t="s">
+        <v>1051</v>
+      </c>
       <c r="F116" t="s">
         <v>1012</v>
       </c>
@@ -7931,6 +8015,9 @@
       </c>
       <c r="H116" t="s">
         <v>1014</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>1053</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -7938,25 +8025,25 @@
         <v>1024</v>
       </c>
       <c r="B117" t="s">
-        <v>1021</v>
+        <v>505</v>
       </c>
       <c r="C117" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D117" t="s">
-        <v>926</v>
+        <v>1011</v>
       </c>
       <c r="E117" t="s">
-        <v>1016</v>
+        <v>1052</v>
       </c>
       <c r="F117" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>1018</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>1019</v>
+        <v>1012</v>
+      </c>
+      <c r="G117" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H117" t="s">
+        <v>1014</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>1054</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -7964,31 +8051,25 @@
         <v>1024</v>
       </c>
       <c r="B118" t="s">
-        <v>987</v>
+        <v>1021</v>
       </c>
       <c r="C118" t="s">
-        <v>924</v>
+        <v>1015</v>
       </c>
       <c r="D118" t="s">
         <v>926</v>
       </c>
       <c r="E118" t="s">
-        <v>1005</v>
+        <v>1016</v>
       </c>
       <c r="F118" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G118" t="s">
-        <v>1007</v>
-      </c>
-      <c r="H118" t="s">
-        <v>1008</v>
-      </c>
-      <c r="I118" t="s">
-        <v>1009</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>1010</v>
+        <v>1017</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>1019</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -7996,31 +8077,31 @@
         <v>1024</v>
       </c>
       <c r="B119" t="s">
-        <v>936</v>
+        <v>987</v>
       </c>
       <c r="C119" t="s">
-        <v>937</v>
+        <v>924</v>
       </c>
       <c r="D119" t="s">
-        <v>938</v>
+        <v>926</v>
       </c>
       <c r="E119" t="s">
-        <v>939</v>
+        <v>1005</v>
       </c>
       <c r="F119" t="s">
-        <v>940</v>
+        <v>1006</v>
       </c>
       <c r="G119" t="s">
-        <v>941</v>
+        <v>1007</v>
       </c>
       <c r="H119" t="s">
-        <v>942</v>
+        <v>1008</v>
       </c>
       <c r="I119" t="s">
-        <v>943</v>
+        <v>1009</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>944</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8028,113 +8109,107 @@
         <v>1024</v>
       </c>
       <c r="B120" t="s">
-        <v>1027</v>
+        <v>936</v>
       </c>
       <c r="C120" t="s">
-        <v>1028</v>
+        <v>937</v>
       </c>
       <c r="D120" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="E120" t="s">
-        <v>1029</v>
+        <v>939</v>
       </c>
       <c r="F120" t="s">
-        <v>1030</v>
+        <v>940</v>
       </c>
       <c r="G120" t="s">
-        <v>1031</v>
-      </c>
-      <c r="J120" s="1"/>
+        <v>941</v>
+      </c>
+      <c r="H120" t="s">
+        <v>942</v>
+      </c>
+      <c r="I120" t="s">
+        <v>943</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>944</v>
+      </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>1024</v>
       </c>
       <c r="B121" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
       <c r="C121" t="s">
-        <v>1037</v>
+        <v>1028</v>
+      </c>
+      <c r="D121" t="s">
+        <v>926</v>
       </c>
       <c r="E121" t="s">
-        <v>1038</v>
+        <v>1029</v>
       </c>
       <c r="F121" t="s">
-        <v>1039</v>
+        <v>1030</v>
       </c>
       <c r="G121" t="s">
-        <v>1040</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>1041</v>
-      </c>
-      <c r="J121" s="1" t="s">
-        <v>1042</v>
-      </c>
+        <v>1031</v>
+      </c>
+      <c r="J121" s="1"/>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B122" t="s">
-        <v>518</v>
+        <v>1036</v>
       </c>
       <c r="C122" t="s">
-        <v>396</v>
-      </c>
-      <c r="D122" t="s">
-        <v>397</v>
+        <v>1037</v>
       </c>
       <c r="E122" t="s">
-        <v>395</v>
+        <v>1043</v>
       </c>
       <c r="F122" t="s">
-        <v>398</v>
+        <v>1039</v>
       </c>
       <c r="G122" t="s">
-        <v>399</v>
-      </c>
-      <c r="H122" t="s">
-        <v>400</v>
-      </c>
-      <c r="I122" t="s">
-        <v>401</v>
-      </c>
-      <c r="J122" t="s">
-        <v>402</v>
+        <v>1040</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>1044</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B123" t="s">
-        <v>518</v>
+        <v>1036</v>
       </c>
       <c r="C123" t="s">
-        <v>316</v>
-      </c>
-      <c r="D123" t="s">
-        <v>317</v>
+        <v>1037</v>
       </c>
       <c r="E123" t="s">
-        <v>315</v>
+        <v>1038</v>
       </c>
       <c r="F123" t="s">
-        <v>318</v>
+        <v>1039</v>
       </c>
       <c r="G123" t="s">
-        <v>319</v>
-      </c>
-      <c r="H123" t="s">
-        <v>320</v>
-      </c>
-      <c r="I123" t="s">
-        <v>321</v>
-      </c>
-      <c r="J123" t="s">
-        <v>322</v>
+        <v>1040</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>1042</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8142,31 +8217,31 @@
         <v>1026</v>
       </c>
       <c r="B124" t="s">
-        <v>874</v>
+        <v>518</v>
       </c>
       <c r="C124" t="s">
-        <v>686</v>
+        <v>396</v>
       </c>
       <c r="D124" t="s">
-        <v>687</v>
+        <v>397</v>
       </c>
       <c r="E124" t="s">
-        <v>688</v>
+        <v>395</v>
       </c>
       <c r="F124" t="s">
-        <v>851</v>
+        <v>398</v>
       </c>
       <c r="G124" t="s">
-        <v>689</v>
+        <v>399</v>
       </c>
       <c r="H124" t="s">
-        <v>690</v>
+        <v>400</v>
       </c>
       <c r="I124" t="s">
-        <v>691</v>
+        <v>401</v>
       </c>
       <c r="J124" t="s">
-        <v>692</v>
+        <v>402</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8174,31 +8249,31 @@
         <v>1026</v>
       </c>
       <c r="B125" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C125" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="D125" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="E125" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="F125" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="G125" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="H125" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="I125" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="J125" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8206,25 +8281,31 @@
         <v>1026</v>
       </c>
       <c r="B126" t="s">
-        <v>514</v>
+        <v>874</v>
       </c>
       <c r="C126" t="s">
-        <v>608</v>
+        <v>686</v>
       </c>
       <c r="D126" t="s">
-        <v>646</v>
+        <v>687</v>
       </c>
       <c r="E126" t="s">
-        <v>647</v>
+        <v>688</v>
       </c>
       <c r="F126" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="G126" t="s">
-        <v>648</v>
+        <v>689</v>
+      </c>
+      <c r="H126" t="s">
+        <v>690</v>
+      </c>
+      <c r="I126" t="s">
+        <v>691</v>
       </c>
       <c r="J126" t="s">
-        <v>649</v>
+        <v>692</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8232,28 +8313,31 @@
         <v>1026</v>
       </c>
       <c r="B127" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C127" t="s">
-        <v>608</v>
+        <v>300</v>
       </c>
       <c r="D127" t="s">
-        <v>650</v>
+        <v>301</v>
       </c>
       <c r="E127" t="s">
-        <v>651</v>
+        <v>299</v>
       </c>
       <c r="F127" t="s">
-        <v>845</v>
+        <v>302</v>
       </c>
       <c r="G127" t="s">
-        <v>648</v>
+        <v>303</v>
       </c>
       <c r="H127" t="s">
-        <v>652</v>
+        <v>304</v>
+      </c>
+      <c r="I127" t="s">
+        <v>305</v>
       </c>
       <c r="J127" t="s">
-        <v>653</v>
+        <v>306</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8264,28 +8348,22 @@
         <v>514</v>
       </c>
       <c r="C128" t="s">
-        <v>284</v>
+        <v>608</v>
       </c>
       <c r="D128" t="s">
-        <v>285</v>
+        <v>646</v>
       </c>
       <c r="E128" t="s">
-        <v>283</v>
+        <v>647</v>
       </c>
       <c r="F128" t="s">
-        <v>286</v>
+        <v>845</v>
       </c>
       <c r="G128" t="s">
-        <v>287</v>
-      </c>
-      <c r="H128" t="s">
-        <v>288</v>
-      </c>
-      <c r="I128" t="s">
-        <v>289</v>
+        <v>648</v>
       </c>
       <c r="J128" t="s">
-        <v>290</v>
+        <v>649</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8296,25 +8374,25 @@
         <v>514</v>
       </c>
       <c r="C129" t="s">
-        <v>284</v>
+        <v>608</v>
+      </c>
+      <c r="D129" t="s">
+        <v>650</v>
       </c>
       <c r="E129" t="s">
-        <v>785</v>
+        <v>651</v>
       </c>
       <c r="F129" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="G129" t="s">
-        <v>786</v>
+        <v>648</v>
       </c>
       <c r="H129" t="s">
-        <v>787</v>
-      </c>
-      <c r="I129" t="s">
-        <v>788</v>
+        <v>652</v>
       </c>
       <c r="J129" t="s">
-        <v>789</v>
+        <v>653</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8328,25 +8406,25 @@
         <v>284</v>
       </c>
       <c r="D130" t="s">
-        <v>562</v>
+        <v>285</v>
       </c>
       <c r="E130" t="s">
-        <v>800</v>
+        <v>283</v>
       </c>
       <c r="F130" t="s">
-        <v>863</v>
+        <v>286</v>
       </c>
       <c r="G130" t="s">
-        <v>801</v>
+        <v>287</v>
       </c>
       <c r="H130" t="s">
-        <v>802</v>
+        <v>288</v>
       </c>
       <c r="I130" t="s">
-        <v>803</v>
+        <v>289</v>
       </c>
       <c r="J130" t="s">
-        <v>804</v>
+        <v>290</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8354,28 +8432,28 @@
         <v>1026</v>
       </c>
       <c r="B131" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="C131" t="s">
-        <v>584</v>
-      </c>
-      <c r="D131" t="s">
-        <v>585</v>
+        <v>284</v>
+      </c>
+      <c r="E131" t="s">
+        <v>785</v>
       </c>
       <c r="F131" t="s">
-        <v>586</v>
+        <v>860</v>
       </c>
       <c r="G131" t="s">
-        <v>587</v>
+        <v>786</v>
       </c>
       <c r="H131" t="s">
-        <v>588</v>
+        <v>787</v>
       </c>
       <c r="I131" t="s">
-        <v>589</v>
+        <v>788</v>
       </c>
       <c r="J131" t="s">
-        <v>590</v>
+        <v>789</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8383,31 +8461,31 @@
         <v>1026</v>
       </c>
       <c r="B132" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="C132" t="s">
-        <v>443</v>
+        <v>284</v>
       </c>
       <c r="D132" t="s">
-        <v>444</v>
+        <v>562</v>
       </c>
       <c r="E132" t="s">
-        <v>442</v>
+        <v>800</v>
       </c>
       <c r="F132" t="s">
-        <v>445</v>
+        <v>863</v>
       </c>
       <c r="G132" t="s">
-        <v>446</v>
+        <v>801</v>
       </c>
       <c r="H132" t="s">
-        <v>447</v>
+        <v>802</v>
       </c>
       <c r="I132" t="s">
-        <v>448</v>
+        <v>803</v>
       </c>
       <c r="J132" t="s">
-        <v>449</v>
+        <v>804</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8415,31 +8493,28 @@
         <v>1026</v>
       </c>
       <c r="B133" t="s">
-        <v>501</v>
+        <v>529</v>
       </c>
       <c r="C133" t="s">
-        <v>138</v>
+        <v>584</v>
       </c>
       <c r="D133" t="s">
-        <v>139</v>
-      </c>
-      <c r="E133" t="s">
-        <v>137</v>
+        <v>585</v>
       </c>
       <c r="F133" t="s">
-        <v>140</v>
+        <v>586</v>
       </c>
       <c r="G133" t="s">
-        <v>141</v>
+        <v>587</v>
       </c>
       <c r="H133" t="s">
-        <v>142</v>
+        <v>588</v>
       </c>
       <c r="I133" t="s">
-        <v>143</v>
+        <v>589</v>
       </c>
       <c r="J133" t="s">
-        <v>144</v>
+        <v>590</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8447,31 +8522,31 @@
         <v>1026</v>
       </c>
       <c r="B134" t="s">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="C134" t="s">
-        <v>254</v>
+        <v>443</v>
       </c>
       <c r="D134" t="s">
-        <v>165</v>
+        <v>444</v>
       </c>
       <c r="E134" t="s">
-        <v>253</v>
+        <v>442</v>
       </c>
       <c r="F134" t="s">
-        <v>255</v>
+        <v>445</v>
       </c>
       <c r="G134" t="s">
-        <v>256</v>
+        <v>446</v>
       </c>
       <c r="H134" t="s">
-        <v>256</v>
+        <v>447</v>
       </c>
       <c r="I134" t="s">
-        <v>257</v>
+        <v>448</v>
       </c>
       <c r="J134" t="s">
-        <v>258</v>
+        <v>449</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8479,31 +8554,31 @@
         <v>1026</v>
       </c>
       <c r="B135" t="s">
-        <v>870</v>
+        <v>501</v>
       </c>
       <c r="C135" t="s">
-        <v>597</v>
+        <v>138</v>
       </c>
       <c r="D135" t="s">
-        <v>598</v>
+        <v>139</v>
       </c>
       <c r="E135" t="s">
-        <v>599</v>
+        <v>137</v>
       </c>
       <c r="F135" t="s">
-        <v>841</v>
+        <v>140</v>
       </c>
       <c r="G135" t="s">
-        <v>600</v>
+        <v>141</v>
       </c>
       <c r="H135" t="s">
-        <v>601</v>
+        <v>142</v>
       </c>
       <c r="I135" t="s">
-        <v>602</v>
+        <v>143</v>
       </c>
       <c r="J135" t="s">
-        <v>603</v>
+        <v>144</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8511,31 +8586,31 @@
         <v>1026</v>
       </c>
       <c r="B136" t="s">
-        <v>870</v>
+        <v>512</v>
       </c>
       <c r="C136" t="s">
-        <v>597</v>
+        <v>254</v>
       </c>
       <c r="D136" t="s">
-        <v>604</v>
+        <v>165</v>
       </c>
       <c r="E136" t="s">
-        <v>605</v>
+        <v>253</v>
       </c>
       <c r="F136" t="s">
-        <v>841</v>
+        <v>255</v>
       </c>
       <c r="G136" t="s">
-        <v>600</v>
+        <v>256</v>
       </c>
       <c r="H136" t="s">
-        <v>601</v>
+        <v>256</v>
       </c>
       <c r="I136" t="s">
-        <v>606</v>
+        <v>257</v>
       </c>
       <c r="J136" t="s">
-        <v>607</v>
+        <v>258</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8543,31 +8618,31 @@
         <v>1026</v>
       </c>
       <c r="B137" t="s">
-        <v>530</v>
+        <v>870</v>
       </c>
       <c r="C137" t="s">
-        <v>458</v>
+        <v>597</v>
       </c>
       <c r="D137" t="s">
-        <v>165</v>
+        <v>598</v>
       </c>
       <c r="E137" t="s">
-        <v>457</v>
+        <v>599</v>
       </c>
       <c r="F137" t="s">
-        <v>459</v>
+        <v>841</v>
       </c>
       <c r="G137" t="s">
-        <v>460</v>
+        <v>600</v>
       </c>
       <c r="H137" t="s">
-        <v>461</v>
+        <v>601</v>
       </c>
       <c r="I137" t="s">
-        <v>462</v>
+        <v>602</v>
       </c>
       <c r="J137" t="s">
-        <v>463</v>
+        <v>603</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8575,28 +8650,31 @@
         <v>1026</v>
       </c>
       <c r="B138" t="s">
-        <v>530</v>
+        <v>870</v>
       </c>
       <c r="C138" t="s">
-        <v>458</v>
+        <v>597</v>
+      </c>
+      <c r="D138" t="s">
+        <v>604</v>
       </c>
       <c r="E138" t="s">
-        <v>464</v>
+        <v>605</v>
       </c>
       <c r="F138" t="s">
-        <v>459</v>
+        <v>841</v>
       </c>
       <c r="G138" t="s">
-        <v>460</v>
+        <v>600</v>
       </c>
       <c r="H138" t="s">
-        <v>461</v>
+        <v>601</v>
       </c>
       <c r="I138" t="s">
-        <v>465</v>
+        <v>606</v>
       </c>
       <c r="J138" t="s">
-        <v>463</v>
+        <v>607</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8604,31 +8682,31 @@
         <v>1026</v>
       </c>
       <c r="B139" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C139" t="s">
-        <v>491</v>
+        <v>458</v>
       </c>
       <c r="D139" t="s">
-        <v>492</v>
+        <v>165</v>
       </c>
       <c r="E139" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="F139" t="s">
-        <v>493</v>
+        <v>459</v>
       </c>
       <c r="G139" t="s">
-        <v>494</v>
+        <v>460</v>
       </c>
       <c r="H139" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="I139" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="J139" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8636,31 +8714,28 @@
         <v>1026</v>
       </c>
       <c r="B140" t="s">
-        <v>958</v>
+        <v>530</v>
       </c>
       <c r="C140" t="s">
-        <v>946</v>
-      </c>
-      <c r="D140" t="s">
-        <v>926</v>
+        <v>458</v>
       </c>
       <c r="E140" t="s">
-        <v>947</v>
+        <v>464</v>
       </c>
       <c r="F140" t="s">
-        <v>994</v>
+        <v>459</v>
       </c>
       <c r="G140" t="s">
-        <v>959</v>
+        <v>460</v>
       </c>
       <c r="H140" t="s">
-        <v>959</v>
+        <v>461</v>
       </c>
       <c r="I140" t="s">
-        <v>960</v>
-      </c>
-      <c r="J140" s="1" t="s">
-        <v>948</v>
+        <v>465</v>
+      </c>
+      <c r="J140" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8668,52 +8743,80 @@
         <v>1026</v>
       </c>
       <c r="B141" t="s">
-        <v>950</v>
+        <v>533</v>
       </c>
       <c r="C141" t="s">
-        <v>949</v>
+        <v>491</v>
+      </c>
+      <c r="D141" t="s">
+        <v>492</v>
+      </c>
+      <c r="E141" t="s">
+        <v>490</v>
+      </c>
+      <c r="F141" t="s">
+        <v>493</v>
       </c>
       <c r="G141" t="s">
-        <v>961</v>
+        <v>494</v>
       </c>
       <c r="H141" t="s">
-        <v>962</v>
-      </c>
-      <c r="J141" s="1"/>
+        <v>495</v>
+      </c>
+      <c r="I141" t="s">
+        <v>496</v>
+      </c>
+      <c r="J141" t="s">
+        <v>497</v>
+      </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
         <v>1026</v>
       </c>
       <c r="B142" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="C142" t="s">
-        <v>963</v>
+        <v>946</v>
+      </c>
+      <c r="D142" t="s">
+        <v>926</v>
+      </c>
+      <c r="E142" t="s">
+        <v>947</v>
+      </c>
+      <c r="F142" t="s">
+        <v>994</v>
       </c>
       <c r="G142" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="H142" t="s">
-        <v>965</v>
-      </c>
-      <c r="J142" s="1"/>
+        <v>959</v>
+      </c>
+      <c r="I142" t="s">
+        <v>960</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
         <v>1026</v>
       </c>
       <c r="B143" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C143" t="s">
-        <v>966</v>
+        <v>949</v>
       </c>
       <c r="G143" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="H143" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="J143" s="1"/>
     </row>
@@ -8722,16 +8825,16 @@
         <v>1026</v>
       </c>
       <c r="B144" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C144" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="G144" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="H144" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="J144" s="1"/>
     </row>
@@ -8740,13 +8843,16 @@
         <v>1026</v>
       </c>
       <c r="B145" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C145" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="G145" t="s">
-        <v>973</v>
+        <v>967</v>
+      </c>
+      <c r="H145" t="s">
+        <v>968</v>
       </c>
       <c r="J145" s="1"/>
     </row>
@@ -8755,16 +8861,16 @@
         <v>1026</v>
       </c>
       <c r="B146" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C146" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="G146" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="H146" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="J146" s="1"/>
     </row>
@@ -8773,16 +8879,13 @@
         <v>1026</v>
       </c>
       <c r="B147" t="s">
-        <v>977</v>
+        <v>954</v>
       </c>
       <c r="C147" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="G147" t="s">
-        <v>979</v>
-      </c>
-      <c r="H147" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="J147" s="1"/>
     </row>
@@ -8791,16 +8894,16 @@
         <v>1026</v>
       </c>
       <c r="B148" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C148" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="G148" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="H148" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="J148" s="1"/>
     </row>
@@ -8809,16 +8912,16 @@
         <v>1026</v>
       </c>
       <c r="B149" t="s">
-        <v>957</v>
+        <v>977</v>
       </c>
       <c r="C149" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="G149" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="H149" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="J149" s="1"/>
     </row>
@@ -8827,64 +8930,36 @@
         <v>1026</v>
       </c>
       <c r="B150" t="s">
-        <v>864</v>
+        <v>956</v>
       </c>
       <c r="C150" t="s">
-        <v>260</v>
-      </c>
-      <c r="D150" t="s">
-        <v>261</v>
-      </c>
-      <c r="E150" t="s">
-        <v>259</v>
-      </c>
-      <c r="F150" t="s">
-        <v>262</v>
+        <v>981</v>
       </c>
       <c r="G150" t="s">
-        <v>263</v>
+        <v>982</v>
       </c>
       <c r="H150" t="s">
-        <v>264</v>
-      </c>
-      <c r="I150" t="s">
-        <v>265</v>
-      </c>
-      <c r="J150" t="s">
-        <v>266</v>
-      </c>
+        <v>983</v>
+      </c>
+      <c r="J150" s="1"/>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" t="s">
         <v>1026</v>
       </c>
       <c r="B151" t="s">
-        <v>864</v>
+        <v>957</v>
       </c>
       <c r="C151" t="s">
-        <v>534</v>
-      </c>
-      <c r="D151" t="s">
-        <v>535</v>
-      </c>
-      <c r="E151" t="s">
-        <v>536</v>
-      </c>
-      <c r="F151" t="s">
-        <v>833</v>
+        <v>984</v>
       </c>
       <c r="G151" t="s">
-        <v>537</v>
+        <v>985</v>
       </c>
       <c r="H151" t="s">
-        <v>538</v>
-      </c>
-      <c r="I151" t="s">
-        <v>539</v>
-      </c>
-      <c r="J151" t="s">
-        <v>540</v>
-      </c>
+        <v>986</v>
+      </c>
+      <c r="J151" s="1"/>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
@@ -8894,28 +8969,28 @@
         <v>864</v>
       </c>
       <c r="C152" t="s">
-        <v>541</v>
+        <v>260</v>
       </c>
       <c r="D152" t="s">
-        <v>542</v>
+        <v>261</v>
       </c>
       <c r="E152" t="s">
-        <v>543</v>
+        <v>259</v>
       </c>
       <c r="F152" t="s">
-        <v>834</v>
+        <v>262</v>
       </c>
       <c r="G152" t="s">
-        <v>544</v>
+        <v>263</v>
       </c>
       <c r="H152" t="s">
-        <v>545</v>
+        <v>264</v>
       </c>
       <c r="I152" t="s">
-        <v>546</v>
+        <v>265</v>
       </c>
       <c r="J152" t="s">
-        <v>547</v>
+        <v>266</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8926,86 +9001,89 @@
         <v>864</v>
       </c>
       <c r="C153" t="s">
-        <v>164</v>
+        <v>534</v>
       </c>
       <c r="D153" t="s">
-        <v>165</v>
+        <v>535</v>
       </c>
       <c r="E153" t="s">
-        <v>163</v>
+        <v>536</v>
       </c>
       <c r="F153" t="s">
-        <v>166</v>
+        <v>833</v>
       </c>
       <c r="G153" t="s">
-        <v>167</v>
+        <v>537</v>
       </c>
       <c r="H153" t="s">
-        <v>168</v>
+        <v>538</v>
+      </c>
+      <c r="I153" t="s">
+        <v>539</v>
       </c>
       <c r="J153" t="s">
-        <v>169</v>
+        <v>540</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="B154" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="C154" t="s">
-        <v>115</v>
+        <v>541</v>
       </c>
       <c r="D154" t="s">
-        <v>825</v>
+        <v>542</v>
       </c>
       <c r="E154" t="s">
-        <v>824</v>
+        <v>543</v>
       </c>
       <c r="F154" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="G154" t="s">
-        <v>827</v>
+        <v>544</v>
       </c>
       <c r="H154" t="s">
-        <v>119</v>
+        <v>545</v>
+      </c>
+      <c r="I154" t="s">
+        <v>546</v>
       </c>
       <c r="J154" t="s">
-        <v>120</v>
+        <v>547</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="B155" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="C155" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="D155" t="s">
-        <v>609</v>
+        <v>165</v>
       </c>
       <c r="E155" t="s">
-        <v>610</v>
+        <v>163</v>
       </c>
       <c r="F155" t="s">
-        <v>842</v>
+        <v>166</v>
       </c>
       <c r="G155" t="s">
-        <v>611</v>
+        <v>167</v>
       </c>
       <c r="H155" t="s">
-        <v>119</v>
-      </c>
-      <c r="I155" t="s">
-        <v>612</v>
+        <v>168</v>
       </c>
       <c r="J155" t="s">
-        <v>613</v>
+        <v>169</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9019,16 +9097,22 @@
         <v>115</v>
       </c>
       <c r="D156" t="s">
-        <v>614</v>
+        <v>825</v>
       </c>
       <c r="E156" t="s">
-        <v>615</v>
+        <v>824</v>
       </c>
       <c r="F156" t="s">
-        <v>843</v>
+        <v>826</v>
       </c>
       <c r="G156" t="s">
-        <v>616</v>
+        <v>827</v>
+      </c>
+      <c r="H156" t="s">
+        <v>119</v>
+      </c>
+      <c r="J156" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9042,25 +9126,25 @@
         <v>115</v>
       </c>
       <c r="D157" t="s">
-        <v>535</v>
+        <v>609</v>
       </c>
       <c r="E157" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="F157" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G157" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="H157" t="s">
-        <v>618</v>
+        <v>119</v>
       </c>
       <c r="I157" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="J157" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9074,25 +9158,16 @@
         <v>115</v>
       </c>
       <c r="D158" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="E158" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="F158" t="s">
         <v>843</v>
       </c>
       <c r="G158" t="s">
         <v>616</v>
-      </c>
-      <c r="H158" t="s">
-        <v>618</v>
-      </c>
-      <c r="I158" t="s">
-        <v>623</v>
-      </c>
-      <c r="J158" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9106,25 +9181,25 @@
         <v>115</v>
       </c>
       <c r="D159" t="s">
-        <v>625</v>
+        <v>535</v>
       </c>
       <c r="E159" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="F159" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G159" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="H159" t="s">
-        <v>119</v>
+        <v>618</v>
       </c>
       <c r="I159" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="J159" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9138,10 +9213,10 @@
         <v>115</v>
       </c>
       <c r="D160" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="E160" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="F160" t="s">
         <v>843</v>
@@ -9153,10 +9228,10 @@
         <v>618</v>
       </c>
       <c r="I160" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="J160" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9170,22 +9245,25 @@
         <v>115</v>
       </c>
       <c r="D161" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="E161" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="F161" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="G161" t="s">
-        <v>635</v>
+        <v>611</v>
+      </c>
+      <c r="H161" t="s">
+        <v>119</v>
       </c>
       <c r="I161" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="J161" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9199,22 +9277,25 @@
         <v>115</v>
       </c>
       <c r="D162" t="s">
-        <v>317</v>
+        <v>629</v>
       </c>
       <c r="E162" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="F162" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G162" t="s">
-        <v>635</v>
+        <v>616</v>
+      </c>
+      <c r="H162" t="s">
+        <v>618</v>
       </c>
       <c r="I162" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="J162" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9228,25 +9309,22 @@
         <v>115</v>
       </c>
       <c r="D163" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="E163" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="F163" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="G163" t="s">
-        <v>642</v>
-      </c>
-      <c r="H163" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="I163" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="J163" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9254,25 +9332,28 @@
         <v>1022</v>
       </c>
       <c r="B164" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
       <c r="C164" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="D164" t="s">
-        <v>10</v>
+        <v>317</v>
       </c>
       <c r="E164" t="s">
-        <v>8</v>
+        <v>638</v>
       </c>
       <c r="F164" t="s">
-        <v>11</v>
+        <v>844</v>
       </c>
       <c r="G164" t="s">
-        <v>12</v>
-      </c>
-      <c r="H164" t="s">
-        <v>13</v>
+        <v>635</v>
+      </c>
+      <c r="I164" t="s">
+        <v>639</v>
+      </c>
+      <c r="J164" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9280,31 +9361,31 @@
         <v>1022</v>
       </c>
       <c r="B165" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
       <c r="C165" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="D165" t="s">
-        <v>16</v>
+        <v>621</v>
       </c>
       <c r="E165" t="s">
-        <v>14</v>
+        <v>641</v>
       </c>
       <c r="F165" t="s">
-        <v>17</v>
+        <v>842</v>
       </c>
       <c r="G165" t="s">
-        <v>18</v>
+        <v>642</v>
       </c>
       <c r="H165" t="s">
-        <v>19</v>
+        <v>643</v>
       </c>
       <c r="I165" t="s">
-        <v>20</v>
+        <v>644</v>
       </c>
       <c r="J165" t="s">
-        <v>21</v>
+        <v>645</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9315,28 +9396,22 @@
         <v>880</v>
       </c>
       <c r="C166" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D166" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E166" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F166" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G166" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H166" t="s">
-        <v>19</v>
-      </c>
-      <c r="I166" t="s">
-        <v>24</v>
-      </c>
-      <c r="J166" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9350,25 +9425,25 @@
         <v>15</v>
       </c>
       <c r="D167" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E167" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F167" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G167" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H167" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I167" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J167" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9382,25 +9457,25 @@
         <v>15</v>
       </c>
       <c r="D168" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E168" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F168" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G168" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H168" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I168" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J168" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9414,10 +9489,10 @@
         <v>15</v>
       </c>
       <c r="D169" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E169" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F169" t="s">
         <v>28</v>
@@ -9429,10 +9504,10 @@
         <v>30</v>
       </c>
       <c r="I169" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="J169" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9443,59 +9518,89 @@
         <v>880</v>
       </c>
       <c r="C170" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="D170" t="s">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="E170" t="s">
-        <v>114</v>
+        <v>33</v>
       </c>
       <c r="F170" t="s">
-        <v>117</v>
+        <v>28</v>
       </c>
       <c r="G170" t="s">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="H170" t="s">
-        <v>119</v>
+        <v>30</v>
+      </c>
+      <c r="I170" t="s">
+        <v>35</v>
       </c>
       <c r="J170" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" t="s">
-        <v>888</v>
+        <v>1022</v>
+      </c>
+      <c r="B171" t="s">
+        <v>880</v>
       </c>
       <c r="C171" t="s">
-        <v>913</v>
+        <v>15</v>
       </c>
       <c r="D171" t="s">
-        <v>889</v>
+        <v>38</v>
       </c>
       <c r="E171" t="s">
-        <v>893</v>
+        <v>37</v>
+      </c>
+      <c r="F171" t="s">
+        <v>28</v>
+      </c>
+      <c r="G171" t="s">
+        <v>29</v>
+      </c>
+      <c r="H171" t="s">
+        <v>30</v>
       </c>
       <c r="I171" t="s">
-        <v>904</v>
+        <v>39</v>
+      </c>
+      <c r="J171" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" t="s">
-        <v>888</v>
+        <v>1022</v>
+      </c>
+      <c r="B172" t="s">
+        <v>880</v>
       </c>
       <c r="C172" t="s">
-        <v>913</v>
+        <v>115</v>
       </c>
       <c r="D172" t="s">
-        <v>890</v>
+        <v>116</v>
       </c>
       <c r="E172" t="s">
-        <v>894</v>
-      </c>
-      <c r="I172" t="s">
-        <v>905</v>
+        <v>114</v>
+      </c>
+      <c r="F172" t="s">
+        <v>117</v>
+      </c>
+      <c r="G172" t="s">
+        <v>118</v>
+      </c>
+      <c r="H172" t="s">
+        <v>119</v>
+      </c>
+      <c r="J172" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9506,13 +9611,13 @@
         <v>913</v>
       </c>
       <c r="D173" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="E173" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="I173" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9523,13 +9628,13 @@
         <v>913</v>
       </c>
       <c r="D174" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="E174" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="I174" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9540,13 +9645,13 @@
         <v>913</v>
       </c>
       <c r="D175" t="s">
-        <v>902</v>
+        <v>891</v>
       </c>
       <c r="E175" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="I175" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9557,13 +9662,13 @@
         <v>913</v>
       </c>
       <c r="D176" t="s">
-        <v>902</v>
+        <v>892</v>
       </c>
       <c r="E176" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="I176" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -9574,13 +9679,13 @@
         <v>913</v>
       </c>
       <c r="D177" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E177" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="I177" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -9591,13 +9696,13 @@
         <v>913</v>
       </c>
       <c r="D178" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E178" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="I178" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -9611,28 +9716,117 @@
         <v>903</v>
       </c>
       <c r="E179" t="s">
+        <v>899</v>
+      </c>
+      <c r="I179" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A180" t="s">
+        <v>888</v>
+      </c>
+      <c r="C180" t="s">
+        <v>913</v>
+      </c>
+      <c r="D180" t="s">
+        <v>903</v>
+      </c>
+      <c r="E180" t="s">
+        <v>900</v>
+      </c>
+      <c r="I180" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A181" t="s">
+        <v>888</v>
+      </c>
+      <c r="C181" t="s">
+        <v>913</v>
+      </c>
+      <c r="D181" t="s">
+        <v>903</v>
+      </c>
+      <c r="E181" t="s">
         <v>901</v>
       </c>
-      <c r="I179" t="s">
+      <c r="I181" t="s">
         <v>912</v>
       </c>
     </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A182" t="s">
+        <v>888</v>
+      </c>
+      <c r="C182" t="s">
+        <v>913</v>
+      </c>
+      <c r="D182" t="s">
+        <v>903</v>
+      </c>
+      <c r="E182" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I182" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A183" t="s">
+        <v>888</v>
+      </c>
+      <c r="C183" t="s">
+        <v>913</v>
+      </c>
+      <c r="D183" t="s">
+        <v>903</v>
+      </c>
+      <c r="E183" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I183" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A184" t="s">
+        <v>888</v>
+      </c>
+      <c r="C184" t="s">
+        <v>913</v>
+      </c>
+      <c r="D184" t="s">
+        <v>903</v>
+      </c>
+      <c r="E184" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I184" t="s">
+        <v>1048</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A43:J170">
-    <sortCondition ref="A43:A170"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A43:J172">
+    <sortCondition ref="A43:A172"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="J42" r:id="rId1" xr:uid="{8A5F4D1B-75DE-4D67-8A11-0F1BAE0155F6}"/>
     <hyperlink ref="J87" r:id="rId2" xr:uid="{04B79727-E872-4B92-B9FF-E52CDD567289}"/>
     <hyperlink ref="J88" r:id="rId3" xr:uid="{58FC3E9B-DA5E-47AE-A0FA-48744DC7E69C}"/>
-    <hyperlink ref="J119" r:id="rId4" xr:uid="{0CDDE2B0-9A66-4763-82CA-FB9054DBD36D}"/>
-    <hyperlink ref="J140" r:id="rId5" xr:uid="{D959C86A-275E-4D89-91FD-60DBE69A6EE8}"/>
+    <hyperlink ref="J120" r:id="rId4" xr:uid="{0CDDE2B0-9A66-4763-82CA-FB9054DBD36D}"/>
+    <hyperlink ref="J142" r:id="rId5" xr:uid="{D959C86A-275E-4D89-91FD-60DBE69A6EE8}"/>
     <hyperlink ref="J82" r:id="rId6" xr:uid="{AE797D3F-4BC0-45F7-BAAF-49AAE05332D6}"/>
-    <hyperlink ref="J118" r:id="rId7" xr:uid="{E353EA49-C20B-4A50-9E3E-3B8FC192D763}"/>
+    <hyperlink ref="J119" r:id="rId7" xr:uid="{E353EA49-C20B-4A50-9E3E-3B8FC192D763}"/>
     <hyperlink ref="J100" r:id="rId8" xr:uid="{A98CDD58-6463-49F3-9952-BC0BEE6FEAA2}"/>
-    <hyperlink ref="J121" r:id="rId9" xr:uid="{AB76B266-A10F-4CFC-8443-AA6443702A5B}"/>
+    <hyperlink ref="J123" r:id="rId9" xr:uid="{AB76B266-A10F-4CFC-8443-AA6443702A5B}"/>
+    <hyperlink ref="J122" r:id="rId10" xr:uid="{A88927C8-9E1E-434F-A07F-E27E8344EA27}"/>
+    <hyperlink ref="J116" r:id="rId11" xr:uid="{A3DB0C85-A479-46A9-8A6D-D812158F6817}"/>
+    <hyperlink ref="J117" r:id="rId12" xr:uid="{492D0E6B-9BAE-4D34-9274-D000647E8A16}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kiuchi-my.sharepoint.com/personal/isozaki_kiuchi_co_jp/Documents/fmsf-phone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="842" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6835AA75-F783-4CD3-B043-31EE5AFDA4F8}"/>
+  <xr:revisionPtr revIDLastSave="843" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{857474ED-1FD6-4EB1-814C-A8E22AC0EE30}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="1055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="1054">
   <si>
     <t>氏名</t>
   </si>
@@ -4034,16 +4034,6 @@
       <t>シア</t>
     </rPh>
     <rPh sb="3" eb="5">
-      <t>コウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>躯体工事</t>
-    <rPh sb="0" eb="2">
-      <t>クタイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
       <t>コウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -7071,7 +7061,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B86" t="s">
         <v>923</v>
@@ -7097,7 +7087,7 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B87" t="s">
         <v>914</v>
@@ -7129,7 +7119,7 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B88" t="s">
         <v>914</v>
@@ -7522,10 +7512,10 @@
         <v>183</v>
       </c>
       <c r="D100" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E100" t="s">
         <v>1032</v>
-      </c>
-      <c r="E100" t="s">
-        <v>1033</v>
       </c>
       <c r="F100" t="s">
         <v>185</v>
@@ -7537,10 +7527,10 @@
         <v>187</v>
       </c>
       <c r="I100" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J100" s="3" t="s">
         <v>1034</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8005,7 +7995,7 @@
         <v>1011</v>
       </c>
       <c r="E116" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F116" t="s">
         <v>1012</v>
@@ -8017,7 +8007,7 @@
         <v>1014</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8031,7 +8021,7 @@
         <v>1011</v>
       </c>
       <c r="E117" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F117" t="s">
         <v>1012</v>
@@ -8043,7 +8033,7 @@
         <v>1014</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8141,22 +8131,22 @@
         <v>1024</v>
       </c>
       <c r="B121" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C121" t="s">
         <v>1027</v>
-      </c>
-      <c r="C121" t="s">
-        <v>1028</v>
       </c>
       <c r="D121" t="s">
         <v>926</v>
       </c>
       <c r="E121" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F121" t="s">
         <v>1029</v>
       </c>
-      <c r="F121" t="s">
+      <c r="G121" t="s">
         <v>1030</v>
-      </c>
-      <c r="G121" t="s">
-        <v>1031</v>
       </c>
       <c r="J121" s="1"/>
     </row>
@@ -8165,25 +8155,25 @@
         <v>1024</v>
       </c>
       <c r="B122" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C122" t="s">
         <v>1036</v>
       </c>
-      <c r="C122" t="s">
-        <v>1037</v>
-      </c>
       <c r="E122" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F122" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G122" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="J122" s="1" t="s">
         <v>1043</v>
-      </c>
-      <c r="F122" t="s">
-        <v>1039</v>
-      </c>
-      <c r="G122" t="s">
-        <v>1040</v>
-      </c>
-      <c r="H122" s="4" t="s">
-        <v>1041</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8191,30 +8181,30 @@
         <v>1024</v>
       </c>
       <c r="B123" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C123" t="s">
         <v>1036</v>
       </c>
-      <c r="C123" t="s">
+      <c r="E123" t="s">
         <v>1037</v>
       </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
         <v>1038</v>
       </c>
-      <c r="F123" t="s">
+      <c r="G123" t="s">
         <v>1039</v>
       </c>
-      <c r="G123" t="s">
+      <c r="H123" s="4" t="s">
         <v>1040</v>
       </c>
-      <c r="H123" s="4" t="s">
+      <c r="J123" s="1" t="s">
         <v>1041</v>
-      </c>
-      <c r="J123" s="1" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B124" t="s">
         <v>518</v>
@@ -8246,7 +8236,7 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B125" t="s">
         <v>518</v>
@@ -8278,7 +8268,7 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B126" t="s">
         <v>874</v>
@@ -8310,7 +8300,7 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B127" t="s">
         <v>516</v>
@@ -8342,7 +8332,7 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B128" t="s">
         <v>514</v>
@@ -8368,7 +8358,7 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B129" t="s">
         <v>514</v>
@@ -8397,7 +8387,7 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B130" t="s">
         <v>514</v>
@@ -8429,7 +8419,7 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B131" t="s">
         <v>514</v>
@@ -8458,7 +8448,7 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B132" t="s">
         <v>514</v>
@@ -8490,7 +8480,7 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B133" t="s">
         <v>529</v>
@@ -8519,7 +8509,7 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B134" t="s">
         <v>529</v>
@@ -8551,7 +8541,7 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B135" t="s">
         <v>501</v>
@@ -8583,7 +8573,7 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B136" t="s">
         <v>512</v>
@@ -8615,7 +8605,7 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B137" t="s">
         <v>870</v>
@@ -8647,7 +8637,7 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B138" t="s">
         <v>870</v>
@@ -8679,7 +8669,7 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B139" t="s">
         <v>530</v>
@@ -8711,7 +8701,7 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B140" t="s">
         <v>530</v>
@@ -8740,7 +8730,7 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B141" t="s">
         <v>533</v>
@@ -8772,7 +8762,7 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B142" t="s">
         <v>958</v>
@@ -8804,7 +8794,7 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B143" t="s">
         <v>950</v>
@@ -8822,7 +8812,7 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B144" t="s">
         <v>951</v>
@@ -8840,7 +8830,7 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B145" t="s">
         <v>952</v>
@@ -8858,7 +8848,7 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B146" t="s">
         <v>953</v>
@@ -8876,7 +8866,7 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B147" t="s">
         <v>954</v>
@@ -8891,7 +8881,7 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B148" t="s">
         <v>955</v>
@@ -8909,7 +8899,7 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B149" t="s">
         <v>977</v>
@@ -8927,7 +8917,7 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B150" t="s">
         <v>956</v>
@@ -8945,7 +8935,7 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B151" t="s">
         <v>957</v>
@@ -8963,7 +8953,7 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B152" t="s">
         <v>864</v>
@@ -8995,7 +8985,7 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B153" t="s">
         <v>864</v>
@@ -9027,7 +9017,7 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B154" t="s">
         <v>864</v>
@@ -9059,7 +9049,7 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B155" t="s">
         <v>864</v>
@@ -9767,10 +9757,10 @@
         <v>903</v>
       </c>
       <c r="E182" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I182" t="s">
         <v>1045</v>
-      </c>
-      <c r="I182" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -9784,10 +9774,10 @@
         <v>903</v>
       </c>
       <c r="E183" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="I183" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -9801,10 +9791,10 @@
         <v>903</v>
       </c>
       <c r="E184" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="I184" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kiuchi-my.sharepoint.com/personal/isozaki_kiuchi_co_jp/Documents/fmsf-phone/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kiuchi-my.sharepoint.com/personal/isozaki_kiuchi_co_jp/Documents/FMSF-Direct-line/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="843" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{857474ED-1FD6-4EB1-814C-A8E22AC0EE30}"/>
+  <xr:revisionPtr revIDLastSave="848" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9311776B-EB00-47F4-9764-E61527219151}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="1058">
   <si>
     <t>氏名</t>
   </si>
@@ -4248,6 +4248,34 @@
   </si>
   <si>
     <t>awata@ys-h.co.jp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現場事務員</t>
+    <rPh sb="0" eb="5">
+      <t>ゲンバジムイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事務</t>
+    <rPh sb="0" eb="2">
+      <t>ジム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>磯﨑 艶子</t>
+    <rPh sb="0" eb="2">
+      <t>イソザキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ツヤコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>080-2605-5075</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4359,10 +4387,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4682,7 +4706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED22340-6398-430F-AD0F-E88DFD8C2F52}">
-  <dimension ref="A1:J184"/>
+  <dimension ref="A1:J185"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="8.9140625" customWidth="1"/>
@@ -9795,6 +9819,23 @@
       </c>
       <c r="I184" t="s">
         <v>1047</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A185" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C185" t="s">
+        <v>913</v>
+      </c>
+      <c r="D185" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E185" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I185" t="s">
+        <v>1057</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kiuchi-my.sharepoint.com/personal/isozaki_kiuchi_co_jp/Documents/FMSF-Direct-line/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="848" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9311776B-EB00-47F4-9764-E61527219151}"/>
+  <xr:revisionPtr revIDLastSave="850" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{100A0465-9C33-40FF-AB9A-CA79DD370F80}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="1054">
   <si>
     <t>氏名</t>
   </si>
@@ -4248,34 +4248,6 @@
   </si>
   <si>
     <t>awata@ys-h.co.jp</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>現場事務員</t>
-    <rPh sb="0" eb="5">
-      <t>ゲンバジムイン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>事務</t>
-    <rPh sb="0" eb="2">
-      <t>ジム</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>磯﨑 艶子</t>
-    <rPh sb="0" eb="2">
-      <t>イソザキ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ツヤコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>080-2605-5075</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4387,6 +4359,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4706,7 +4682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED22340-6398-430F-AD0F-E88DFD8C2F52}">
-  <dimension ref="A1:J185"/>
+  <dimension ref="A1:J184"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="8.9140625" customWidth="1"/>
@@ -9819,23 +9795,6 @@
       </c>
       <c r="I184" t="s">
         <v>1047</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A185" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C185" t="s">
-        <v>913</v>
-      </c>
-      <c r="D185" t="s">
-        <v>1055</v>
-      </c>
-      <c r="E185" t="s">
-        <v>1056</v>
-      </c>
-      <c r="I185" t="s">
-        <v>1057</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kiuchi-my.sharepoint.com/personal/isozaki_kiuchi_co_jp/Documents/FMSF-Direct-line/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="850" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{100A0465-9C33-40FF-AB9A-CA79DD370F80}"/>
+  <xr:revisionPtr revIDLastSave="851" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6F63A65-3910-451A-B9E3-D27059AFFA83}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
   </bookViews>
@@ -4686,7 +4686,7 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="8.9140625" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
     <col min="5" max="5" width="15.08203125" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kiuchi-my.sharepoint.com/personal/isozaki_kiuchi_co_jp/Documents/FMSF-Direct-line/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="848" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9311776B-EB00-47F4-9764-E61527219151}"/>
+  <xr:revisionPtr revIDLastSave="853" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6989B90-6A57-4B70-8A28-D34CAAA6E246}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="1054">
   <si>
     <t>氏名</t>
   </si>
@@ -4248,34 +4248,6 @@
   </si>
   <si>
     <t>awata@ys-h.co.jp</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>現場事務員</t>
-    <rPh sb="0" eb="5">
-      <t>ゲンバジムイン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>事務</t>
-    <rPh sb="0" eb="2">
-      <t>ジム</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>磯﨑 艶子</t>
-    <rPh sb="0" eb="2">
-      <t>イソザキ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ツヤコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>080-2605-5075</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4387,6 +4359,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4706,11 +4682,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED22340-6398-430F-AD0F-E88DFD8C2F52}">
-  <dimension ref="A1:J185"/>
+  <dimension ref="A1:J184"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="8.9140625" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
     <col min="5" max="5" width="15.08203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9819,23 +9795,6 @@
       </c>
       <c r="I184" t="s">
         <v>1047</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A185" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C185" t="s">
-        <v>913</v>
-      </c>
-      <c r="D185" t="s">
-        <v>1055</v>
-      </c>
-      <c r="E185" t="s">
-        <v>1056</v>
-      </c>
-      <c r="I185" t="s">
-        <v>1057</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kiuchi-my.sharepoint.com/personal/isozaki_kiuchi_co_jp/Documents/FMSF-Direct-line/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="855" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{850699EF-3DE7-45F0-BA15-B843B1519762}"/>
+  <xr:revisionPtr revIDLastSave="857" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29A1AA21-5222-4729-B2A3-DB4EB3D505B1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
   </bookViews>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kiuchi-my.sharepoint.com/personal/isozaki_kiuchi_co_jp/Documents/FMSF-Direct-line/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="857" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29A1AA21-5222-4729-B2A3-DB4EB3D505B1}"/>
+  <xr:revisionPtr revIDLastSave="862" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9958DD9A-E70D-4B28-8A8F-AFBEB6EA0F70}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="1058">
   <si>
     <t>氏名</t>
   </si>
@@ -4248,6 +4248,37 @@
   </si>
   <si>
     <t>awata@ys-h.co.jp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現場事務員</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンバ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ジムイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事務</t>
+    <rPh sb="0" eb="2">
+      <t>ジム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>磯崎 艶子</t>
+    <rPh sb="0" eb="2">
+      <t>イソザキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ツヤコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>080-2605-5075</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4682,7 +4713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED22340-6398-430F-AD0F-E88DFD8C2F52}">
-  <dimension ref="A1:J184"/>
+  <dimension ref="A1:J185"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="8.9140625" customWidth="1"/>
@@ -9795,6 +9826,23 @@
       </c>
       <c r="I184" t="s">
         <v>1047</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A185" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C185" t="s">
+        <v>913</v>
+      </c>
+      <c r="D185" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E185" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I185" t="s">
+        <v>1057</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kiuchi-my.sharepoint.com/personal/isozaki_kiuchi_co_jp/Documents/FMSF-Direct-line/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="862" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9958DD9A-E70D-4B28-8A8F-AFBEB6EA0F70}"/>
+  <xr:revisionPtr revIDLastSave="867" documentId="8_{F85A9A68-4E93-4088-9ED5-1903CFFF7F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{369C4320-1810-4FF4-8CB0-62908D35CC1A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D411879D-5147-439A-8907-627E102D99C2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="1060">
   <si>
     <t>氏名</t>
   </si>
@@ -4279,6 +4279,17 @@
   </si>
   <si>
     <t>080-2605-5075</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鈴木　りゅうすけ</t>
+    <rPh sb="0" eb="2">
+      <t>スズキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>080-2601-6593</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4713,7 +4724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED22340-6398-430F-AD0F-E88DFD8C2F52}">
-  <dimension ref="A1:J185"/>
+  <dimension ref="A1:J186"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="8.9140625" customWidth="1"/>
@@ -8514,28 +8525,25 @@
         <v>1025</v>
       </c>
       <c r="B133" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="C133" t="s">
-        <v>584</v>
-      </c>
-      <c r="D133" t="s">
-        <v>585</v>
+        <v>284</v>
+      </c>
+      <c r="E133" t="s">
+        <v>1058</v>
       </c>
       <c r="F133" t="s">
-        <v>586</v>
+        <v>863</v>
       </c>
       <c r="G133" t="s">
-        <v>587</v>
+        <v>801</v>
       </c>
       <c r="H133" t="s">
-        <v>588</v>
+        <v>802</v>
       </c>
       <c r="I133" t="s">
-        <v>589</v>
-      </c>
-      <c r="J133" t="s">
-        <v>590</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8546,28 +8554,25 @@
         <v>529</v>
       </c>
       <c r="C134" t="s">
-        <v>443</v>
+        <v>584</v>
       </c>
       <c r="D134" t="s">
-        <v>444</v>
-      </c>
-      <c r="E134" t="s">
-        <v>442</v>
+        <v>585</v>
       </c>
       <c r="F134" t="s">
-        <v>445</v>
+        <v>586</v>
       </c>
       <c r="G134" t="s">
-        <v>446</v>
+        <v>587</v>
       </c>
       <c r="H134" t="s">
-        <v>447</v>
+        <v>588</v>
       </c>
       <c r="I134" t="s">
-        <v>448</v>
+        <v>589</v>
       </c>
       <c r="J134" t="s">
-        <v>449</v>
+        <v>590</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8575,31 +8580,31 @@
         <v>1025</v>
       </c>
       <c r="B135" t="s">
-        <v>501</v>
+        <v>529</v>
       </c>
       <c r="C135" t="s">
-        <v>138</v>
+        <v>443</v>
       </c>
       <c r="D135" t="s">
-        <v>139</v>
+        <v>444</v>
       </c>
       <c r="E135" t="s">
-        <v>137</v>
+        <v>442</v>
       </c>
       <c r="F135" t="s">
-        <v>140</v>
+        <v>445</v>
       </c>
       <c r="G135" t="s">
-        <v>141</v>
+        <v>446</v>
       </c>
       <c r="H135" t="s">
-        <v>142</v>
+        <v>447</v>
       </c>
       <c r="I135" t="s">
-        <v>143</v>
+        <v>448</v>
       </c>
       <c r="J135" t="s">
-        <v>144</v>
+        <v>449</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8607,31 +8612,31 @@
         <v>1025</v>
       </c>
       <c r="B136" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="C136" t="s">
-        <v>254</v>
+        <v>138</v>
       </c>
       <c r="D136" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="E136" t="s">
-        <v>253</v>
+        <v>137</v>
       </c>
       <c r="F136" t="s">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="G136" t="s">
-        <v>256</v>
+        <v>141</v>
       </c>
       <c r="H136" t="s">
-        <v>256</v>
+        <v>142</v>
       </c>
       <c r="I136" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="J136" t="s">
-        <v>258</v>
+        <v>144</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8639,31 +8644,31 @@
         <v>1025</v>
       </c>
       <c r="B137" t="s">
-        <v>870</v>
+        <v>512</v>
       </c>
       <c r="C137" t="s">
-        <v>597</v>
+        <v>254</v>
       </c>
       <c r="D137" t="s">
-        <v>598</v>
+        <v>165</v>
       </c>
       <c r="E137" t="s">
-        <v>599</v>
+        <v>253</v>
       </c>
       <c r="F137" t="s">
-        <v>841</v>
+        <v>255</v>
       </c>
       <c r="G137" t="s">
-        <v>600</v>
+        <v>256</v>
       </c>
       <c r="H137" t="s">
-        <v>601</v>
+        <v>256</v>
       </c>
       <c r="I137" t="s">
-        <v>602</v>
+        <v>257</v>
       </c>
       <c r="J137" t="s">
-        <v>603</v>
+        <v>258</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8677,10 +8682,10 @@
         <v>597</v>
       </c>
       <c r="D138" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="E138" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="F138" t="s">
         <v>841</v>
@@ -8692,10 +8697,10 @@
         <v>601</v>
       </c>
       <c r="I138" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="J138" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8703,31 +8708,31 @@
         <v>1025</v>
       </c>
       <c r="B139" t="s">
-        <v>530</v>
+        <v>870</v>
       </c>
       <c r="C139" t="s">
-        <v>458</v>
+        <v>597</v>
       </c>
       <c r="D139" t="s">
-        <v>165</v>
+        <v>604</v>
       </c>
       <c r="E139" t="s">
-        <v>457</v>
+        <v>605</v>
       </c>
       <c r="F139" t="s">
-        <v>459</v>
+        <v>841</v>
       </c>
       <c r="G139" t="s">
-        <v>460</v>
+        <v>600</v>
       </c>
       <c r="H139" t="s">
-        <v>461</v>
+        <v>601</v>
       </c>
       <c r="I139" t="s">
-        <v>462</v>
+        <v>606</v>
       </c>
       <c r="J139" t="s">
-        <v>463</v>
+        <v>607</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8740,8 +8745,11 @@
       <c r="C140" t="s">
         <v>458</v>
       </c>
+      <c r="D140" t="s">
+        <v>165</v>
+      </c>
       <c r="E140" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="F140" t="s">
         <v>459</v>
@@ -8753,7 +8761,7 @@
         <v>461</v>
       </c>
       <c r="I140" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="J140" t="s">
         <v>463</v>
@@ -8764,31 +8772,28 @@
         <v>1025</v>
       </c>
       <c r="B141" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C141" t="s">
-        <v>491</v>
-      </c>
-      <c r="D141" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="E141" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
       <c r="F141" t="s">
-        <v>493</v>
+        <v>459</v>
       </c>
       <c r="G141" t="s">
-        <v>494</v>
+        <v>460</v>
       </c>
       <c r="H141" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="I141" t="s">
-        <v>496</v>
+        <v>465</v>
       </c>
       <c r="J141" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8796,31 +8801,31 @@
         <v>1025</v>
       </c>
       <c r="B142" t="s">
-        <v>958</v>
+        <v>533</v>
       </c>
       <c r="C142" t="s">
-        <v>946</v>
+        <v>491</v>
       </c>
       <c r="D142" t="s">
-        <v>926</v>
+        <v>492</v>
       </c>
       <c r="E142" t="s">
-        <v>947</v>
+        <v>490</v>
       </c>
       <c r="F142" t="s">
-        <v>994</v>
+        <v>493</v>
       </c>
       <c r="G142" t="s">
-        <v>959</v>
+        <v>494</v>
       </c>
       <c r="H142" t="s">
-        <v>959</v>
+        <v>495</v>
       </c>
       <c r="I142" t="s">
-        <v>960</v>
-      </c>
-      <c r="J142" s="1" t="s">
-        <v>948</v>
+        <v>496</v>
+      </c>
+      <c r="J142" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8828,34 +8833,48 @@
         <v>1025</v>
       </c>
       <c r="B143" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="C143" t="s">
-        <v>949</v>
+        <v>946</v>
+      </c>
+      <c r="D143" t="s">
+        <v>926</v>
+      </c>
+      <c r="E143" t="s">
+        <v>947</v>
+      </c>
+      <c r="F143" t="s">
+        <v>994</v>
       </c>
       <c r="G143" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="H143" t="s">
-        <v>962</v>
-      </c>
-      <c r="J143" s="1"/>
+        <v>959</v>
+      </c>
+      <c r="I143" t="s">
+        <v>960</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
         <v>1025</v>
       </c>
       <c r="B144" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C144" t="s">
-        <v>963</v>
+        <v>949</v>
       </c>
       <c r="G144" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="H144" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="J144" s="1"/>
     </row>
@@ -8864,16 +8883,16 @@
         <v>1025</v>
       </c>
       <c r="B145" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C145" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="G145" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="H145" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="J145" s="1"/>
     </row>
@@ -8882,16 +8901,16 @@
         <v>1025</v>
       </c>
       <c r="B146" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C146" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="G146" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="H146" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="J146" s="1"/>
     </row>
@@ -8900,13 +8919,16 @@
         <v>1025</v>
       </c>
       <c r="B147" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C147" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="G147" t="s">
-        <v>973</v>
+        <v>970</v>
+      </c>
+      <c r="H147" t="s">
+        <v>971</v>
       </c>
       <c r="J147" s="1"/>
     </row>
@@ -8915,16 +8937,13 @@
         <v>1025</v>
       </c>
       <c r="B148" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C148" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G148" t="s">
-        <v>975</v>
-      </c>
-      <c r="H148" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="J148" s="1"/>
     </row>
@@ -8933,16 +8952,16 @@
         <v>1025</v>
       </c>
       <c r="B149" t="s">
-        <v>977</v>
+        <v>955</v>
       </c>
       <c r="C149" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="G149" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="H149" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="J149" s="1"/>
     </row>
@@ -8951,16 +8970,16 @@
         <v>1025</v>
       </c>
       <c r="B150" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="C150" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="G150" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="H150" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="J150" s="1"/>
     </row>
@@ -8969,16 +8988,16 @@
         <v>1025</v>
       </c>
       <c r="B151" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C151" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="G151" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="H151" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="J151" s="1"/>
     </row>
@@ -8987,32 +9006,18 @@
         <v>1025</v>
       </c>
       <c r="B152" t="s">
-        <v>864</v>
+        <v>957</v>
       </c>
       <c r="C152" t="s">
-        <v>260</v>
-      </c>
-      <c r="D152" t="s">
-        <v>261</v>
-      </c>
-      <c r="E152" t="s">
-        <v>259</v>
-      </c>
-      <c r="F152" t="s">
-        <v>262</v>
+        <v>984</v>
       </c>
       <c r="G152" t="s">
-        <v>263</v>
+        <v>985</v>
       </c>
       <c r="H152" t="s">
-        <v>264</v>
-      </c>
-      <c r="I152" t="s">
-        <v>265</v>
-      </c>
-      <c r="J152" t="s">
-        <v>266</v>
-      </c>
+        <v>986</v>
+      </c>
+      <c r="J152" s="1"/>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
@@ -9022,28 +9027,28 @@
         <v>864</v>
       </c>
       <c r="C153" t="s">
-        <v>534</v>
+        <v>260</v>
       </c>
       <c r="D153" t="s">
-        <v>535</v>
+        <v>261</v>
       </c>
       <c r="E153" t="s">
-        <v>536</v>
+        <v>259</v>
       </c>
       <c r="F153" t="s">
-        <v>833</v>
+        <v>262</v>
       </c>
       <c r="G153" t="s">
-        <v>537</v>
+        <v>263</v>
       </c>
       <c r="H153" t="s">
-        <v>538</v>
+        <v>264</v>
       </c>
       <c r="I153" t="s">
-        <v>539</v>
+        <v>265</v>
       </c>
       <c r="J153" t="s">
-        <v>540</v>
+        <v>266</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9054,28 +9059,28 @@
         <v>864</v>
       </c>
       <c r="C154" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D154" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="E154" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="F154" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G154" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="H154" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="I154" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="J154" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9086,54 +9091,57 @@
         <v>864</v>
       </c>
       <c r="C155" t="s">
-        <v>164</v>
+        <v>541</v>
       </c>
       <c r="D155" t="s">
-        <v>165</v>
+        <v>542</v>
       </c>
       <c r="E155" t="s">
-        <v>163</v>
+        <v>543</v>
       </c>
       <c r="F155" t="s">
-        <v>166</v>
+        <v>834</v>
       </c>
       <c r="G155" t="s">
-        <v>167</v>
+        <v>544</v>
       </c>
       <c r="H155" t="s">
-        <v>168</v>
+        <v>545</v>
+      </c>
+      <c r="I155" t="s">
+        <v>546</v>
       </c>
       <c r="J155" t="s">
-        <v>169</v>
+        <v>547</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="B156" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="C156" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="D156" t="s">
-        <v>825</v>
+        <v>165</v>
       </c>
       <c r="E156" t="s">
-        <v>824</v>
+        <v>163</v>
       </c>
       <c r="F156" t="s">
-        <v>826</v>
+        <v>166</v>
       </c>
       <c r="G156" t="s">
-        <v>827</v>
+        <v>167</v>
       </c>
       <c r="H156" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="J156" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9147,25 +9155,22 @@
         <v>115</v>
       </c>
       <c r="D157" t="s">
-        <v>609</v>
+        <v>825</v>
       </c>
       <c r="E157" t="s">
-        <v>610</v>
+        <v>824</v>
       </c>
       <c r="F157" t="s">
-        <v>842</v>
+        <v>826</v>
       </c>
       <c r="G157" t="s">
-        <v>611</v>
+        <v>827</v>
       </c>
       <c r="H157" t="s">
         <v>119</v>
       </c>
-      <c r="I157" t="s">
-        <v>612</v>
-      </c>
       <c r="J157" t="s">
-        <v>613</v>
+        <v>120</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9179,16 +9184,25 @@
         <v>115</v>
       </c>
       <c r="D158" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="E158" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="F158" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G158" t="s">
-        <v>616</v>
+        <v>611</v>
+      </c>
+      <c r="H158" t="s">
+        <v>119</v>
+      </c>
+      <c r="I158" t="s">
+        <v>612</v>
+      </c>
+      <c r="J158" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9202,25 +9216,16 @@
         <v>115</v>
       </c>
       <c r="D159" t="s">
-        <v>535</v>
+        <v>614</v>
       </c>
       <c r="E159" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="F159" t="s">
         <v>843</v>
       </c>
       <c r="G159" t="s">
         <v>616</v>
-      </c>
-      <c r="H159" t="s">
-        <v>618</v>
-      </c>
-      <c r="I159" t="s">
-        <v>619</v>
-      </c>
-      <c r="J159" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9234,10 +9239,10 @@
         <v>115</v>
       </c>
       <c r="D160" t="s">
-        <v>621</v>
+        <v>535</v>
       </c>
       <c r="E160" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="F160" t="s">
         <v>843</v>
@@ -9249,10 +9254,10 @@
         <v>618</v>
       </c>
       <c r="I160" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="J160" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9266,25 +9271,25 @@
         <v>115</v>
       </c>
       <c r="D161" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="E161" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="F161" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G161" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="H161" t="s">
-        <v>119</v>
+        <v>618</v>
       </c>
       <c r="I161" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="J161" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9298,25 +9303,25 @@
         <v>115</v>
       </c>
       <c r="D162" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="E162" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="F162" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G162" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="H162" t="s">
-        <v>618</v>
+        <v>119</v>
       </c>
       <c r="I162" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="J162" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9330,22 +9335,25 @@
         <v>115</v>
       </c>
       <c r="D163" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="E163" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="F163" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G163" t="s">
-        <v>635</v>
+        <v>616</v>
+      </c>
+      <c r="H163" t="s">
+        <v>618</v>
       </c>
       <c r="I163" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="J163" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9359,10 +9367,10 @@
         <v>115</v>
       </c>
       <c r="D164" t="s">
-        <v>317</v>
+        <v>633</v>
       </c>
       <c r="E164" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="F164" t="s">
         <v>844</v>
@@ -9371,10 +9379,10 @@
         <v>635</v>
       </c>
       <c r="I164" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="J164" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9388,25 +9396,22 @@
         <v>115</v>
       </c>
       <c r="D165" t="s">
-        <v>621</v>
+        <v>317</v>
       </c>
       <c r="E165" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F165" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="G165" t="s">
-        <v>642</v>
-      </c>
-      <c r="H165" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="I165" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="J165" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9414,25 +9419,31 @@
         <v>1022</v>
       </c>
       <c r="B166" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
       <c r="C166" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="D166" t="s">
-        <v>10</v>
+        <v>621</v>
       </c>
       <c r="E166" t="s">
-        <v>8</v>
+        <v>641</v>
       </c>
       <c r="F166" t="s">
-        <v>11</v>
+        <v>842</v>
       </c>
       <c r="G166" t="s">
-        <v>12</v>
+        <v>642</v>
       </c>
       <c r="H166" t="s">
-        <v>13</v>
+        <v>643</v>
+      </c>
+      <c r="I166" t="s">
+        <v>644</v>
+      </c>
+      <c r="J166" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9443,28 +9454,22 @@
         <v>880</v>
       </c>
       <c r="C167" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D167" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E167" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F167" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G167" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H167" t="s">
-        <v>19</v>
-      </c>
-      <c r="I167" t="s">
-        <v>20</v>
-      </c>
-      <c r="J167" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9478,10 +9483,10 @@
         <v>15</v>
       </c>
       <c r="D168" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E168" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F168" t="s">
         <v>17</v>
@@ -9493,10 +9498,10 @@
         <v>19</v>
       </c>
       <c r="I168" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J168" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9510,25 +9515,25 @@
         <v>15</v>
       </c>
       <c r="D169" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E169" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F169" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G169" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H169" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I169" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J169" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9542,10 +9547,10 @@
         <v>15</v>
       </c>
       <c r="D170" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E170" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -9557,10 +9562,10 @@
         <v>30</v>
       </c>
       <c r="I170" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J170" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9574,10 +9579,10 @@
         <v>15</v>
       </c>
       <c r="D171" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E171" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F171" t="s">
         <v>28</v>
@@ -9589,10 +9594,10 @@
         <v>30</v>
       </c>
       <c r="I171" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J171" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9603,42 +9608,57 @@
         <v>880</v>
       </c>
       <c r="C172" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="D172" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="E172" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="F172" t="s">
-        <v>117</v>
+        <v>28</v>
       </c>
       <c r="G172" t="s">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="H172" t="s">
-        <v>119</v>
+        <v>30</v>
+      </c>
+      <c r="I172" t="s">
+        <v>39</v>
       </c>
       <c r="J172" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" t="s">
-        <v>888</v>
+        <v>1022</v>
+      </c>
+      <c r="B173" t="s">
+        <v>880</v>
       </c>
       <c r="C173" t="s">
-        <v>913</v>
+        <v>115</v>
       </c>
       <c r="D173" t="s">
-        <v>889</v>
+        <v>116</v>
       </c>
       <c r="E173" t="s">
-        <v>893</v>
-      </c>
-      <c r="I173" t="s">
-        <v>904</v>
+        <v>114</v>
+      </c>
+      <c r="F173" t="s">
+        <v>117</v>
+      </c>
+      <c r="G173" t="s">
+        <v>118</v>
+      </c>
+      <c r="H173" t="s">
+        <v>119</v>
+      </c>
+      <c r="J173" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9649,13 +9669,13 @@
         <v>913</v>
       </c>
       <c r="D174" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E174" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="I174" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9666,13 +9686,13 @@
         <v>913</v>
       </c>
       <c r="D175" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E175" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="I175" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9683,13 +9703,13 @@
         <v>913</v>
       </c>
       <c r="D176" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E176" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="I176" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -9700,13 +9720,13 @@
         <v>913</v>
       </c>
       <c r="D177" t="s">
-        <v>902</v>
+        <v>892</v>
       </c>
       <c r="E177" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="I177" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -9720,10 +9740,10 @@
         <v>902</v>
       </c>
       <c r="E178" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="I178" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -9734,13 +9754,13 @@
         <v>913</v>
       </c>
       <c r="D179" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E179" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="I179" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -9754,10 +9774,10 @@
         <v>903</v>
       </c>
       <c r="E180" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="I180" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -9771,10 +9791,10 @@
         <v>903</v>
       </c>
       <c r="E181" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="I181" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -9788,10 +9808,10 @@
         <v>903</v>
       </c>
       <c r="E182" t="s">
-        <v>1044</v>
+        <v>901</v>
       </c>
       <c r="I182" t="s">
-        <v>1045</v>
+        <v>912</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -9805,10 +9825,10 @@
         <v>903</v>
       </c>
       <c r="E183" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="I183" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -9822,32 +9842,49 @@
         <v>903</v>
       </c>
       <c r="E184" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="I184" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" t="s">
-        <v>1054</v>
+        <v>888</v>
       </c>
       <c r="C185" t="s">
         <v>913</v>
       </c>
       <c r="D185" t="s">
+        <v>903</v>
+      </c>
+      <c r="E185" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I185" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A186" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C186" t="s">
+        <v>913</v>
+      </c>
+      <c r="D186" t="s">
         <v>1055</v>
       </c>
-      <c r="E185" t="s">
+      <c r="E186" t="s">
         <v>1056</v>
       </c>
-      <c r="I185" t="s">
+      <c r="I186" t="s">
         <v>1057</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A43:J172">
-    <sortCondition ref="A43:A172"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A43:J173">
+    <sortCondition ref="A43:A173"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -9855,7 +9892,7 @@
     <hyperlink ref="J87" r:id="rId2" xr:uid="{04B79727-E872-4B92-B9FF-E52CDD567289}"/>
     <hyperlink ref="J88" r:id="rId3" xr:uid="{58FC3E9B-DA5E-47AE-A0FA-48744DC7E69C}"/>
     <hyperlink ref="J120" r:id="rId4" xr:uid="{0CDDE2B0-9A66-4763-82CA-FB9054DBD36D}"/>
-    <hyperlink ref="J142" r:id="rId5" xr:uid="{D959C86A-275E-4D89-91FD-60DBE69A6EE8}"/>
+    <hyperlink ref="J143" r:id="rId5" xr:uid="{D959C86A-275E-4D89-91FD-60DBE69A6EE8}"/>
     <hyperlink ref="J82" r:id="rId6" xr:uid="{AE797D3F-4BC0-45F7-BAAF-49AAE05332D6}"/>
     <hyperlink ref="J119" r:id="rId7" xr:uid="{E353EA49-C20B-4A50-9E3E-3B8FC192D763}"/>
     <hyperlink ref="J100" r:id="rId8" xr:uid="{A98CDD58-6463-49F3-9952-BC0BEE6FEAA2}"/>
